--- a/Settlements of Albany.xlsx
+++ b/Settlements of Albany.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a38c727b2e27c7e/Documents/Creative Writing/Tabletop/Albany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5290763A-AF8B-41AA-9B36-0F08EBB5F7B1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="330">
   <si>
     <t>Old Kingdom</t>
   </si>
@@ -258,9 +258,6 @@
     <t>Caereustace</t>
   </si>
   <si>
-    <t>Pen Maelow</t>
-  </si>
-  <si>
     <t>Aberteifi</t>
   </si>
   <si>
@@ -673,13 +670,361 @@
   </si>
   <si>
     <t>Mootburne</t>
+  </si>
+  <si>
+    <t>Arms</t>
+  </si>
+  <si>
+    <t>Lord</t>
+  </si>
+  <si>
+    <t>vert a stone circle argent</t>
+  </si>
+  <si>
+    <t>Walter de Hameton</t>
+  </si>
+  <si>
+    <t>per chevron vairy argent and azure and papelonny gules and or, on a sun or a horse rampant sable</t>
+  </si>
+  <si>
+    <t>William FitzAlan</t>
+  </si>
+  <si>
+    <t>vert, a dragon displayed gules</t>
+  </si>
+  <si>
+    <t>Gruffudd Sant-Ioan</t>
+  </si>
+  <si>
+    <t>vert, a dragon rampant gules</t>
+  </si>
+  <si>
+    <t>quarterly checky azure argent, crusilly sable or, three moon increscent argent</t>
+  </si>
+  <si>
+    <t>per saltire checky azure argent, crusilly sable or, three moon decrescent argent</t>
+  </si>
+  <si>
+    <t>per pale embattled argent and azure, an ox gules</t>
+  </si>
+  <si>
+    <t>per fess argent and azure, A chalice or,motto of "Er Cof Amdanof I"</t>
+  </si>
+  <si>
+    <t>party per barry wavy gules and azure, a castle or, supporters pegasus Segreant argent and dragon rampant gules</t>
+  </si>
+  <si>
+    <t>per pale ermine and gules, in second quarter a wolf sejant, in fourth quarter a ship argent</t>
+  </si>
+  <si>
+    <t>per chevron gules and lozengy azure and argent, in chief a sun or, a sunburst or</t>
+  </si>
+  <si>
+    <t>lozengy argent and azure, a knight mounted sable armoured argent maned argent caparisoned or, unguled or</t>
+  </si>
+  <si>
+    <t>quarterly estencely azure and argent and roundelly argent and azure, three lions rampant or</t>
+  </si>
+  <si>
+    <t>per pale fretty argent and azure and argent, in sinister side a lion rampant azure</t>
+  </si>
+  <si>
+    <t>per chausse fretty azure and argent and argent, a fish embowed or</t>
+  </si>
+  <si>
+    <t>rosace vert and or, a gauntlet argent en soleil much smaller</t>
+  </si>
+  <si>
+    <t>purpure, a rosary or above a lion dormant argent</t>
+  </si>
+  <si>
+    <t>erminois, a dragon rampant sable</t>
+  </si>
+  <si>
+    <t>azure, seven crosses couped in annulo or, a dragon head much smaller caboshed gules</t>
+  </si>
+  <si>
+    <t>vert, two dragon heads couped gules respecting each other</t>
+  </si>
+  <si>
+    <t>gules, two bends or, a dog-head-collared-couped gules</t>
+  </si>
+  <si>
+    <t>azure, a dragon in annulo gules</t>
+  </si>
+  <si>
+    <t>Pen Maelor</t>
+  </si>
+  <si>
+    <t>vert, ford, in sinister side a dragon rampant gules and in dexter side a sea dragon gules</t>
+  </si>
+  <si>
+    <t>sable, a dragon couchant argent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checky vert and sable, a bow with arrow nocked or </t>
+  </si>
+  <si>
+    <t>fretty sable and gules, a quarter ermine</t>
+  </si>
+  <si>
+    <t>per fess vert and estencely azure and vert, three ravens sable</t>
+  </si>
+  <si>
+    <t>argent, four cinquefoils gules arranged two one one</t>
+  </si>
+  <si>
+    <t>Duke William FitzAlan</t>
+  </si>
+  <si>
+    <t>Earl Robert Daubenay</t>
+  </si>
+  <si>
+    <t>Earl Robert Hylton</t>
+  </si>
+  <si>
+    <t>Earl William "Wakeful" Hylton</t>
+  </si>
+  <si>
+    <t>Duke Walter de Hameton</t>
+  </si>
+  <si>
+    <t>Earl Alisaunder de Hameton</t>
+  </si>
+  <si>
+    <t>Earl Owain ap Ieuan</t>
+  </si>
+  <si>
+    <t>Duke Gruffudd Sant-Ioan</t>
+  </si>
+  <si>
+    <t>Earl Rhodri Gwinwr</t>
+  </si>
+  <si>
+    <t>Earl Llwelyn ap Owain o'r Gaer</t>
+  </si>
+  <si>
+    <t>sable, a cross vert, four wolves rampant argent combatant</t>
+  </si>
+  <si>
+    <t>mullety of 10 azure and or, a wolf rampant argent</t>
+  </si>
+  <si>
+    <t>sable, a chevron ploye ermine, three wolf's heads argent</t>
+  </si>
+  <si>
+    <t>per fess azure and barry wavy azure and argent, in chief a beaver or</t>
+  </si>
+  <si>
+    <t>barry wavy azure and argent, in fess three croziers vert above a mitre or</t>
+  </si>
+  <si>
+    <t>barry bowed vert and argent, a boars head caboshed or</t>
+  </si>
+  <si>
+    <t>barry wavy gules and azure, a wolf rampant gules</t>
+  </si>
+  <si>
+    <t>sable, ford, a tower argent above a ship or</t>
+  </si>
+  <si>
+    <t>per fess gules and argent, in first quarter a virgin argent and in second quarter a paschal lamb argent banner or and a mitre gules smaller</t>
+  </si>
+  <si>
+    <t>per fess argent and checky azure and argent, a mitre vert surrounded by two angels kneeling attired or respecting each other</t>
+  </si>
+  <si>
+    <t>per bend mullety of 10 or and gules and maily azure and or, in dexter side a bear rampant argent</t>
+  </si>
+  <si>
+    <t>per fess arched gules and vert, enty in point argent, in fess a castle triple towered much smaller argent, between in base two horses respectant sable larger</t>
+  </si>
+  <si>
+    <t>per fess argent and gules, in chief two Dog Courant Collared gules and in base a boar passant argent. Supporters lymphad</t>
+  </si>
+  <si>
+    <t>per pale chequy argent and azure and lozengy argent and azure, a fess azure charged with three bells or, in chief a crown or and in base a tower argent.</t>
+  </si>
+  <si>
+    <t>Laird Murdoch MacNab</t>
+  </si>
+  <si>
+    <t>azure, a boar argent</t>
+  </si>
+  <si>
+    <t>John of Jorvale*</t>
+  </si>
+  <si>
+    <t>King Henry of Aberlune</t>
+  </si>
+  <si>
+    <t>or, a dog courant gules</t>
+  </si>
+  <si>
+    <t>Earl Richard of Jorvale</t>
+  </si>
+  <si>
+    <t>sable, a dolmen argent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sable, ford, a raven or </t>
+  </si>
+  <si>
+    <t>barry wavy vert and or, three wheat sheafs or</t>
+  </si>
+  <si>
+    <t>Bishop Richard</t>
+  </si>
+  <si>
+    <t>per bend sinister azure and sable, three cranes argent legged or beaked gules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quarterly 1st and 4th, papelonny vert and argent, 2nd and 3rd, paly sable and or a falcon striking argent; </t>
+  </si>
+  <si>
+    <t>barry indented one in the other vert and or</t>
+  </si>
+  <si>
+    <t>argent, ford, a cross or</t>
+  </si>
+  <si>
+    <t>houndstooth gules and vert</t>
+  </si>
+  <si>
+    <t>houndstooth gules and azure</t>
+  </si>
+  <si>
+    <t>gules, three annulets interlaced vert</t>
+  </si>
+  <si>
+    <t>azure, a triskele vert</t>
+  </si>
+  <si>
+    <t>orly vert and azure</t>
+  </si>
+  <si>
+    <t>azure, three roundels sable</t>
+  </si>
+  <si>
+    <t>tartan gules and sable</t>
+  </si>
+  <si>
+    <t>tartan azure and vert</t>
+  </si>
+  <si>
+    <t>tartan or and gules</t>
+  </si>
+  <si>
+    <t>azure, a savage head vert</t>
+  </si>
+  <si>
+    <t>glen check azure and vert</t>
+  </si>
+  <si>
+    <t>glen check azure and or</t>
+  </si>
+  <si>
+    <t>shepherd check sable and vert</t>
+  </si>
+  <si>
+    <t>shepherd check or and vert</t>
+  </si>
+  <si>
+    <t>shepherd check gules and vert</t>
+  </si>
+  <si>
+    <t>azure, three trees vert</t>
+  </si>
+  <si>
+    <t>argent, three hearts gules</t>
+  </si>
+  <si>
+    <t>azure, an elk trippant argent</t>
+  </si>
+  <si>
+    <t>or, three stags lodged azure</t>
+  </si>
+  <si>
+    <t>or a yale rampant gules, tressure gules</t>
+  </si>
+  <si>
+    <t>checky or and sable, a griffin passant gules</t>
+  </si>
+  <si>
+    <t>orly gules and or</t>
+  </si>
+  <si>
+    <t>vert, a pantheon rampant or</t>
+  </si>
+  <si>
+    <t>vert, ford, three trefoils argent in fess</t>
+  </si>
+  <si>
+    <t>gules, ford, a bend argent, a dragon's head or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sable, ford, three gauntlet argent in fess </t>
+  </si>
+  <si>
+    <t>sable, a bear carrying a cross argent</t>
+  </si>
+  <si>
+    <t>quarterly gules and azure, a cross or</t>
+  </si>
+  <si>
+    <t>per fess embattled, azure and gules, a pitcher or</t>
+  </si>
+  <si>
+    <t>sable three dragon heads or</t>
+  </si>
+  <si>
+    <t>argent a mitre or above a dragon's head or</t>
+  </si>
+  <si>
+    <t>azure, a gorge vert</t>
+  </si>
+  <si>
+    <t>quarterly gules and vert, an inescutcheon sable, overall a dragon rampant or</t>
+  </si>
+  <si>
+    <t>Earl Emrys Cadwallader</t>
+  </si>
+  <si>
+    <t>Sir Howell Tresco</t>
+  </si>
+  <si>
+    <t>Earl Sjoskip</t>
+  </si>
+  <si>
+    <t>fretty vert and argent, two ash trees eradicated or above a stag lodged reguardant or</t>
+  </si>
+  <si>
+    <t>checky vert and argent, an ash trees eradicated or</t>
+  </si>
+  <si>
+    <t>quarterly checky argent and azure, and maily sable and or, crancelin or</t>
+  </si>
+  <si>
+    <t>quarterly lozengy argent and azure and mullety of 10 sable and or</t>
+  </si>
+  <si>
+    <t>azure, in chief fess invected or, in chief three elder blossoms argent in fess</t>
+  </si>
+  <si>
+    <t>mullety of 10 azure and argent, a tree or leafed vert</t>
+  </si>
+  <si>
+    <t>per fess gules and papelonny azure and argent</t>
+  </si>
+  <si>
+    <t>quarterly lozengy argent and azure and checky azure and argent, five roundels or in orle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -698,8 +1043,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -727,6 +1078,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
@@ -823,14 +1186,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -844,8 +1206,14 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,6 +1287,10 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFF6D6D"/>
+      <color rgb="FF729FCF"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1228,17 +1600,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="120" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="1025" width="11.5703125"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="133.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="1025" width="11.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1248,11 +1622,17 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E1" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -1265,300 +1645,376 @@
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="6"/>
+      <c r="B3" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="D3" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="D4" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="D5" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="D7" s="8" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="D8" s="8" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="D8" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="D9" s="8" t="s">
+      <c r="F8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="D9" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="D10" s="8" t="s">
+      <c r="F9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="D10" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="D11" s="8" t="s">
+      <c r="F10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="D11" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="F11" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="D13" s="8" t="s">
+      <c r="F12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="D13" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="D14" s="8" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="D14" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="D15" s="8" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="D16" s="8" t="s">
+      <c r="F15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="D16" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="D17" s="8" t="s">
+      <c r="F16" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="D17" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="F17" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="D19" s="8" t="s">
+      <c r="F18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="D20" s="8" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="D20" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="D21" s="8" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="D21" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="D22" s="8" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="D22" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="D23" s="8" t="s">
+      <c r="F22" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="D23" s="7" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="D24" s="8" t="s">
+      <c r="F23" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="D24" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
       <c r="C25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="D26" s="8" t="s">
+      <c r="F25" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="D26" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="D27" s="8" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="D27" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="D28" s="8" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="D28" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="F28" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
       <c r="C29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="D30" s="8" t="s">
+      <c r="F29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="D30" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="D31" s="8" t="s">
+      <c r="F30" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="D31" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="D32" s="8" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="D32" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="D33" s="8" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="D33" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
+      <c r="F33" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="D35" s="8" t="s">
+      <c r="F34" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="D35" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="D36" s="8" t="s">
+      <c r="F35" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="D36" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
+      <c r="F36" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="D38" s="8" t="s">
+      <c r="F37" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="D38" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="D39" s="8" t="s">
+      <c r="F38" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="D39" s="7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11" t="s">
+      <c r="F39" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="12" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -1567,1069 +2023,1332 @@
       <c r="D41" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="D42" s="8" t="s">
+      <c r="F41" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="12"/>
+      <c r="B42" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="D43" s="8" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="D44" s="8" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="D44" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
-      <c r="D45" s="8" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+      <c r="D45" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
-      <c r="D46" s="8" t="s">
+      <c r="F45" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="D46" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
-      <c r="D47" s="8" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="D47" s="7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
+      <c r="F47" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
       <c r="C48" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="13"/>
-      <c r="B49" s="13"/>
-      <c r="D49" s="8" t="s">
+      <c r="F48" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+      <c r="D49" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="13"/>
-      <c r="B50" s="13"/>
-      <c r="D50" s="8" t="s">
+      <c r="F49" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+      <c r="D50" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="D51" s="8" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="D51" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="D52" s="8" t="s">
+      <c r="F51" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+      <c r="D52" s="7" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="13"/>
-      <c r="B53" s="13"/>
-      <c r="D53" s="8" t="s">
+      <c r="F52" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="D53" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
-      <c r="D54" s="8" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+      <c r="D54" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
-      <c r="D55" s="8" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="D55" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="D56" s="8" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="D56" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="D57" s="8" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="D57" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
-      <c r="D58" s="8" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+      <c r="D58" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
       <c r="C59" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="13"/>
-      <c r="B60" s="13"/>
-      <c r="D60" s="8" t="s">
+      <c r="F59" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="D60" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="13"/>
-      <c r="B61" s="13"/>
-      <c r="D61" s="8" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="D61" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="13"/>
-      <c r="B62" s="13"/>
-      <c r="D62" s="8" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="D62" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F62" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="D63" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="13"/>
-      <c r="B63" s="13"/>
-      <c r="D63" s="8" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="13"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="8" t="s">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="12"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="13"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="11" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="13"/>
-      <c r="B66" s="13" t="s">
+      <c r="C66" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="E66" t="s">
+        <v>255</v>
+      </c>
+      <c r="F66" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="13"/>
-      <c r="B67" s="13"/>
-      <c r="D67" s="8" t="s">
+      <c r="F67" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="13"/>
-      <c r="B68" s="13"/>
-      <c r="D68" s="8" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
+      <c r="D69" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="13"/>
-      <c r="B69" s="13"/>
-      <c r="D69" s="8" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+      <c r="D70" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="13"/>
-      <c r="B70" s="13"/>
-      <c r="D70" s="8" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+      <c r="D71" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
-      <c r="D71" s="8" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="12"/>
+      <c r="B72" s="12"/>
+      <c r="D72" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
-      <c r="D72" s="8" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="12"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="13"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="F73" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+      <c r="D74" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="13"/>
-      <c r="B74" s="13"/>
-      <c r="D74" s="8" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+      <c r="D75" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="13"/>
-      <c r="B75" s="13"/>
-      <c r="D75" s="8" t="s">
+      <c r="F75" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
+      <c r="D76" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="13"/>
-      <c r="B76" s="13"/>
-      <c r="D76" s="8" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="12"/>
+      <c r="B77" s="12"/>
+      <c r="D77" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="13"/>
-      <c r="B77" s="13"/>
-      <c r="D77" s="8" t="s">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+      <c r="D78" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="13"/>
-      <c r="B78" s="13"/>
-      <c r="D78" s="8" t="s">
+      <c r="F78" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+      <c r="D79" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
-      <c r="D79" s="8" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="12"/>
+      <c r="B80" s="12"/>
+      <c r="D80" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="13"/>
-      <c r="B80" s="13"/>
-      <c r="D80" s="8" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="12"/>
+      <c r="B81" s="12"/>
+      <c r="D81" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="13"/>
-      <c r="B81" s="13"/>
-      <c r="D81" s="8" t="s">
+      <c r="F81" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="12"/>
+      <c r="B82" s="12"/>
+      <c r="D82" s="7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="13"/>
-      <c r="B82" s="13"/>
-      <c r="D82" s="8" t="s">
+      <c r="F82" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="12"/>
+      <c r="B83" s="12"/>
+      <c r="D83" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="13"/>
-      <c r="B83" s="13"/>
-      <c r="D83" s="8" t="s">
+      <c r="F83" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="12"/>
+      <c r="B84" s="12"/>
+      <c r="D84" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
-      <c r="D84" s="8" t="s">
+      <c r="E84" t="s">
+        <v>254</v>
+      </c>
+      <c r="F84" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="12"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="13"/>
-      <c r="B85" s="13"/>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="E85" t="s">
+        <v>256</v>
+      </c>
+      <c r="F85" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="12"/>
+      <c r="B86" s="12"/>
+      <c r="D86" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="13"/>
-      <c r="B86" s="13"/>
-      <c r="D86" s="8" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="12"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="13"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="E87" t="s">
+        <v>257</v>
+      </c>
+      <c r="F87" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="12"/>
+      <c r="B88" s="12"/>
+      <c r="D88" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="13"/>
-      <c r="B88" s="13"/>
-      <c r="D88" s="8" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="12"/>
+      <c r="B89" s="12"/>
+      <c r="D89" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="13"/>
-      <c r="B89" s="13"/>
-      <c r="D89" s="8" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="12"/>
+      <c r="B90" s="12"/>
+      <c r="D90" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="13"/>
-      <c r="B90" s="13"/>
-      <c r="D90" s="8" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="12"/>
+      <c r="B91" s="12"/>
+      <c r="D91" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="13"/>
-      <c r="B91" s="13"/>
-      <c r="D91" s="8" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="12"/>
+      <c r="B92" s="12"/>
+      <c r="D92" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="13"/>
-      <c r="B92" s="13"/>
-      <c r="D92" s="8" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="12"/>
+      <c r="B93" s="12"/>
+      <c r="D93" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="13"/>
-      <c r="B93" s="13"/>
-      <c r="D93" s="8" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="12"/>
+      <c r="B94" s="12"/>
+      <c r="D94" s="7" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="13"/>
-      <c r="B94" s="13"/>
-      <c r="D94" s="8" t="s">
+      <c r="F94" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="12"/>
+      <c r="B95" s="12"/>
+      <c r="D95" s="7" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="13"/>
-      <c r="B95" s="13"/>
-      <c r="D95" s="8" t="s">
+      <c r="F95" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="12"/>
+      <c r="B96" s="12"/>
+      <c r="D96" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="13"/>
-      <c r="B96" s="13"/>
-      <c r="D96" s="8" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="12"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="13"/>
-      <c r="B97" s="13"/>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="E97" t="s">
+        <v>319</v>
+      </c>
+      <c r="F97" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="14"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="10" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="15"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="11" t="s">
+      <c r="E98" t="s">
+        <v>320</v>
+      </c>
+      <c r="F98" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="15" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="16" t="s">
+      <c r="B99" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="C99" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F99" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="16"/>
+      <c r="B100" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D100" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="17"/>
-      <c r="B100" s="17"/>
-      <c r="D100" s="8" t="s">
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="16"/>
+      <c r="B101" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="D101" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="17"/>
-      <c r="B101" s="17"/>
-      <c r="D101" s="8" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="16"/>
+      <c r="B102" s="16"/>
+      <c r="D102" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="17"/>
-      <c r="B102" s="17"/>
-      <c r="D102" s="8" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="16"/>
+      <c r="B103" s="16"/>
+      <c r="D103" s="7" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="17"/>
-      <c r="B103" s="17"/>
-      <c r="D103" s="8" t="s">
+      <c r="F103" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="16"/>
+      <c r="B104" s="16"/>
+      <c r="D104" s="7" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="17"/>
-      <c r="B104" s="17"/>
-      <c r="D104" s="8" t="s">
+      <c r="E104" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="16"/>
+      <c r="B105" s="16"/>
+      <c r="D105" s="7" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="17"/>
-      <c r="B105" s="17"/>
-      <c r="D105" s="8" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="16"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="17"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E106" t="s">
+        <v>277</v>
+      </c>
+      <c r="F106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="16"/>
+      <c r="B107" s="16"/>
+      <c r="D107" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D106" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="17"/>
-      <c r="B107" s="17"/>
-      <c r="D107" s="8" t="s">
+      <c r="F107" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="16"/>
+      <c r="B108" s="16"/>
+      <c r="D108" s="7" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="17"/>
-      <c r="B108" s="17"/>
-      <c r="D108" s="8" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="16"/>
+      <c r="B109" s="16"/>
+      <c r="D109" s="7" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="17"/>
-      <c r="B109" s="17"/>
-      <c r="D109" s="8" t="s">
+      <c r="F109" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="16"/>
+      <c r="B110" s="16"/>
+      <c r="D110" s="7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="17"/>
-      <c r="B110" s="17"/>
-      <c r="D110" s="8" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="16"/>
+      <c r="B111" s="16"/>
+      <c r="D111" s="7" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="17"/>
-      <c r="B111" s="17"/>
-      <c r="D111" s="8" t="s">
+      <c r="F111" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="16"/>
+      <c r="B112" s="16"/>
+      <c r="D112" s="7" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="17"/>
-      <c r="B112" s="17"/>
-      <c r="D112" s="8" t="s">
+      <c r="F112" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="D113" s="7" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="17"/>
-      <c r="B113" s="17"/>
-      <c r="D113" s="8" t="s">
+      <c r="F113" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="16"/>
+      <c r="B114" s="16"/>
+      <c r="D114" s="7" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="17"/>
-      <c r="B114" s="17"/>
-      <c r="D114" s="8" t="s">
+      <c r="F114" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="16"/>
+      <c r="B115" s="16"/>
+      <c r="D115" s="7" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="17"/>
-      <c r="B115" s="17"/>
-      <c r="D115" s="8" t="s">
+      <c r="F115" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="16"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="17"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F116" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="16"/>
+      <c r="B117" s="16"/>
+      <c r="D117" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D116" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="17"/>
-      <c r="B117" s="17"/>
-      <c r="D117" s="8" t="s">
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="16"/>
+      <c r="B118" s="16"/>
+      <c r="D118" s="7" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="17"/>
-      <c r="B118" s="17"/>
-      <c r="D118" s="8" t="s">
+      <c r="F118" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="16"/>
+      <c r="B119" s="16"/>
+      <c r="D119" s="7" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="17"/>
-      <c r="B119" s="17"/>
-      <c r="D119" s="8" t="s">
+      <c r="F119" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="16"/>
+      <c r="B120" s="16"/>
+      <c r="D120" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="17"/>
-      <c r="B120" s="17"/>
-      <c r="D120" s="8" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="16"/>
+      <c r="B121" s="16"/>
+      <c r="D121" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="17"/>
-      <c r="B121" s="17"/>
-      <c r="D121" s="8" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="16"/>
+      <c r="B122" s="16"/>
+      <c r="D122" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="17"/>
-      <c r="B122" s="17"/>
-      <c r="D122" s="8" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="16"/>
+      <c r="B123" s="16"/>
+      <c r="D123" s="7" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="17"/>
-      <c r="B123" s="17"/>
-      <c r="D123" s="8" t="s">
+      <c r="F123" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="16"/>
+      <c r="B124" s="16"/>
+      <c r="D124" s="7" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="17"/>
-      <c r="B124" s="17"/>
-      <c r="D124" s="8" t="s">
+      <c r="F124" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="16"/>
+      <c r="B125" s="16"/>
+      <c r="D125" s="7" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="17"/>
-      <c r="B125" s="17"/>
-      <c r="D125" s="8" t="s">
+      <c r="F125" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="16"/>
+      <c r="B126" s="16"/>
+      <c r="D126" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="17"/>
-      <c r="B126" s="17"/>
-      <c r="D126" s="8" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127" s="16"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="17"/>
-      <c r="B127" s="17"/>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F127" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128" s="17"/>
+      <c r="B128" s="17"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D127" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="18"/>
-      <c r="B128" s="18"/>
-      <c r="C128" s="10"/>
-      <c r="D128" s="11" t="s">
+      <c r="F128" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" s="18" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="19" t="s">
+      <c r="B129" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B129" s="20" t="s">
+      <c r="C129" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E129" t="s">
+        <v>248</v>
+      </c>
+      <c r="F129" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" s="18"/>
+      <c r="B130" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D129" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="19"/>
-      <c r="B130" s="19"/>
-      <c r="D130" s="8" t="s">
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" s="18"/>
+      <c r="B131" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="D131" s="7" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="19"/>
-      <c r="B131" s="19"/>
-      <c r="D131" s="8" t="s">
+      <c r="F131" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" s="18"/>
+      <c r="B132" s="24"/>
+      <c r="D132" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="19"/>
-      <c r="B132" s="19"/>
-      <c r="D132" s="8" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="18"/>
+      <c r="B133" s="24"/>
+      <c r="D133" s="7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133" s="19"/>
-      <c r="B133" s="19"/>
-      <c r="D133" s="8" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" s="18"/>
+      <c r="B134" s="24"/>
+      <c r="D134" s="7" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" s="19"/>
-      <c r="B134" s="19"/>
-      <c r="D134" s="8" t="s">
+      <c r="F134" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="18"/>
+      <c r="B135" s="24"/>
+      <c r="D135" s="7" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="19"/>
-      <c r="B135" s="19"/>
-      <c r="D135" s="8" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" s="18"/>
+      <c r="B136" s="24"/>
+      <c r="D136" s="7" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" s="19"/>
-      <c r="B136" s="19"/>
-      <c r="D136" s="8" t="s">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="18"/>
+      <c r="B137" s="24"/>
+      <c r="D137" s="7" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" s="19"/>
-      <c r="B137" s="19"/>
-      <c r="D137" s="8" t="s">
+      <c r="F137" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="18"/>
+      <c r="B138" s="24"/>
+      <c r="D138" s="7" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" s="19"/>
-      <c r="B138" s="19"/>
-      <c r="D138" s="8" t="s">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="18"/>
+      <c r="B139" s="24"/>
+      <c r="D139" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" s="19"/>
-      <c r="B139" s="19"/>
-      <c r="D139" s="8" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="18"/>
+      <c r="B140" s="24"/>
+      <c r="C140" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" s="19"/>
-      <c r="B140" s="19"/>
-      <c r="C140" s="1" t="s">
+      <c r="D140" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E140" t="s">
+        <v>249</v>
+      </c>
+      <c r="F140" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="18"/>
+      <c r="B141" s="24"/>
+      <c r="D141" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D140" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" s="19"/>
-      <c r="B141" s="19"/>
-      <c r="D141" s="8" t="s">
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="18"/>
+      <c r="B142" s="24"/>
+      <c r="D142" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" s="19"/>
-      <c r="B142" s="19"/>
-      <c r="D142" s="8" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="18"/>
+      <c r="B143" s="24"/>
+      <c r="D143" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" s="19"/>
-      <c r="B143" s="19"/>
-      <c r="D143" s="8" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="18"/>
+      <c r="B144" s="24"/>
+      <c r="C144" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" s="19"/>
-      <c r="B144" s="19"/>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D144" s="8" t="s">
+      <c r="F144" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="18"/>
+      <c r="B145" s="24"/>
+      <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A145" s="19"/>
-      <c r="B145" s="19"/>
-      <c r="D145" s="8" t="s">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="18"/>
+      <c r="B146" s="24"/>
+      <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A146" s="19"/>
-      <c r="B146" s="19"/>
-      <c r="D146" s="8" t="s">
+      <c r="F146" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="18"/>
+      <c r="B147" s="24"/>
+      <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147" s="19"/>
-      <c r="B147" s="19"/>
-      <c r="D147" s="8" t="s">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="18"/>
+      <c r="B148" s="24"/>
+      <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A148" s="19"/>
-      <c r="B148" s="19"/>
-      <c r="D148" s="8" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="18"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="1" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A149" s="19"/>
-      <c r="B149" s="19"/>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D149" s="8" t="s">
+      <c r="F149" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="18"/>
+      <c r="B150" s="24"/>
+      <c r="D150" s="7" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A150" s="19"/>
-      <c r="B150" s="19"/>
-      <c r="D150" s="8" t="s">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="18"/>
+      <c r="B151" s="24"/>
+      <c r="D151" s="7" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A151" s="19"/>
-      <c r="B151" s="19"/>
-      <c r="D151" s="8" t="s">
+      <c r="F151" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="18"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="10" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A152" s="19"/>
-      <c r="B152" s="21"/>
-      <c r="C152" s="10"/>
-      <c r="D152" s="11" t="s">
+      <c r="F152" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="18"/>
+      <c r="B153" s="24" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A153" s="19"/>
-      <c r="B153" s="19" t="s">
+      <c r="C153" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D153" s="8" t="s">
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="18"/>
+      <c r="B154" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D154" s="7" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A154" s="19"/>
-      <c r="B154" s="19"/>
-      <c r="D154" s="8" t="s">
+      <c r="E154" t="s">
+        <v>250</v>
+      </c>
+      <c r="F154" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="18"/>
+      <c r="B155" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D155" s="7" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A155" s="19"/>
-      <c r="B155" s="19"/>
-      <c r="D155" s="8" t="s">
+      <c r="E155" t="s">
+        <v>251</v>
+      </c>
+      <c r="F155" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="18"/>
+      <c r="B156" s="24"/>
+      <c r="D156" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156" s="19"/>
-      <c r="B156" s="19"/>
-      <c r="D156" s="8" t="s">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="18"/>
+      <c r="B157" s="24"/>
+      <c r="D157" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157" s="19"/>
-      <c r="B157" s="19"/>
-      <c r="D157" s="8" t="s">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="18"/>
+      <c r="B158" s="24"/>
+      <c r="D158" s="7" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158" s="19"/>
-      <c r="B158" s="19"/>
-      <c r="D158" s="8" t="s">
+      <c r="F158" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="18"/>
+      <c r="B159" s="24"/>
+      <c r="D159" s="7" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" s="19"/>
-      <c r="B159" s="19"/>
-      <c r="D159" s="8" t="s">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="18"/>
+      <c r="B160" s="18"/>
+      <c r="D160" s="7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160" s="19"/>
-      <c r="B160" s="19"/>
-      <c r="D160" s="8" t="s">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="18"/>
+      <c r="B161" s="18"/>
+      <c r="C161" s="1" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161" s="19"/>
-      <c r="B161" s="19"/>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D161" s="8" t="s">
+      <c r="E161" t="s">
+        <v>252</v>
+      </c>
+      <c r="F161" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="18"/>
+      <c r="B162" s="18"/>
+      <c r="D162" s="7" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A162" s="19"/>
-      <c r="B162" s="19"/>
-      <c r="D162" s="8" t="s">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="18"/>
+      <c r="B163" s="18"/>
+      <c r="D163" s="7" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163" s="19"/>
-      <c r="B163" s="19"/>
-      <c r="D163" s="8" t="s">
+      <c r="F163" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="18"/>
+      <c r="B164" s="18"/>
+      <c r="D164" s="7" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A164" s="19"/>
-      <c r="B164" s="19"/>
-      <c r="D164" s="8" t="s">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="18"/>
+      <c r="B165" s="18"/>
+      <c r="D165" s="7" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A165" s="19"/>
-      <c r="B165" s="19"/>
-      <c r="D165" s="8" t="s">
+      <c r="E165" t="s">
+        <v>281</v>
+      </c>
+      <c r="F165" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="18"/>
+      <c r="B166" s="18"/>
+      <c r="D166" s="7" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A166" s="19"/>
-      <c r="B166" s="19"/>
-      <c r="D166" s="8" t="s">
+      <c r="E166" t="s">
+        <v>253</v>
+      </c>
+      <c r="F166" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="18"/>
+      <c r="B167" s="18"/>
+      <c r="C167" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A167" s="19"/>
-      <c r="B167" s="19"/>
-      <c r="C167" s="1" t="s">
+      <c r="D167" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D167" s="8" t="s">
+      <c r="F167" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="18"/>
+      <c r="B168" s="18"/>
+      <c r="D168" s="7" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A168" s="19"/>
-      <c r="B168" s="19"/>
-      <c r="D168" s="8" t="s">
+      <c r="F168" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="18"/>
+      <c r="B169" s="18"/>
+      <c r="D169" s="7" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A169" s="19"/>
-      <c r="B169" s="19"/>
-      <c r="D169" s="8" t="s">
+      <c r="F169" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="18"/>
+      <c r="B170" s="18"/>
+      <c r="D170" s="7" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A170" s="19"/>
-      <c r="B170" s="19"/>
-      <c r="D170" s="8" t="s">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="18"/>
+      <c r="B171" s="18"/>
+      <c r="D171" s="7" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A171" s="19"/>
-      <c r="B171" s="19"/>
-      <c r="D171" s="8" t="s">
+      <c r="F171" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="18"/>
+      <c r="B172" s="18"/>
+      <c r="D172" s="7" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A172" s="19"/>
-      <c r="B172" s="19"/>
-      <c r="D172" s="8" t="s">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="18"/>
+      <c r="B173" s="18"/>
+      <c r="D173" s="7" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A173" s="19"/>
-      <c r="B173" s="19"/>
-      <c r="D173" s="8" t="s">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="18"/>
+      <c r="B174" s="18"/>
+      <c r="D174" s="7" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A174" s="19"/>
-      <c r="B174" s="19"/>
-      <c r="D174" s="8" t="s">
+      <c r="F174" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="18"/>
+      <c r="B175" s="18"/>
+      <c r="D175" s="7" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A175" s="19"/>
-      <c r="B175" s="19"/>
-      <c r="D175" s="8" t="s">
+      <c r="F175" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="18"/>
+      <c r="B176" s="18"/>
+      <c r="C176" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A176" s="19"/>
-      <c r="B176" s="19"/>
-      <c r="C176" s="1" t="s">
+      <c r="D176" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D176" s="8" t="s">
+      <c r="F176" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="18"/>
+      <c r="B177" s="18"/>
+      <c r="D177" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A177" s="19"/>
-      <c r="B177" s="19"/>
-      <c r="D177" s="8" t="s">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" s="18"/>
+      <c r="B178" s="18"/>
+      <c r="D178" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A178" s="19"/>
-      <c r="B178" s="19"/>
-      <c r="D178" s="8" t="s">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" s="18"/>
+      <c r="B179" s="18"/>
+      <c r="D179" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A179" s="19"/>
-      <c r="B179" s="19"/>
-      <c r="D179" s="8" t="s">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" s="18"/>
+      <c r="B180" s="18"/>
+      <c r="D180" s="7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A180" s="19"/>
-      <c r="B180" s="19"/>
-      <c r="D180" s="8" t="s">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" s="18"/>
+      <c r="B181" s="18"/>
+      <c r="D181" s="7" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A181" s="19"/>
-      <c r="B181" s="19"/>
-      <c r="D181" s="8" t="s">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" s="19"/>
+      <c r="B182" s="19"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="10" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A182" s="21"/>
-      <c r="B182" s="21"/>
-      <c r="C182" s="10"/>
-      <c r="D182" s="11" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/Settlements of Albany.xlsx
+++ b/Settlements of Albany.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a38c727b2e27c7e/Documents/Creative Writing/Tabletop/Albany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5290763A-AF8B-41AA-9B36-0F08EBB5F7B1}"/>
+  <xr:revisionPtr revIDLastSave="304" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CF5F5AE-D138-4051-BC83-84D8245F08FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="411">
   <si>
     <t>Old Kingdom</t>
   </si>
@@ -42,10 +53,16 @@
     <t>City</t>
   </si>
   <si>
+    <t>Lord</t>
+  </si>
+  <si>
+    <t>Arms</t>
+  </si>
+  <si>
     <t>PICTONY</t>
   </si>
   <si>
-    <t>LAIRD CHIEF OF LOTHBURN*</t>
+    <t>LAIRD CHIEF OF LOTHBURN* *The Pictish Clans in practice do not recognise the supremacy of Ducal tites, and the Laird Chief is a ceremonial title from The Old Kingdom</t>
   </si>
   <si>
     <t>LOTHBURN</t>
@@ -54,7 +71,10 @@
     <t>DUN EIDYNN</t>
   </si>
   <si>
-    <t>*The Pictish Clans in practice do not recognise the supremacy of Ducal tites, and the Laird Chief is a ceremonial title from The Old Kingdom</t>
+    <t>Laird Murdoch MacNab</t>
+  </si>
+  <si>
+    <t>or a yale rampant gules, tressure gules</t>
   </si>
   <si>
     <t>Kilrymont</t>
@@ -66,6 +86,9 @@
     <t>Dun Pharlain</t>
   </si>
   <si>
+    <t>checky or and sable, a griffin passant gules</t>
+  </si>
+  <si>
     <t>Ecclesbrith</t>
   </si>
   <si>
@@ -75,18 +98,33 @@
     <t>Inbhirleith</t>
   </si>
   <si>
+    <t>vert, a pantheon rampant or</t>
+  </si>
+  <si>
     <t>Dun Barra</t>
   </si>
   <si>
+    <t>azure, a savage head vert</t>
+  </si>
+  <si>
     <t>Selsbrith</t>
   </si>
   <si>
+    <t>or, three stags lodged azure</t>
+  </si>
+  <si>
     <t>Lockardsby</t>
   </si>
   <si>
+    <t>azure, three trees vert</t>
+  </si>
+  <si>
     <t>AYR</t>
   </si>
   <si>
+    <t>azure, three roundels sable</t>
+  </si>
+  <si>
     <t>Cairnryan</t>
   </si>
   <si>
@@ -96,18 +134,30 @@
     <t>Tynron Doon</t>
   </si>
   <si>
+    <t>orly gules and or</t>
+  </si>
+  <si>
     <t>Dun Douglas</t>
   </si>
   <si>
+    <t>argent, three hearts gules</t>
+  </si>
+  <si>
     <t>Dun Drennan</t>
   </si>
   <si>
+    <t>azure, a gorge vert</t>
+  </si>
+  <si>
     <t>LANARK</t>
   </si>
   <si>
     <t>GARSCADDEN</t>
   </si>
   <si>
+    <t>shepherd check sable and vert</t>
+  </si>
+  <si>
     <t>Marnock</t>
   </si>
   <si>
@@ -120,9 +170,15 @@
     <t>Dun Bhlathain</t>
   </si>
   <si>
+    <t>shepherd check or and vert</t>
+  </si>
+  <si>
     <t>Pitloch Atholl</t>
   </si>
   <si>
+    <t>shepherd check gules and vert</t>
+  </si>
+  <si>
     <t>Chatnaich</t>
   </si>
   <si>
@@ -132,6 +188,9 @@
     <t>BREADHAIG</t>
   </si>
   <si>
+    <t>azure, a triskele vert</t>
+  </si>
+  <si>
     <t>Inbhirora</t>
   </si>
   <si>
@@ -141,15 +200,24 @@
     <t>Dun Cambel</t>
   </si>
   <si>
+    <t>orly vert and azure</t>
+  </si>
+  <si>
     <t>CAIRNWATH</t>
   </si>
   <si>
     <t>DUN DEAGH</t>
   </si>
   <si>
+    <t>azure, an elk trippant argent</t>
+  </si>
+  <si>
     <t>Sgain</t>
   </si>
   <si>
+    <t>glen check azure and or</t>
+  </si>
+  <si>
     <t>Ghlinn Sidh</t>
   </si>
   <si>
@@ -159,27 +227,48 @@
     <t>Dunn Kiliwhimin</t>
   </si>
   <si>
+    <t>glen check azure and vert</t>
+  </si>
+  <si>
     <t>INBHIRNESS</t>
   </si>
   <si>
+    <t>houndstooth gules and vert</t>
+  </si>
+  <si>
     <t>Narann</t>
   </si>
   <si>
+    <t>houndstooth gules and azure</t>
+  </si>
+  <si>
     <t>Thulnain</t>
   </si>
   <si>
+    <t>gules, three annulets interlaced vert</t>
+  </si>
+  <si>
     <t>DHEATHAIN</t>
   </si>
   <si>
     <t>INBHIRDHEATH</t>
   </si>
   <si>
+    <t>tartan gules and sable</t>
+  </si>
+  <si>
     <t>Dun Fraser</t>
   </si>
   <si>
+    <t>tartan azure and vert</t>
+  </si>
+  <si>
     <t>Duniness</t>
   </si>
   <si>
+    <t>tartan or and gules</t>
+  </si>
+  <si>
     <t>Bhrothaig</t>
   </si>
   <si>
@@ -192,6 +281,12 @@
     <t>ABERLUNE</t>
   </si>
   <si>
+    <t>or, a dog courant gules</t>
+  </si>
+  <si>
+    <t>King Henry of Aberlune</t>
+  </si>
+  <si>
     <t>Caerferes</t>
   </si>
   <si>
@@ -204,27 +299,42 @@
     <t>Harbwr Gwyn</t>
   </si>
   <si>
+    <t>vert, ford, three trefoils argent in fess</t>
+  </si>
+  <si>
     <t>Trefoffeiriad</t>
   </si>
   <si>
     <t>Manceinion</t>
   </si>
   <si>
+    <t>gules, two bends or, a dog-head-collared-couped gules</t>
+  </si>
+  <si>
     <t>TEYRNLLWG</t>
   </si>
   <si>
     <t>DEVERDOEU</t>
   </si>
   <si>
+    <t>azure, seven crosses couped in annulo or, a dragon head much smaller caboshed gules</t>
+  </si>
+  <si>
     <t>Penbedw</t>
   </si>
   <si>
+    <t>vert, two dragon heads couped gules respecting each other</t>
+  </si>
+  <si>
     <t>Gwrexham</t>
   </si>
   <si>
     <t>Pengwern</t>
   </si>
   <si>
+    <t>erminois, a dragon rampant sable</t>
+  </si>
+  <si>
     <t>Llanllieni</t>
   </si>
   <si>
@@ -252,12 +362,21 @@
     <t>CYNWY</t>
   </si>
   <si>
+    <t>sable, a dragon couchant argent</t>
+  </si>
+  <si>
     <t>Cor Gybi</t>
   </si>
   <si>
     <t>Caereustace</t>
   </si>
   <si>
+    <t>Pen Maelor</t>
+  </si>
+  <si>
+    <t>vert, ford, in sinister side a dragon rampant gules and in dexter side a sea dragon gules</t>
+  </si>
+  <si>
     <t>Aberteifi</t>
   </si>
   <si>
@@ -279,9 +398,24 @@
     <t>CAERTADD</t>
   </si>
   <si>
+    <t>Duke Gruffudd Sant-Ioan</t>
+  </si>
+  <si>
+    <t>vert, a dragon displayed gules</t>
+  </si>
+  <si>
+    <t>Gruffudd Sant-Ioan</t>
+  </si>
+  <si>
     <t>Pont Myrddin</t>
   </si>
   <si>
+    <t>azure, a dragon in annulo gules</t>
+  </si>
+  <si>
+    <t>vert, a dragon rampant gules</t>
+  </si>
+  <si>
     <t>Mortdunum</t>
   </si>
   <si>
@@ -303,12 +437,18 @@
     <t>ABONA</t>
   </si>
   <si>
+    <t>gules, ford, a bend argent, a dragon's head or</t>
+  </si>
+  <si>
     <t>Ty Cerrig</t>
   </si>
   <si>
     <t>Caerloyw</t>
   </si>
   <si>
+    <t>rosace vert and or, a gauntlet argent en soleil much smaller</t>
+  </si>
+  <si>
     <t>Treffynnon</t>
   </si>
   <si>
@@ -318,6 +458,9 @@
     <t>Dyrh</t>
   </si>
   <si>
+    <t>per fess embattled, azure and gules, a pitcher or</t>
+  </si>
+  <si>
     <t>Bryn-y-Moch</t>
   </si>
   <si>
@@ -327,21 +470,39 @@
     <t>Durnovara</t>
   </si>
   <si>
+    <t>quarterly gules and azure, a cross or</t>
+  </si>
+  <si>
     <t>Caer Morglawdd</t>
   </si>
   <si>
+    <t xml:space="preserve">sable, ford, three gauntlet argent in fess </t>
+  </si>
+  <si>
     <t>Croesi Arth</t>
   </si>
   <si>
+    <t>sable, a bear carrying a cross argent</t>
+  </si>
+  <si>
     <t>Hen Sarum</t>
   </si>
   <si>
+    <t>vert a stone circle argent</t>
+  </si>
+  <si>
     <t>WYTH</t>
   </si>
   <si>
     <t>NANT-Y-BRENIN</t>
   </si>
   <si>
+    <t>Earl Rhodri Gwinwr</t>
+  </si>
+  <si>
+    <t>per fess argent and azure, A chalice or,motto of "Er Cof Amdanof I"</t>
+  </si>
+  <si>
     <t>Gwinwr</t>
   </si>
   <si>
@@ -351,6 +512,12 @@
     <t>ABERISKA</t>
   </si>
   <si>
+    <t>Earl Llwelyn ap Owain o'r Gaer</t>
+  </si>
+  <si>
+    <t>party per barry wavy gules and azure, a castle or, supporters pegasus Segreant argent and dragon rampant gules</t>
+  </si>
+  <si>
     <t>Ynys Wydr</t>
   </si>
   <si>
@@ -372,9 +539,15 @@
     <t>Tairafon</t>
   </si>
   <si>
+    <t>sable three dragon heads or</t>
+  </si>
+  <si>
     <t>Pensanctaidd</t>
   </si>
   <si>
+    <t>argent a mitre or above a dragon's head or</t>
+  </si>
+  <si>
     <t>Abertamari</t>
   </si>
   <si>
@@ -384,9 +557,21 @@
     <t>PORTHENNOR</t>
   </si>
   <si>
+    <t>Earl Emrys Cadwallader</t>
+  </si>
+  <si>
+    <t>quarterly gules and vert, an inescutcheon sable, overall a dragon rampant or</t>
+  </si>
+  <si>
     <t>Skaw</t>
   </si>
   <si>
+    <t>Sir Howell Tresco</t>
+  </si>
+  <si>
+    <t>azure, in chief fess invected or, in chief three elder blossoms argent in fess</t>
+  </si>
+  <si>
     <t>NORSKANY</t>
   </si>
   <si>
@@ -396,9 +581,18 @@
     <t>DUNHELM</t>
   </si>
   <si>
+    <t>sable, a cross vert, four wolves rampant argent combatant</t>
+  </si>
+  <si>
+    <t>John of Jorvale*</t>
+  </si>
+  <si>
     <t>Wallsend</t>
   </si>
   <si>
+    <t>azure, a boar argent</t>
+  </si>
+  <si>
     <t>Morgate</t>
   </si>
   <si>
@@ -408,6 +602,9 @@
     <t>Aida</t>
   </si>
   <si>
+    <t>argent, ford, a cross or</t>
+  </si>
+  <si>
     <t>Byggwyk</t>
   </si>
   <si>
@@ -417,45 +614,78 @@
     <t>JORVALE</t>
   </si>
   <si>
+    <t>Earl Richard of Jorvale</t>
+  </si>
+  <si>
     <t>Horgrsgate</t>
   </si>
   <si>
+    <t>barry bowed vert and argent, a boars head caboshed or</t>
+  </si>
+  <si>
     <t>Rypon</t>
   </si>
   <si>
     <t>Loidis</t>
   </si>
   <si>
+    <t>mullety of 10 azure and or, a wolf rampant argent</t>
+  </si>
+  <si>
     <t>Breidford</t>
   </si>
   <si>
     <t>Raudmarsh</t>
   </si>
   <si>
+    <t>barry wavy gules and azure, a wolf rampant gules</t>
+  </si>
+  <si>
     <t>Hvitby</t>
   </si>
   <si>
+    <t>barry wavy azure and argent, in fess three croziers vert above a mitre or</t>
+  </si>
+  <si>
     <t>Skardaborough</t>
   </si>
   <si>
+    <t>sable, ford, a tower argent above a ship or</t>
+  </si>
+  <si>
     <t>Bjorrton</t>
   </si>
   <si>
+    <t>per fess azure and barry wavy azure and argent, in chief a beaver or</t>
+  </si>
+  <si>
     <t>Wyke</t>
   </si>
   <si>
+    <t>sable, a chevron ploye ermine, three wolf's heads argent</t>
+  </si>
+  <si>
     <t>LINDIS</t>
   </si>
   <si>
+    <t>per fess gules and argent, in first quarter a virgin argent and in second quarter a paschal lamb argent banner or and a mitre gules smaller</t>
+  </si>
+  <si>
     <t>Torksey</t>
   </si>
   <si>
     <t>Konigsby</t>
   </si>
   <si>
+    <t>barry indented one in the other vert and or</t>
+  </si>
+  <si>
     <t>Gegnesborough</t>
   </si>
   <si>
+    <t xml:space="preserve">quarterly 1st and 4th, papelonny vert and argent, 2nd and 3rd, paly sable and or a falcon striking argent; </t>
+  </si>
+  <si>
     <t>Gransthrop</t>
   </si>
   <si>
@@ -468,21 +698,36 @@
     <t>Skumasthorp</t>
   </si>
   <si>
+    <t>barry wavy vert and or, three wheat sheafs or</t>
+  </si>
+  <si>
     <t>Vodinnswyk</t>
   </si>
   <si>
+    <t xml:space="preserve">sable, ford, a raven or </t>
+  </si>
+  <si>
     <t>Skaggisness</t>
   </si>
   <si>
+    <t>per bend sinister azure and sable, three cranes argent legged or beaked gules</t>
+  </si>
+  <si>
     <t>Skirbeck</t>
   </si>
   <si>
     <t>DEORABY</t>
   </si>
   <si>
+    <t>fretty vert and argent, two ash trees eradicated or above a stag lodged reguardant or</t>
+  </si>
+  <si>
     <t>Notingborough</t>
   </si>
   <si>
+    <t>checky vert and argent, an ash trees eradicated or</t>
+  </si>
+  <si>
     <t>SAESONY</t>
   </si>
   <si>
@@ -492,12 +737,24 @@
     <t>WAERICK</t>
   </si>
   <si>
+    <t>Duke William FitzAlan</t>
+  </si>
+  <si>
+    <t>per bend mullety of 10 or and gules and maily azure and or, in dexter side a bear rampant argent</t>
+  </si>
+  <si>
+    <t>William FitzAlan</t>
+  </si>
+  <si>
     <t>Arbury</t>
   </si>
   <si>
     <t>Soarcester</t>
   </si>
   <si>
+    <t>argent, four cinquefoils gules arranged two one one</t>
+  </si>
+  <si>
     <t>Middleton</t>
   </si>
   <si>
@@ -507,6 +764,9 @@
     <t>Huntaton</t>
   </si>
   <si>
+    <t xml:space="preserve">checky vert and sable, a bow with arrow nocked or </t>
+  </si>
+  <si>
     <t>Thraepston</t>
   </si>
   <si>
@@ -516,6 +776,9 @@
     <t>Laminton</t>
   </si>
   <si>
+    <t>fretty sable and gules, a quarter ermine</t>
+  </si>
+  <si>
     <t>Silverton</t>
   </si>
   <si>
@@ -525,6 +788,12 @@
     <t>UXBRIDGE</t>
   </si>
   <si>
+    <t>Earl Robert Daubenay</t>
+  </si>
+  <si>
+    <t>per pale embattled argent and azure, an ox gules</t>
+  </si>
+  <si>
     <t>Gildenborough</t>
   </si>
   <si>
@@ -540,12 +809,18 @@
     <t>NORWYK</t>
   </si>
   <si>
+    <t>per pale ermine and gules, in second quarter a wolf sejant, in fourth quarter a ship argent</t>
+  </si>
+  <si>
     <t>Lunn</t>
   </si>
   <si>
     <t>Vodinnsmere</t>
   </si>
   <si>
+    <t>per fess vert and estencely azure and vert, three ravens sable</t>
+  </si>
+  <si>
     <t>Yarm</t>
   </si>
   <si>
@@ -558,15 +833,24 @@
     <t>GYPPESWYK</t>
   </si>
   <si>
+    <t>per chevron gules and lozengy azure and argent, in chief a sun or, a sunburst or</t>
+  </si>
+  <si>
     <t>Dunwyk</t>
   </si>
   <si>
     <t>Saesmond</t>
   </si>
   <si>
+    <t>per chausse fretty azure and argent and argent, a fish embowed or</t>
+  </si>
+  <si>
     <t>Aedmondsbury</t>
   </si>
   <si>
+    <t>per pale fretty argent and azure and argent, in sinister side a lion rampant azure</t>
+  </si>
+  <si>
     <t>DUCHY OF HAMETONSHIRE</t>
   </si>
   <si>
@@ -576,12 +860,30 @@
     <t>CELMFORD</t>
   </si>
   <si>
+    <t>Walter de Hameton</t>
+  </si>
+  <si>
     <t>Rivenhall</t>
   </si>
   <si>
+    <t>Earl Robert Hylton</t>
+  </si>
+  <si>
+    <t>per saltire checky azure argent, crusilly sable or, three moon decrescent argent</t>
+  </si>
+  <si>
+    <t>per chevron vairy argent and azure and papelonny gules and or, on a sun or a horse rampant sable</t>
+  </si>
+  <si>
     <t>Nivenhall</t>
   </si>
   <si>
+    <t>Earl William "Wakeful" Hylton</t>
+  </si>
+  <si>
+    <t>quarterly checky azure argent, crusilly sable or, three moon increscent argent</t>
+  </si>
+  <si>
     <t>Southminster</t>
   </si>
   <si>
@@ -591,6 +893,9 @@
     <t>Waecia</t>
   </si>
   <si>
+    <t>quarterly lozengy argent and azure and checky azure and argent, five roundels or in orle</t>
+  </si>
+  <si>
     <t>Boerthaldon</t>
   </si>
   <si>
@@ -603,39 +908,72 @@
     <t>NORTHOME</t>
   </si>
   <si>
+    <t>Duke Walter de Hameton</t>
+  </si>
+  <si>
+    <t>per fess arched gules and vert, enty in point argent, in fess a castle triple towered much smaller argent, between in base two horses respectant sable larger</t>
+  </si>
+  <si>
     <t>Marlbury</t>
   </si>
   <si>
     <t>Avesbury</t>
   </si>
   <si>
+    <t>sable, a dolmen argent</t>
+  </si>
+  <si>
     <t>Silford</t>
   </si>
   <si>
     <t>Winford</t>
   </si>
   <si>
+    <t>Bishop Richard</t>
+  </si>
+  <si>
+    <t>per fess argent and checky azure and argent, a mitre vert surrounded by two angels kneeling attired or respecting each other</t>
+  </si>
+  <si>
     <t>Southome</t>
   </si>
   <si>
+    <t>Earl Alisaunder de Hameton</t>
+  </si>
+  <si>
+    <t>per fess argent and gules, in chief two Dog Courant Collared gules and in base a boar passant argent. Supporters lymphad</t>
+  </si>
+  <si>
     <t>HAESTASHIRE</t>
   </si>
   <si>
     <t>GREATMINSTER</t>
   </si>
   <si>
+    <t>per pale chequy argent and azure and lozengy argent and azure, a fess azure charged with three bells or, in chief a crown or and in base a tower argent.</t>
+  </si>
+  <si>
     <t>Elmbridge</t>
   </si>
   <si>
+    <t>mullety of 10 azure and argent, a tree or leafed vert</t>
+  </si>
+  <si>
     <t>Tandridge</t>
   </si>
   <si>
+    <t>quarterly lozengy argent and azure and mullety of 10 sable and or</t>
+  </si>
+  <si>
     <t>Windle</t>
   </si>
   <si>
     <t>Redhill</t>
   </si>
   <si>
+    <t>per fess gules and papelonny azure and argent</t>
+  </si>
+  <si>
     <t>Crowly</t>
   </si>
   <si>
@@ -645,15 +983,24 @@
     <t>Harhenhall</t>
   </si>
   <si>
+    <t>quarterly checky argent and azure, and maily sable and or, crancelin or</t>
+  </si>
+  <si>
     <t>Haesta</t>
   </si>
   <si>
+    <t>lozengy argent and azure, a knight mounted sable armoured argent maned argent caparisoned or, unguled or</t>
+  </si>
+  <si>
     <t>CANTIA</t>
   </si>
   <si>
     <t>CANTIABURY</t>
   </si>
   <si>
+    <t>quarterly estencely azure and argent and roundelly argent and azure, three lions rampant or</t>
+  </si>
+  <si>
     <t>Dourmouth</t>
   </si>
   <si>
@@ -672,352 +1019,259 @@
     <t>Mootburne</t>
   </si>
   <si>
-    <t>Arms</t>
-  </si>
-  <si>
-    <t>Lord</t>
-  </si>
-  <si>
-    <t>vert a stone circle argent</t>
-  </si>
-  <si>
-    <t>Walter de Hameton</t>
-  </si>
-  <si>
-    <t>per chevron vairy argent and azure and papelonny gules and or, on a sun or a horse rampant sable</t>
-  </si>
-  <si>
-    <t>William FitzAlan</t>
-  </si>
-  <si>
-    <t>vert, a dragon displayed gules</t>
-  </si>
-  <si>
-    <t>Gruffudd Sant-Ioan</t>
-  </si>
-  <si>
-    <t>vert, a dragon rampant gules</t>
-  </si>
-  <si>
-    <t>quarterly checky azure argent, crusilly sable or, three moon increscent argent</t>
-  </si>
-  <si>
-    <t>per saltire checky azure argent, crusilly sable or, three moon decrescent argent</t>
-  </si>
-  <si>
-    <t>per pale embattled argent and azure, an ox gules</t>
-  </si>
-  <si>
-    <t>per fess argent and azure, A chalice or,motto of "Er Cof Amdanof I"</t>
-  </si>
-  <si>
-    <t>party per barry wavy gules and azure, a castle or, supporters pegasus Segreant argent and dragon rampant gules</t>
-  </si>
-  <si>
-    <t>per pale ermine and gules, in second quarter a wolf sejant, in fourth quarter a ship argent</t>
-  </si>
-  <si>
-    <t>per chevron gules and lozengy azure and argent, in chief a sun or, a sunburst or</t>
-  </si>
-  <si>
-    <t>lozengy argent and azure, a knight mounted sable armoured argent maned argent caparisoned or, unguled or</t>
-  </si>
-  <si>
-    <t>quarterly estencely azure and argent and roundelly argent and azure, three lions rampant or</t>
-  </si>
-  <si>
-    <t>per pale fretty argent and azure and argent, in sinister side a lion rampant azure</t>
-  </si>
-  <si>
-    <t>per chausse fretty azure and argent and argent, a fish embowed or</t>
-  </si>
-  <si>
-    <t>rosace vert and or, a gauntlet argent en soleil much smaller</t>
-  </si>
-  <si>
-    <t>purpure, a rosary or above a lion dormant argent</t>
-  </si>
-  <si>
-    <t>erminois, a dragon rampant sable</t>
-  </si>
-  <si>
-    <t>azure, seven crosses couped in annulo or, a dragon head much smaller caboshed gules</t>
-  </si>
-  <si>
-    <t>vert, two dragon heads couped gules respecting each other</t>
-  </si>
-  <si>
-    <t>gules, two bends or, a dog-head-collared-couped gules</t>
-  </si>
-  <si>
-    <t>azure, a dragon in annulo gules</t>
-  </si>
-  <si>
-    <t>Pen Maelor</t>
-  </si>
-  <si>
-    <t>vert, ford, in sinister side a dragon rampant gules and in dexter side a sea dragon gules</t>
-  </si>
-  <si>
-    <t>sable, a dragon couchant argent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">checky vert and sable, a bow with arrow nocked or </t>
-  </si>
-  <si>
-    <t>fretty sable and gules, a quarter ermine</t>
-  </si>
-  <si>
-    <t>per fess vert and estencely azure and vert, three ravens sable</t>
-  </si>
-  <si>
-    <t>argent, four cinquefoils gules arranged two one one</t>
-  </si>
-  <si>
-    <t>Duke William FitzAlan</t>
-  </si>
-  <si>
-    <t>Earl Robert Daubenay</t>
-  </si>
-  <si>
-    <t>Earl Robert Hylton</t>
-  </si>
-  <si>
-    <t>Earl William "Wakeful" Hylton</t>
-  </si>
-  <si>
-    <t>Duke Walter de Hameton</t>
-  </si>
-  <si>
-    <t>Earl Alisaunder de Hameton</t>
-  </si>
-  <si>
-    <t>Earl Owain ap Ieuan</t>
-  </si>
-  <si>
-    <t>Duke Gruffudd Sant-Ioan</t>
-  </si>
-  <si>
-    <t>Earl Rhodri Gwinwr</t>
-  </si>
-  <si>
-    <t>Earl Llwelyn ap Owain o'r Gaer</t>
-  </si>
-  <si>
-    <t>sable, a cross vert, four wolves rampant argent combatant</t>
-  </si>
-  <si>
-    <t>mullety of 10 azure and or, a wolf rampant argent</t>
-  </si>
-  <si>
-    <t>sable, a chevron ploye ermine, three wolf's heads argent</t>
-  </si>
-  <si>
-    <t>per fess azure and barry wavy azure and argent, in chief a beaver or</t>
-  </si>
-  <si>
-    <t>barry wavy azure and argent, in fess three croziers vert above a mitre or</t>
-  </si>
-  <si>
-    <t>barry bowed vert and argent, a boars head caboshed or</t>
-  </si>
-  <si>
-    <t>barry wavy gules and azure, a wolf rampant gules</t>
-  </si>
-  <si>
-    <t>sable, ford, a tower argent above a ship or</t>
-  </si>
-  <si>
-    <t>per fess gules and argent, in first quarter a virgin argent and in second quarter a paschal lamb argent banner or and a mitre gules smaller</t>
-  </si>
-  <si>
-    <t>per fess argent and checky azure and argent, a mitre vert surrounded by two angels kneeling attired or respecting each other</t>
-  </si>
-  <si>
-    <t>per bend mullety of 10 or and gules and maily azure and or, in dexter side a bear rampant argent</t>
-  </si>
-  <si>
-    <t>per fess arched gules and vert, enty in point argent, in fess a castle triple towered much smaller argent, between in base two horses respectant sable larger</t>
-  </si>
-  <si>
-    <t>per fess argent and gules, in chief two Dog Courant Collared gules and in base a boar passant argent. Supporters lymphad</t>
-  </si>
-  <si>
-    <t>per pale chequy argent and azure and lozengy argent and azure, a fess azure charged with three bells or, in chief a crown or and in base a tower argent.</t>
-  </si>
-  <si>
-    <t>Laird Murdoch MacNab</t>
-  </si>
-  <si>
-    <t>azure, a boar argent</t>
-  </si>
-  <si>
-    <t>John of Jorvale*</t>
-  </si>
-  <si>
-    <t>King Henry of Aberlune</t>
-  </si>
-  <si>
-    <t>or, a dog courant gules</t>
-  </si>
-  <si>
-    <t>Earl Richard of Jorvale</t>
-  </si>
-  <si>
-    <t>sable, a dolmen argent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sable, ford, a raven or </t>
-  </si>
-  <si>
-    <t>barry wavy vert and or, three wheat sheafs or</t>
-  </si>
-  <si>
-    <t>Bishop Richard</t>
-  </si>
-  <si>
-    <t>per bend sinister azure and sable, three cranes argent legged or beaked gules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quarterly 1st and 4th, papelonny vert and argent, 2nd and 3rd, paly sable and or a falcon striking argent; </t>
-  </si>
-  <si>
-    <t>barry indented one in the other vert and or</t>
-  </si>
-  <si>
-    <t>argent, ford, a cross or</t>
-  </si>
-  <si>
-    <t>houndstooth gules and vert</t>
-  </si>
-  <si>
-    <t>houndstooth gules and azure</t>
-  </si>
-  <si>
-    <t>gules, three annulets interlaced vert</t>
-  </si>
-  <si>
-    <t>azure, a triskele vert</t>
-  </si>
-  <si>
-    <t>orly vert and azure</t>
-  </si>
-  <si>
-    <t>azure, three roundels sable</t>
-  </si>
-  <si>
-    <t>tartan gules and sable</t>
-  </si>
-  <si>
-    <t>tartan azure and vert</t>
-  </si>
-  <si>
-    <t>tartan or and gules</t>
-  </si>
-  <si>
-    <t>azure, a savage head vert</t>
-  </si>
-  <si>
-    <t>glen check azure and vert</t>
-  </si>
-  <si>
-    <t>glen check azure and or</t>
-  </si>
-  <si>
-    <t>shepherd check sable and vert</t>
-  </si>
-  <si>
-    <t>shepherd check or and vert</t>
-  </si>
-  <si>
-    <t>shepherd check gules and vert</t>
-  </si>
-  <si>
-    <t>azure, three trees vert</t>
-  </si>
-  <si>
-    <t>argent, three hearts gules</t>
-  </si>
-  <si>
-    <t>azure, an elk trippant argent</t>
-  </si>
-  <si>
-    <t>or, three stags lodged azure</t>
-  </si>
-  <si>
-    <t>or a yale rampant gules, tressure gules</t>
-  </si>
-  <si>
-    <t>checky or and sable, a griffin passant gules</t>
-  </si>
-  <si>
-    <t>orly gules and or</t>
-  </si>
-  <si>
-    <t>vert, a pantheon rampant or</t>
-  </si>
-  <si>
-    <t>vert, ford, three trefoils argent in fess</t>
-  </si>
-  <si>
-    <t>gules, ford, a bend argent, a dragon's head or</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sable, ford, three gauntlet argent in fess </t>
-  </si>
-  <si>
-    <t>sable, a bear carrying a cross argent</t>
-  </si>
-  <si>
-    <t>quarterly gules and azure, a cross or</t>
-  </si>
-  <si>
-    <t>per fess embattled, azure and gules, a pitcher or</t>
-  </si>
-  <si>
-    <t>sable three dragon heads or</t>
-  </si>
-  <si>
-    <t>argent a mitre or above a dragon's head or</t>
-  </si>
-  <si>
-    <t>azure, a gorge vert</t>
-  </si>
-  <si>
-    <t>quarterly gules and vert, an inescutcheon sable, overall a dragon rampant or</t>
-  </si>
-  <si>
-    <t>Earl Emrys Cadwallader</t>
-  </si>
-  <si>
-    <t>Sir Howell Tresco</t>
-  </si>
-  <si>
-    <t>Earl Sjoskip</t>
-  </si>
-  <si>
-    <t>fretty vert and argent, two ash trees eradicated or above a stag lodged reguardant or</t>
-  </si>
-  <si>
-    <t>checky vert and argent, an ash trees eradicated or</t>
-  </si>
-  <si>
-    <t>quarterly checky argent and azure, and maily sable and or, crancelin or</t>
-  </si>
-  <si>
-    <t>quarterly lozengy argent and azure and mullety of 10 sable and or</t>
-  </si>
-  <si>
-    <t>azure, in chief fess invected or, in chief three elder blossoms argent in fess</t>
-  </si>
-  <si>
-    <t>mullety of 10 azure and argent, a tree or leafed vert</t>
-  </si>
-  <si>
-    <t>per fess gules and papelonny azure and argent</t>
-  </si>
-  <si>
-    <t>quarterly lozengy argent and azure and checky azure and argent, five roundels or in orle</t>
+    <t>Lord Mayor Nicholas Downes</t>
+  </si>
+  <si>
+    <t>Earl Harold Thirkell</t>
+  </si>
+  <si>
+    <t>Baron Sjoskip</t>
+  </si>
+  <si>
+    <t>Abbott Cuthbert</t>
+  </si>
+  <si>
+    <t>Earl Gareth Beausire</t>
+  </si>
+  <si>
+    <t>Earl Tomos ap Arwyn</t>
+  </si>
+  <si>
+    <t>ermine, two wolves reguardant sable combatant</t>
+  </si>
+  <si>
+    <t>per fess wavy vert and azure, a sword argent above three trees vert</t>
+  </si>
+  <si>
+    <t>Earl Thomas Falstaff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earl Dafydd Llewelyn </t>
+  </si>
+  <si>
+    <t>gules, a rosary or above a lion dormant argent</t>
+  </si>
+  <si>
+    <t>Earl Edmund Ansell</t>
+  </si>
+  <si>
+    <t>Earl Marc ap Rhodri</t>
+  </si>
+  <si>
+    <t>Earl Owain ap Ieuan Gradawc</t>
+  </si>
+  <si>
+    <t>Earl Ieuan Gulliver</t>
+  </si>
+  <si>
+    <t>Earl Cadeyrn Cynwrig</t>
+  </si>
+  <si>
+    <t>Earl Cyndeyrn Wyllt</t>
+  </si>
+  <si>
+    <t>Earl Gerard Lovell</t>
+  </si>
+  <si>
+    <t>per chief throughout azure and argent, a sea-lion gules above seven oak trees vert</t>
+  </si>
+  <si>
+    <t>Earl Eric Sandgate</t>
+  </si>
+  <si>
+    <t>Baron Robert Tyrrell</t>
+  </si>
+  <si>
+    <t>Mayor Hardwin Gunn</t>
+  </si>
+  <si>
+    <t>Earl Osmond Sanderson</t>
+  </si>
+  <si>
+    <t>Mayor Ronald Beck</t>
+  </si>
+  <si>
+    <t>Earl Robert Lund</t>
+  </si>
+  <si>
+    <t>Earl Ralph Ormsby</t>
+  </si>
+  <si>
+    <t>Baron Thomas Hammond</t>
+  </si>
+  <si>
+    <t>Abbott Hildred</t>
+  </si>
+  <si>
+    <t>Baron Thurston Gill</t>
+  </si>
+  <si>
+    <t>Earl Caradog Conway</t>
+  </si>
+  <si>
+    <t>Baron Rhun ap Madoc</t>
+  </si>
+  <si>
+    <t>Mayor Arwyn ap Trefor</t>
+  </si>
+  <si>
+    <t>Baron William Glyn</t>
+  </si>
+  <si>
+    <t>Earl Charles of Aberlune</t>
+  </si>
+  <si>
+    <t>Baron Wolfstan Thwaite</t>
+  </si>
+  <si>
+    <t>Bishop Thomas</t>
+  </si>
+  <si>
+    <t>Mayor Ranulf Rawlinsson</t>
+  </si>
+  <si>
+    <t>Laird James Buchane</t>
+  </si>
+  <si>
+    <t>Laird Neil MacMartane</t>
+  </si>
+  <si>
+    <t>Chief Giles Patrick</t>
+  </si>
+  <si>
+    <t>Chief Giles Atholl</t>
+  </si>
+  <si>
+    <t>Chief Robert Douglad</t>
+  </si>
+  <si>
+    <t>Chief Angus Drennan</t>
+  </si>
+  <si>
+    <t>Chief Fergus Bhlathain</t>
+  </si>
+  <si>
+    <t>Laird Robert MacNakill</t>
+  </si>
+  <si>
+    <t>Laird Alan Erskyn</t>
+  </si>
+  <si>
+    <t>Laird Davy Wardoon</t>
+  </si>
+  <si>
+    <t>Chief Sym Fraser</t>
+  </si>
+  <si>
+    <t>Chief Amer Ross</t>
+  </si>
+  <si>
+    <t>Chief Thomas MacIne</t>
+  </si>
+  <si>
+    <t>Chief Andrew Lumbard</t>
+  </si>
+  <si>
+    <t>Chief Ralf Pharlain</t>
+  </si>
+  <si>
+    <t>Chief Morris MacPharlain</t>
+  </si>
+  <si>
+    <t>Chief Angus Barra</t>
+  </si>
+  <si>
+    <t>Chief John MacFulchiane</t>
+  </si>
+  <si>
+    <t>Chief William Ogill</t>
+  </si>
+  <si>
+    <t>Chief Gylmyne Kiliwhimin</t>
+  </si>
+  <si>
+    <t>Chief Gawter Campbell</t>
+  </si>
+  <si>
+    <t>Laird James Forster</t>
+  </si>
+  <si>
+    <t>Earl Hywel Bevan</t>
+  </si>
+  <si>
+    <t>Sir Hywel Vaughan</t>
+  </si>
+  <si>
+    <t>Sir Owain Wynne</t>
+  </si>
+  <si>
+    <t>Bishop Dafydd</t>
+  </si>
+  <si>
+    <t>Sir Arthur ap Llwyd</t>
+  </si>
+  <si>
+    <t>Mayor Randel Piers</t>
+  </si>
+  <si>
+    <t>Sir Henry Umber</t>
+  </si>
+  <si>
+    <t>Sir Wymond Raven</t>
+  </si>
+  <si>
+    <t>Sir Gunter Foss</t>
+  </si>
+  <si>
+    <t>Sir Giles Faramond</t>
+  </si>
+  <si>
+    <t>Earl Everard Nivett</t>
+  </si>
+  <si>
+    <t>Sir Edward Godwin</t>
+  </si>
+  <si>
+    <t>Sir Lionel Siward</t>
+  </si>
+  <si>
+    <t>Earl Henry Harding</t>
+  </si>
+  <si>
+    <t>Sir Dafydd ap Terwyn</t>
+  </si>
+  <si>
+    <t>Sir Teyrnon Loyw</t>
+  </si>
+  <si>
+    <t>azure, chevron engrailed or, two doves argent legged or armed gules beaked gules above an oak tree vert</t>
+  </si>
+  <si>
+    <t>Sir Bryn ap Rhys</t>
+  </si>
+  <si>
+    <t>Earl Simon Stannard</t>
+  </si>
+  <si>
+    <t>Sir Edwin Norton</t>
+  </si>
+  <si>
+    <t>Archbishop Peter</t>
+  </si>
+  <si>
+    <t>Sir Bernard Dacre</t>
+  </si>
+  <si>
+    <t>Sir Frederick de Jerrais</t>
+  </si>
+  <si>
+    <t>Sir Charles Bonet</t>
+  </si>
+  <si>
+    <t>Baron Margon Flynn</t>
+  </si>
+  <si>
+    <t>gules, bend dovetailed azure, a dragon head erased or</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1208,7 +1462,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1622,384 +1875,448 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>214</v>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
-      <c r="B3" s="23" t="s">
-        <v>272</v>
+      <c r="B3" s="22" t="s">
+        <v>10</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="D4" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="D5" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>377</v>
       </c>
       <c r="F5" t="s">
-        <v>306</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
-      <c r="B6" s="20" t="s">
-        <v>8</v>
-      </c>
+      <c r="B6" s="20"/>
       <c r="D6" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="D7" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="D8" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>378</v>
       </c>
       <c r="F8" t="s">
-        <v>308</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>379</v>
       </c>
       <c r="F9" t="s">
-        <v>295</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="D10" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>380</v>
       </c>
       <c r="F10" t="s">
-        <v>304</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="D11" s="7" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>381</v>
       </c>
       <c r="F11" t="s">
-        <v>301</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>363</v>
       </c>
       <c r="F12" t="s">
-        <v>291</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="D13" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="D14" s="7" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="D15" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>307</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="D16" s="7" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>367</v>
       </c>
       <c r="F16" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="D17" s="7" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>368</v>
       </c>
       <c r="F17" t="s">
-        <v>317</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>370</v>
       </c>
       <c r="F18" t="s">
-        <v>298</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="D19" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="D20" s="7" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="D21" s="7" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="D22" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>369</v>
       </c>
       <c r="F22" t="s">
-        <v>299</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="D23" s="7" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>366</v>
       </c>
       <c r="F23" t="s">
-        <v>300</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="D24" s="7" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>33</v>
+        <v>48</v>
+      </c>
+      <c r="E25" t="s">
+        <v>371</v>
       </c>
       <c r="F25" t="s">
-        <v>289</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="D26" s="7" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="D27" s="7" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="D28" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>383</v>
       </c>
       <c r="F28" t="s">
-        <v>290</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="1" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
+      </c>
+      <c r="E29" t="s">
+        <v>364</v>
       </c>
       <c r="F29" t="s">
-        <v>303</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="D30" s="7" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>297</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="D31" s="7" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="D32" s="7" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="D33" s="7" t="s">
-        <v>42</v>
+        <v>61</v>
+      </c>
+      <c r="E33" t="s">
+        <v>382</v>
       </c>
       <c r="F33" t="s">
-        <v>296</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>43</v>
+        <v>63</v>
+      </c>
+      <c r="E34" t="s">
+        <v>384</v>
       </c>
       <c r="F34" t="s">
-        <v>286</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="D35" s="7" t="s">
-        <v>44</v>
+        <v>65</v>
+      </c>
+      <c r="E35" t="s">
+        <v>374</v>
       </c>
       <c r="F35" t="s">
-        <v>287</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="D36" s="7" t="s">
-        <v>45</v>
+        <v>67</v>
+      </c>
+      <c r="E36" t="s">
+        <v>375</v>
       </c>
       <c r="F36" t="s">
-        <v>288</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>47</v>
+        <v>70</v>
+      </c>
+      <c r="E37" t="s">
+        <v>372</v>
       </c>
       <c r="F37" t="s">
-        <v>292</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="D38" s="7" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="E38" t="s">
+        <v>373</v>
       </c>
       <c r="F38" t="s">
-        <v>293</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="D39" s="7" t="s">
-        <v>49</v>
+        <v>74</v>
+      </c>
+      <c r="E39" t="s">
+        <v>376</v>
       </c>
       <c r="F39" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2007,222 +2324,255 @@
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
       <c r="D40" s="10" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>53</v>
+        <v>79</v>
+      </c>
+      <c r="E41" t="s">
+        <v>359</v>
       </c>
       <c r="F41" t="s">
-        <v>276</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
       <c r="B42" s="12" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>
       <c r="B43" s="12" t="s">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="D44" s="7" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="D45" s="7" t="s">
-        <v>57</v>
+        <v>85</v>
+      </c>
+      <c r="E45" t="s">
+        <v>357</v>
       </c>
       <c r="F45" t="s">
-        <v>309</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="D46" s="7" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="D47" s="7" t="s">
-        <v>59</v>
+        <v>88</v>
+      </c>
+      <c r="E47" t="s">
+        <v>358</v>
       </c>
       <c r="F47" t="s">
-        <v>239</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="1" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>61</v>
+        <v>91</v>
+      </c>
+      <c r="E48" t="s">
+        <v>385</v>
       </c>
       <c r="F48" t="s">
-        <v>237</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="D49" s="7" t="s">
-        <v>62</v>
+        <v>93</v>
+      </c>
+      <c r="E49" t="s">
+        <v>386</v>
       </c>
       <c r="F49" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="D50" s="7" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="D51" s="7" t="s">
-        <v>64</v>
+        <v>96</v>
+      </c>
+      <c r="E51" t="s">
+        <v>331</v>
       </c>
       <c r="F51" t="s">
-        <v>236</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="D52" s="7" t="s">
-        <v>65</v>
+        <v>98</v>
+      </c>
+      <c r="E52" t="s">
+        <v>335</v>
       </c>
       <c r="F52" t="s">
-        <v>235</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="D53" s="7" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="D54" s="7" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="D55" s="7" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="D56" s="7" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="D57" s="7" t="s">
-        <v>70</v>
+        <v>103</v>
+      </c>
+      <c r="E57" t="s">
+        <v>330</v>
+      </c>
+      <c r="F57" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="D58" s="7" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>73</v>
+        <v>106</v>
+      </c>
+      <c r="E59" t="s">
+        <v>355</v>
       </c>
       <c r="F59" t="s">
-        <v>243</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="D60" s="7" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="D61" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="D62" s="7" t="s">
-        <v>241</v>
+        <v>110</v>
+      </c>
+      <c r="E62" t="s">
+        <v>356</v>
       </c>
       <c r="F62" t="s">
-        <v>242</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="D63" s="7" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="1" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -2230,309 +2580,348 @@
       <c r="B65" s="14"/>
       <c r="C65" s="9"/>
       <c r="D65" s="10" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="12"/>
       <c r="B66" s="12" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="E66" t="s">
-        <v>255</v>
+        <v>119</v>
       </c>
       <c r="F66" t="s">
-        <v>220</v>
+        <v>120</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="12"/>
       <c r="B67" s="12" t="s">
-        <v>221</v>
+        <v>121</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>83</v>
+        <v>122</v>
+      </c>
+      <c r="E67" t="s">
+        <v>342</v>
       </c>
       <c r="F67" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="12"/>
       <c r="B68" s="12" t="s">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="D69" s="7" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="D70" s="7" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="D71" s="7" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="D72" s="7" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="1" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>90</v>
+        <v>131</v>
+      </c>
+      <c r="E73" t="s">
+        <v>338</v>
       </c>
       <c r="F73" t="s">
-        <v>310</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="D74" s="7" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="D75" s="7" t="s">
-        <v>92</v>
+        <v>134</v>
+      </c>
+      <c r="E75" t="s">
+        <v>400</v>
       </c>
       <c r="F75" t="s">
-        <v>234</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="D76" s="7" t="s">
-        <v>93</v>
+        <v>136</v>
+      </c>
+      <c r="E76" t="s">
+        <v>399</v>
+      </c>
+      <c r="F76" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="D77" s="7" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="D78" s="7" t="s">
-        <v>95</v>
+        <v>138</v>
+      </c>
+      <c r="E78" t="s">
+        <v>341</v>
       </c>
       <c r="F78" t="s">
-        <v>314</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="D79" s="7" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="D80" s="7" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="D81" s="7" t="s">
-        <v>98</v>
+        <v>142</v>
+      </c>
+      <c r="E81" t="s">
+        <v>402</v>
       </c>
       <c r="F81" t="s">
-        <v>313</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="D82" s="7" t="s">
-        <v>99</v>
+        <v>144</v>
+      </c>
+      <c r="E82" t="s">
+        <v>340</v>
       </c>
       <c r="F82" t="s">
-        <v>311</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="D83" s="7" t="s">
-        <v>100</v>
+        <v>146</v>
+      </c>
+      <c r="E83" t="s">
+        <v>389</v>
       </c>
       <c r="F83" t="s">
-        <v>312</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="D84" s="7" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="E84" t="s">
-        <v>254</v>
+        <v>339</v>
       </c>
       <c r="F84" t="s">
-        <v>216</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="1" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="E85" t="s">
-        <v>256</v>
+        <v>152</v>
       </c>
       <c r="F85" t="s">
-        <v>226</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="D86" s="7" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="1" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="E87" t="s">
-        <v>257</v>
+        <v>157</v>
       </c>
       <c r="F87" t="s">
-        <v>227</v>
+        <v>158</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="D88" s="7" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="D89" s="7" t="s">
-        <v>108</v>
+        <v>160</v>
+      </c>
+      <c r="E89" t="s">
+        <v>409</v>
+      </c>
+      <c r="F89" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="D90" s="7" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="D91" s="7" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="D92" s="7" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="D93" s="7" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="D94" s="7" t="s">
-        <v>113</v>
+        <v>165</v>
+      </c>
+      <c r="E94" t="s">
+        <v>387</v>
       </c>
       <c r="F94" t="s">
-        <v>315</v>
+        <v>166</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="D95" s="7" t="s">
-        <v>114</v>
+        <v>167</v>
+      </c>
+      <c r="E95" t="s">
+        <v>388</v>
       </c>
       <c r="F95" t="s">
-        <v>316</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="D96" s="7" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="1" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="E97" t="s">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="F97" t="s">
-        <v>318</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -2540,293 +2929,341 @@
       <c r="B98" s="14"/>
       <c r="C98" s="9"/>
       <c r="D98" s="10" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="E98" t="s">
-        <v>320</v>
+        <v>175</v>
       </c>
       <c r="F98" t="s">
-        <v>326</v>
+        <v>176</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="15" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>121</v>
+        <v>179</v>
+      </c>
+      <c r="E99" t="s">
+        <v>327</v>
       </c>
       <c r="F99" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="16"/>
       <c r="B100" s="16" t="s">
-        <v>274</v>
+        <v>181</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="16"/>
       <c r="B101" s="16" t="s">
-        <v>273</v>
+        <v>183</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>123</v>
+        <v>184</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="16"/>
       <c r="B102" s="16"/>
       <c r="D102" s="7" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="16"/>
       <c r="B103" s="16"/>
       <c r="D103" s="7" t="s">
-        <v>125</v>
+        <v>186</v>
+      </c>
+      <c r="E103" t="s">
+        <v>329</v>
       </c>
       <c r="F103" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="16"/>
       <c r="B104" s="16"/>
       <c r="D104" s="7" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="E104" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="16"/>
       <c r="B105" s="16"/>
       <c r="D105" s="7" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
       <c r="C106" s="1" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="E106" t="s">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="F106" t="s">
-        <v>273</v>
+        <v>183</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
       <c r="D107" s="7" t="s">
-        <v>129</v>
+        <v>192</v>
+      </c>
+      <c r="E107" t="s">
+        <v>351</v>
       </c>
       <c r="F107" t="s">
-        <v>263</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
       <c r="D108" s="7" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
       <c r="D109" s="7" t="s">
-        <v>131</v>
+        <v>195</v>
+      </c>
+      <c r="E109" t="s">
+        <v>352</v>
       </c>
       <c r="F109" t="s">
-        <v>259</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
       <c r="D110" s="7" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
       <c r="D111" s="7" t="s">
-        <v>133</v>
+        <v>198</v>
+      </c>
+      <c r="E111" t="s">
+        <v>354</v>
       </c>
       <c r="F111" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
       <c r="D112" s="7" t="s">
-        <v>134</v>
+        <v>200</v>
+      </c>
+      <c r="E112" t="s">
+        <v>353</v>
       </c>
       <c r="F112" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="16"/>
       <c r="B113" s="16"/>
       <c r="D113" s="7" t="s">
-        <v>135</v>
+        <v>202</v>
+      </c>
+      <c r="E113" t="s">
+        <v>345</v>
       </c>
       <c r="F113" t="s">
-        <v>265</v>
+        <v>203</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="16"/>
       <c r="B114" s="16"/>
       <c r="D114" s="7" t="s">
-        <v>136</v>
+        <v>204</v>
+      </c>
+      <c r="E114" t="s">
+        <v>393</v>
       </c>
       <c r="F114" t="s">
-        <v>261</v>
+        <v>205</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="16"/>
       <c r="B115" s="16"/>
       <c r="D115" s="7" t="s">
-        <v>137</v>
+        <v>206</v>
+      </c>
+      <c r="E115" t="s">
+        <v>347</v>
       </c>
       <c r="F115" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="16"/>
       <c r="B116" s="16"/>
       <c r="C116" s="1" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>138</v>
+        <v>208</v>
+      </c>
+      <c r="E116" t="s">
+        <v>361</v>
       </c>
       <c r="F116" t="s">
-        <v>266</v>
+        <v>209</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="16"/>
       <c r="B117" s="16"/>
       <c r="D117" s="7" t="s">
-        <v>139</v>
+        <v>210</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="16"/>
       <c r="B118" s="16"/>
       <c r="D118" s="7" t="s">
-        <v>140</v>
+        <v>211</v>
+      </c>
+      <c r="E118" t="s">
+        <v>390</v>
       </c>
       <c r="F118" t="s">
-        <v>284</v>
+        <v>212</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="16"/>
       <c r="B119" s="16"/>
       <c r="D119" s="7" t="s">
-        <v>141</v>
+        <v>213</v>
+      </c>
+      <c r="E119" t="s">
+        <v>360</v>
       </c>
       <c r="F119" t="s">
-        <v>283</v>
+        <v>214</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="16"/>
       <c r="B120" s="16"/>
       <c r="D120" s="7" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="16"/>
       <c r="B121" s="16"/>
       <c r="D121" s="7" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="16"/>
       <c r="B122" s="16"/>
       <c r="D122" s="7" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="16"/>
       <c r="B123" s="16"/>
       <c r="D123" s="7" t="s">
-        <v>145</v>
+        <v>218</v>
+      </c>
+      <c r="E123" t="s">
+        <v>391</v>
       </c>
       <c r="F123" t="s">
-        <v>280</v>
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="16"/>
       <c r="B124" s="16"/>
       <c r="D124" s="7" t="s">
-        <v>146</v>
+        <v>220</v>
+      </c>
+      <c r="E124" t="s">
+        <v>362</v>
       </c>
       <c r="F124" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="16"/>
       <c r="B125" s="16"/>
       <c r="D125" s="7" t="s">
-        <v>147</v>
+        <v>222</v>
+      </c>
+      <c r="E125" t="s">
+        <v>392</v>
       </c>
       <c r="F125" t="s">
-        <v>282</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="16"/>
       <c r="B126" s="16"/>
       <c r="D126" s="7" t="s">
-        <v>148</v>
+        <v>224</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="16"/>
       <c r="B127" s="16"/>
       <c r="C127" s="1" t="s">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>149</v>
+        <v>225</v>
+      </c>
+      <c r="E127" t="s">
+        <v>348</v>
       </c>
       <c r="F127" t="s">
-        <v>322</v>
+        <v>226</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
@@ -2834,96 +3271,108 @@
       <c r="B128" s="17"/>
       <c r="C128" s="9"/>
       <c r="D128" s="10" t="s">
-        <v>150</v>
+        <v>227</v>
+      </c>
+      <c r="E128" t="s">
+        <v>349</v>
       </c>
       <c r="F128" t="s">
-        <v>323</v>
+        <v>228</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B129" s="25" t="s">
-        <v>152</v>
+        <v>229</v>
+      </c>
+      <c r="B129" s="24" t="s">
+        <v>230</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="E129" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F129" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="18"/>
-      <c r="B130" s="24" t="s">
-        <v>219</v>
+      <c r="B130" s="23" t="s">
+        <v>234</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>154</v>
+        <v>235</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="18"/>
-      <c r="B131" s="24" t="s">
-        <v>268</v>
+      <c r="B131" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>155</v>
+        <v>236</v>
+      </c>
+      <c r="E131" t="s">
+        <v>403</v>
       </c>
       <c r="F131" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="18"/>
-      <c r="B132" s="24"/>
+      <c r="B132" s="23"/>
       <c r="D132" s="7" t="s">
-        <v>156</v>
+        <v>238</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="18"/>
-      <c r="B133" s="24"/>
+      <c r="B133" s="23"/>
       <c r="D133" s="7" t="s">
-        <v>157</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="18"/>
-      <c r="B134" s="24"/>
+      <c r="B134" s="23"/>
       <c r="D134" s="7" t="s">
-        <v>158</v>
+        <v>240</v>
+      </c>
+      <c r="E134" t="s">
+        <v>337</v>
       </c>
       <c r="F134" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="18"/>
-      <c r="B135" s="24"/>
+      <c r="B135" s="23"/>
       <c r="D135" s="7" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="18"/>
-      <c r="B136" s="24"/>
+      <c r="B136" s="23"/>
       <c r="D136" s="7" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="18"/>
-      <c r="B137" s="24"/>
+      <c r="B137" s="23"/>
       <c r="D137" s="7" t="s">
-        <v>161</v>
+        <v>244</v>
+      </c>
+      <c r="E137" t="s">
+        <v>346</v>
       </c>
       <c r="F137" t="s">
         <v>245</v>
@@ -2931,424 +3380,472 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="18"/>
-      <c r="B138" s="24"/>
+      <c r="B138" s="23"/>
       <c r="D138" s="7" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="18"/>
-      <c r="B139" s="24"/>
+      <c r="B139" s="23"/>
       <c r="D139" s="7" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="18"/>
-      <c r="B140" s="24"/>
+      <c r="B140" s="23"/>
       <c r="C140" s="1" t="s">
-        <v>164</v>
+        <v>248</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>164</v>
+        <v>248</v>
       </c>
       <c r="E140" t="s">
         <v>249</v>
       </c>
       <c r="F140" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="18"/>
-      <c r="B141" s="24"/>
+      <c r="B141" s="23"/>
       <c r="D141" s="7" t="s">
-        <v>165</v>
+        <v>251</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="18"/>
-      <c r="B142" s="24"/>
+      <c r="B142" s="23"/>
       <c r="D142" s="7" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="18"/>
-      <c r="B143" s="24"/>
+      <c r="B143" s="23"/>
       <c r="D143" s="7" t="s">
-        <v>167</v>
+        <v>253</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="18"/>
-      <c r="B144" s="24"/>
+      <c r="B144" s="23"/>
       <c r="C144" s="1" t="s">
-        <v>168</v>
+        <v>254</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>169</v>
+        <v>255</v>
+      </c>
+      <c r="E144" t="s">
+        <v>350</v>
       </c>
       <c r="F144" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="18"/>
-      <c r="B145" s="24"/>
+      <c r="B145" s="23"/>
       <c r="D145" s="7" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="18"/>
-      <c r="B146" s="24"/>
+      <c r="B146" s="23"/>
       <c r="D146" s="7" t="s">
-        <v>171</v>
+        <v>258</v>
+      </c>
+      <c r="E146" t="s">
+        <v>394</v>
       </c>
       <c r="F146" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="18"/>
-      <c r="B147" s="24"/>
+      <c r="B147" s="23"/>
       <c r="D147" s="7" t="s">
-        <v>172</v>
+        <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="18"/>
-      <c r="B148" s="24"/>
+      <c r="B148" s="23"/>
       <c r="D148" s="7" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="18"/>
-      <c r="B149" s="24"/>
+      <c r="B149" s="23"/>
       <c r="C149" s="1" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>175</v>
+        <v>263</v>
+      </c>
+      <c r="E149" t="s">
+        <v>395</v>
       </c>
       <c r="F149" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="18"/>
-      <c r="B150" s="24"/>
+      <c r="B150" s="23"/>
       <c r="D150" s="7" t="s">
-        <v>176</v>
+        <v>265</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" s="18"/>
-      <c r="B151" s="24"/>
+      <c r="B151" s="23"/>
       <c r="D151" s="7" t="s">
-        <v>177</v>
+        <v>266</v>
+      </c>
+      <c r="E151" t="s">
+        <v>396</v>
       </c>
       <c r="F151" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="18"/>
-      <c r="B152" s="26"/>
+      <c r="B152" s="25"/>
       <c r="C152" s="9"/>
       <c r="D152" s="10" t="s">
-        <v>178</v>
+        <v>268</v>
+      </c>
+      <c r="E152" t="s">
+        <v>397</v>
       </c>
       <c r="F152" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="18"/>
-      <c r="B153" s="24" t="s">
-        <v>179</v>
+      <c r="B153" s="23" t="s">
+        <v>270</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>181</v>
+        <v>272</v>
+      </c>
+      <c r="E153" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="18"/>
-      <c r="B154" s="24" t="s">
-        <v>217</v>
+      <c r="B154" s="23" t="s">
+        <v>273</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>182</v>
+        <v>274</v>
       </c>
       <c r="E154" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="F154" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="18"/>
-      <c r="B155" s="24" t="s">
-        <v>218</v>
+      <c r="B155" s="23" t="s">
+        <v>277</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>183</v>
+        <v>278</v>
       </c>
       <c r="E155" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F155" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="18"/>
-      <c r="B156" s="24"/>
+      <c r="B156" s="23"/>
       <c r="D156" s="7" t="s">
-        <v>184</v>
+        <v>281</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="18"/>
-      <c r="B157" s="24"/>
+      <c r="B157" s="23"/>
       <c r="D157" s="7" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" s="18"/>
-      <c r="B158" s="24"/>
+      <c r="B158" s="23"/>
       <c r="D158" s="7" t="s">
-        <v>186</v>
+        <v>283</v>
+      </c>
+      <c r="E158" t="s">
+        <v>408</v>
       </c>
       <c r="F158" t="s">
-        <v>329</v>
+        <v>284</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="18"/>
-      <c r="B159" s="24"/>
+      <c r="B159" s="23"/>
       <c r="D159" s="7" t="s">
-        <v>187</v>
+        <v>285</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" s="18"/>
       <c r="B160" s="18"/>
       <c r="D160" s="7" t="s">
-        <v>188</v>
+        <v>286</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="18"/>
       <c r="B161" s="18"/>
       <c r="C161" s="1" t="s">
-        <v>189</v>
+        <v>287</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="E161" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="F161" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="18"/>
       <c r="B162" s="18"/>
       <c r="D162" s="7" t="s">
-        <v>191</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="18"/>
       <c r="B163" s="18"/>
       <c r="D163" s="7" t="s">
-        <v>192</v>
+        <v>292</v>
       </c>
       <c r="F163" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" s="18"/>
       <c r="B164" s="18"/>
       <c r="D164" s="7" t="s">
-        <v>193</v>
+        <v>294</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="18"/>
       <c r="B165" s="18"/>
       <c r="D165" s="7" t="s">
-        <v>194</v>
+        <v>295</v>
       </c>
       <c r="E165" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="F165" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" s="18"/>
       <c r="B166" s="18"/>
       <c r="D166" s="7" t="s">
-        <v>195</v>
+        <v>298</v>
       </c>
       <c r="E166" t="s">
-        <v>253</v>
+        <v>299</v>
       </c>
       <c r="F166" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" s="18"/>
       <c r="B167" s="18"/>
       <c r="C167" s="1" t="s">
-        <v>196</v>
+        <v>301</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>197</v>
+        <v>302</v>
+      </c>
+      <c r="E167" t="s">
+        <v>326</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="18"/>
       <c r="B168" s="18"/>
       <c r="D168" s="7" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="F168" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="18"/>
       <c r="B169" s="18"/>
       <c r="D169" s="7" t="s">
-        <v>199</v>
+        <v>306</v>
       </c>
       <c r="F169" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" s="18"/>
       <c r="B170" s="18"/>
       <c r="D170" s="7" t="s">
-        <v>200</v>
+        <v>308</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" s="18"/>
       <c r="B171" s="18"/>
       <c r="D171" s="7" t="s">
-        <v>201</v>
+        <v>309</v>
+      </c>
+      <c r="E171" t="s">
+        <v>404</v>
       </c>
       <c r="F171" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" s="18"/>
       <c r="B172" s="18"/>
       <c r="D172" s="7" t="s">
-        <v>202</v>
+        <v>311</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="18"/>
       <c r="B173" s="18"/>
       <c r="D173" s="7" t="s">
-        <v>203</v>
+        <v>312</v>
+      </c>
+      <c r="E173" t="s">
+        <v>334</v>
+      </c>
+      <c r="F173" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="18"/>
       <c r="B174" s="18"/>
       <c r="D174" s="7" t="s">
-        <v>204</v>
+        <v>313</v>
+      </c>
+      <c r="E174" t="s">
+        <v>406</v>
       </c>
       <c r="F174" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="18"/>
       <c r="B175" s="18"/>
       <c r="D175" s="7" t="s">
-        <v>205</v>
+        <v>315</v>
+      </c>
+      <c r="E175" t="s">
+        <v>407</v>
       </c>
       <c r="F175" t="s">
-        <v>230</v>
+        <v>316</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="18"/>
       <c r="B176" s="18"/>
       <c r="C176" s="1" t="s">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>207</v>
+        <v>318</v>
+      </c>
+      <c r="E176" t="s">
+        <v>405</v>
       </c>
       <c r="F176" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="18"/>
       <c r="B177" s="18"/>
       <c r="D177" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="18"/>
       <c r="B178" s="18"/>
       <c r="D178" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="18"/>
       <c r="B179" s="18"/>
       <c r="D179" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="18"/>
       <c r="B180" s="18"/>
       <c r="D180" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="18"/>
       <c r="B181" s="18"/>
       <c r="D181" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+      <c r="E181" t="s">
+        <v>343</v>
+      </c>
+      <c r="F181" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" s="19"/>
       <c r="B182" s="19"/>
       <c r="C182" s="9"/>
       <c r="D182" s="10" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/Settlements of Albany.xlsx
+++ b/Settlements of Albany.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a38c727b2e27c7e/Documents/Creative Writing/Tabletop/Albany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="304" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CF5F5AE-D138-4051-BC83-84D8245F08FF}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2D6C51A-E882-45DA-A0CF-18D6C40F2676}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="414">
   <si>
     <t>Old Kingdom</t>
   </si>
@@ -86,6 +86,9 @@
     <t>Dun Pharlain</t>
   </si>
   <si>
+    <t>Chief Ralf Pharlain</t>
+  </si>
+  <si>
     <t>checky or and sable, a griffin passant gules</t>
   </si>
   <si>
@@ -98,30 +101,45 @@
     <t>Inbhirleith</t>
   </si>
   <si>
+    <t>Chief Morris MacPharlain</t>
+  </si>
+  <si>
     <t>vert, a pantheon rampant or</t>
   </si>
   <si>
     <t>Dun Barra</t>
   </si>
   <si>
+    <t>Chief Angus Barra</t>
+  </si>
+  <si>
     <t>azure, a savage head vert</t>
   </si>
   <si>
     <t>Selsbrith</t>
   </si>
   <si>
+    <t>Chief John MacFulchiane</t>
+  </si>
+  <si>
     <t>or, three stags lodged azure</t>
   </si>
   <si>
     <t>Lockardsby</t>
   </si>
   <si>
+    <t>Chief William Ogill</t>
+  </si>
+  <si>
     <t>azure, three trees vert</t>
   </si>
   <si>
     <t>AYR</t>
   </si>
   <si>
+    <t>Laird James Buchane</t>
+  </si>
+  <si>
     <t>azure, three roundels sable</t>
   </si>
   <si>
@@ -131,6 +149,9 @@
     <t>Dun Patrick</t>
   </si>
   <si>
+    <t>Chief Giles Patrick</t>
+  </si>
+  <si>
     <t>Tynron Doon</t>
   </si>
   <si>
@@ -140,12 +161,18 @@
     <t>Dun Douglas</t>
   </si>
   <si>
+    <t>Chief Robert Douglad</t>
+  </si>
+  <si>
     <t>argent, three hearts gules</t>
   </si>
   <si>
     <t>Dun Drennan</t>
   </si>
   <si>
+    <t>Chief Angus Drennan</t>
+  </si>
+  <si>
     <t>azure, a gorge vert</t>
   </si>
   <si>
@@ -155,6 +182,9 @@
     <t>GARSCADDEN</t>
   </si>
   <si>
+    <t>Laird Robert MacNakill</t>
+  </si>
+  <si>
     <t>shepherd check sable and vert</t>
   </si>
   <si>
@@ -170,12 +200,18 @@
     <t>Dun Bhlathain</t>
   </si>
   <si>
+    <t>Chief Fergus Bhlathain</t>
+  </si>
+  <si>
     <t>shepherd check or and vert</t>
   </si>
   <si>
     <t>Pitloch Atholl</t>
   </si>
   <si>
+    <t>Chief Giles Atholl</t>
+  </si>
+  <si>
     <t>shepherd check gules and vert</t>
   </si>
   <si>
@@ -188,6 +224,9 @@
     <t>BREADHAIG</t>
   </si>
   <si>
+    <t>Laird Alan Erskyn</t>
+  </si>
+  <si>
     <t>azure, a triskele vert</t>
   </si>
   <si>
@@ -200,6 +239,9 @@
     <t>Dun Cambel</t>
   </si>
   <si>
+    <t>Chief Gawter Campbell</t>
+  </si>
+  <si>
     <t>orly vert and azure</t>
   </si>
   <si>
@@ -209,6 +251,9 @@
     <t>DUN DEAGH</t>
   </si>
   <si>
+    <t>Laird Neil MacMartane</t>
+  </si>
+  <si>
     <t>azure, an elk trippant argent</t>
   </si>
   <si>
@@ -227,24 +272,36 @@
     <t>Dunn Kiliwhimin</t>
   </si>
   <si>
+    <t>Chief Gylmyne Kiliwhimin</t>
+  </si>
+  <si>
     <t>glen check azure and vert</t>
   </si>
   <si>
     <t>INBHIRNESS</t>
   </si>
   <si>
+    <t>Laird James Forster</t>
+  </si>
+  <si>
     <t>houndstooth gules and vert</t>
   </si>
   <si>
     <t>Narann</t>
   </si>
   <si>
+    <t>Chief Amer Ross</t>
+  </si>
+  <si>
     <t>houndstooth gules and azure</t>
   </si>
   <si>
     <t>Thulnain</t>
   </si>
   <si>
+    <t>Chief Thomas MacIne</t>
+  </si>
+  <si>
     <t>gules, three annulets interlaced vert</t>
   </si>
   <si>
@@ -254,18 +311,27 @@
     <t>INBHIRDHEATH</t>
   </si>
   <si>
+    <t>Laird Davy Wardoon</t>
+  </si>
+  <si>
     <t>tartan gules and sable</t>
   </si>
   <si>
     <t>Dun Fraser</t>
   </si>
   <si>
+    <t>Chief Sym Fraser</t>
+  </si>
+  <si>
     <t>tartan azure and vert</t>
   </si>
   <si>
     <t>Duniness</t>
   </si>
   <si>
+    <t>Chief Andrew Lumbard</t>
+  </si>
+  <si>
     <t>tartan or and gules</t>
   </si>
   <si>
@@ -281,6 +347,9 @@
     <t>ABERLUNE</t>
   </si>
   <si>
+    <t>Earl Charles of Aberlune</t>
+  </si>
+  <si>
     <t>or, a dog courant gules</t>
   </si>
   <si>
@@ -299,6 +368,9 @@
     <t>Harbwr Gwyn</t>
   </si>
   <si>
+    <t>Mayor Arwyn ap Trefor</t>
+  </si>
+  <si>
     <t>vert, ford, three trefoils argent in fess</t>
   </si>
   <si>
@@ -308,6 +380,9 @@
     <t>Manceinion</t>
   </si>
   <si>
+    <t>Baron William Glyn</t>
+  </si>
+  <si>
     <t>gules, two bends or, a dog-head-collared-couped gules</t>
   </si>
   <si>
@@ -317,12 +392,18 @@
     <t>DEVERDOEU</t>
   </si>
   <si>
+    <t>Earl Hywel Bevan</t>
+  </si>
+  <si>
     <t>azure, seven crosses couped in annulo or, a dragon head much smaller caboshed gules</t>
   </si>
   <si>
     <t>Penbedw</t>
   </si>
   <si>
+    <t>Sir Hywel Vaughan</t>
+  </si>
+  <si>
     <t>vert, two dragon heads couped gules respecting each other</t>
   </si>
   <si>
@@ -332,12 +413,21 @@
     <t>Pengwern</t>
   </si>
   <si>
+    <t>Earl Tomos ap Arwyn</t>
+  </si>
+  <si>
     <t>erminois, a dragon rampant sable</t>
   </si>
   <si>
     <t>Llanllieni</t>
   </si>
   <si>
+    <t xml:space="preserve">Earl Dafydd Llewelyn </t>
+  </si>
+  <si>
+    <t>gules, a rosary or above a lion dormant argent</t>
+  </si>
+  <si>
     <t>Rheradr</t>
   </si>
   <si>
@@ -353,6 +443,12 @@
     <t>Caerblaidd</t>
   </si>
   <si>
+    <t>Earl Gareth Beausire</t>
+  </si>
+  <si>
+    <t>ermine, two wolves reguardant sable combatant</t>
+  </si>
+  <si>
     <t>Glanfa Llyffant</t>
   </si>
   <si>
@@ -362,6 +458,9 @@
     <t>CYNWY</t>
   </si>
   <si>
+    <t>Earl Caradog Conway</t>
+  </si>
+  <si>
     <t>sable, a dragon couchant argent</t>
   </si>
   <si>
@@ -374,6 +473,9 @@
     <t>Pen Maelor</t>
   </si>
   <si>
+    <t>Baron Rhun ap Madoc</t>
+  </si>
+  <si>
     <t>vert, ford, in sinister side a dragon rampant gules and in dexter side a sea dragon gules</t>
   </si>
   <si>
@@ -410,6 +512,9 @@
     <t>Pont Myrddin</t>
   </si>
   <si>
+    <t>Earl Cyndeyrn Wyllt</t>
+  </si>
+  <si>
     <t>azure, a dragon in annulo gules</t>
   </si>
   <si>
@@ -437,6 +542,9 @@
     <t>ABONA</t>
   </si>
   <si>
+    <t>Earl Marc ap Rhodri</t>
+  </si>
+  <si>
     <t>gules, ford, a bend argent, a dragon's head or</t>
   </si>
   <si>
@@ -446,18 +554,30 @@
     <t>Caerloyw</t>
   </si>
   <si>
+    <t>Sir Teyrnon Loyw</t>
+  </si>
+  <si>
     <t>rosace vert and or, a gauntlet argent en soleil much smaller</t>
   </si>
   <si>
     <t>Treffynnon</t>
   </si>
   <si>
+    <t>Sir Dafydd ap Terwyn</t>
+  </si>
+  <si>
+    <t>azure, chevron engrailed or, two doves argent legged or armed gules beaked gules above an oak tree vert</t>
+  </si>
+  <si>
     <t>Corinium</t>
   </si>
   <si>
     <t>Dyrh</t>
   </si>
   <si>
+    <t>Earl Cadeyrn Cynwrig</t>
+  </si>
+  <si>
     <t>per fess embattled, azure and gules, a pitcher or</t>
   </si>
   <si>
@@ -470,24 +590,36 @@
     <t>Durnovara</t>
   </si>
   <si>
+    <t>Sir Bryn ap Rhys</t>
+  </si>
+  <si>
     <t>quarterly gules and azure, a cross or</t>
   </si>
   <si>
     <t>Caer Morglawdd</t>
   </si>
   <si>
+    <t>Earl Ieuan Gulliver</t>
+  </si>
+  <si>
     <t xml:space="preserve">sable, ford, three gauntlet argent in fess </t>
   </si>
   <si>
     <t>Croesi Arth</t>
   </si>
   <si>
+    <t>Sir Arthur ap Llwyd</t>
+  </si>
+  <si>
     <t>sable, a bear carrying a cross argent</t>
   </si>
   <si>
     <t>Hen Sarum</t>
   </si>
   <si>
+    <t>Earl Owain ap Ieuan Gradawc</t>
+  </si>
+  <si>
     <t>vert a stone circle argent</t>
   </si>
   <si>
@@ -524,6 +656,12 @@
     <t>Treftone</t>
   </si>
   <si>
+    <t>Baron Margon Flynn</t>
+  </si>
+  <si>
+    <t>gules, bend dovetailed azure, a dragon head erased or</t>
+  </si>
+  <si>
     <t>Gifl</t>
   </si>
   <si>
@@ -539,12 +677,18 @@
     <t>Tairafon</t>
   </si>
   <si>
+    <t>Sir Owain Wynne</t>
+  </si>
+  <si>
     <t>sable three dragon heads or</t>
   </si>
   <si>
     <t>Pensanctaidd</t>
   </si>
   <si>
+    <t>Bishop Dafydd</t>
+  </si>
+  <si>
     <t>argent a mitre or above a dragon's head or</t>
   </si>
   <si>
@@ -566,9 +710,6 @@
     <t>Skaw</t>
   </si>
   <si>
-    <t>Sir Howell Tresco</t>
-  </si>
-  <si>
     <t>azure, in chief fess invected or, in chief three elder blossoms argent in fess</t>
   </si>
   <si>
@@ -581,6 +722,9 @@
     <t>DUNHELM</t>
   </si>
   <si>
+    <t>Earl Harold Thirkell</t>
+  </si>
+  <si>
     <t>sable, a cross vert, four wolves rampant argent combatant</t>
   </si>
   <si>
@@ -602,12 +746,21 @@
     <t>Aida</t>
   </si>
   <si>
+    <t>Abbott Cuthbert</t>
+  </si>
+  <si>
     <t>argent, ford, a cross or</t>
   </si>
   <si>
     <t>Byggwyk</t>
   </si>
   <si>
+    <t>Baron Gunther Sjorefur</t>
+  </si>
+  <si>
+    <t>vert, ford, a sea-fox guardant argent above a longship or</t>
+  </si>
+  <si>
     <t>Jetborough</t>
   </si>
   <si>
@@ -620,6 +773,9 @@
     <t>Horgrsgate</t>
   </si>
   <si>
+    <t>Earl Ralph Ormsby</t>
+  </si>
+  <si>
     <t>barry bowed vert and argent, a boars head caboshed or</t>
   </si>
   <si>
@@ -629,6 +785,9 @@
     <t>Loidis</t>
   </si>
   <si>
+    <t>Baron Thomas Hammond</t>
+  </si>
+  <si>
     <t>mullety of 10 azure and or, a wolf rampant argent</t>
   </si>
   <si>
@@ -638,36 +797,54 @@
     <t>Raudmarsh</t>
   </si>
   <si>
+    <t>Baron Thurston Gill</t>
+  </si>
+  <si>
     <t>barry wavy gules and azure, a wolf rampant gules</t>
   </si>
   <si>
     <t>Hvitby</t>
   </si>
   <si>
+    <t>Abbott Hildred</t>
+  </si>
+  <si>
     <t>barry wavy azure and argent, in fess three croziers vert above a mitre or</t>
   </si>
   <si>
     <t>Skardaborough</t>
   </si>
   <si>
+    <t>Earl Eric Sandgate</t>
+  </si>
+  <si>
     <t>sable, ford, a tower argent above a ship or</t>
   </si>
   <si>
     <t>Bjorrton</t>
   </si>
   <si>
+    <t>Sir Gunter Foss</t>
+  </si>
+  <si>
     <t>per fess azure and barry wavy azure and argent, in chief a beaver or</t>
   </si>
   <si>
     <t>Wyke</t>
   </si>
   <si>
+    <t>Mayor Hardwin Gunn</t>
+  </si>
+  <si>
     <t>sable, a chevron ploye ermine, three wolf's heads argent</t>
   </si>
   <si>
     <t>LINDIS</t>
   </si>
   <si>
+    <t>Bishop Thomas</t>
+  </si>
+  <si>
     <t>per fess gules and argent, in first quarter a virgin argent and in second quarter a paschal lamb argent banner or and a mitre gules smaller</t>
   </si>
   <si>
@@ -677,12 +854,18 @@
     <t>Konigsby</t>
   </si>
   <si>
+    <t>Mayor Randel Piers</t>
+  </si>
+  <si>
     <t>barry indented one in the other vert and or</t>
   </si>
   <si>
     <t>Gegnesborough</t>
   </si>
   <si>
+    <t>Baron Wolfstan Thwaite</t>
+  </si>
+  <si>
     <t xml:space="preserve">quarterly 1st and 4th, papelonny vert and argent, 2nd and 3rd, paly sable and or a falcon striking argent; </t>
   </si>
   <si>
@@ -698,18 +881,27 @@
     <t>Skumasthorp</t>
   </si>
   <si>
+    <t>Sir Henry Umber</t>
+  </si>
+  <si>
     <t>barry wavy vert and or, three wheat sheafs or</t>
   </si>
   <si>
     <t>Vodinnswyk</t>
   </si>
   <si>
+    <t>Mayor Ranulf Rawlinsson</t>
+  </si>
+  <si>
     <t xml:space="preserve">sable, ford, a raven or </t>
   </si>
   <si>
     <t>Skaggisness</t>
   </si>
   <si>
+    <t>Sir Wymond Raven</t>
+  </si>
+  <si>
     <t>per bend sinister azure and sable, three cranes argent legged or beaked gules</t>
   </si>
   <si>
@@ -719,12 +911,18 @@
     <t>DEORABY</t>
   </si>
   <si>
+    <t>Earl Osmond Sanderson</t>
+  </si>
+  <si>
     <t>fretty vert and argent, two ash trees eradicated or above a stag lodged reguardant or</t>
   </si>
   <si>
     <t>Notingborough</t>
   </si>
   <si>
+    <t>Mayor Ronald Beck</t>
+  </si>
+  <si>
     <t>checky vert and argent, an ash trees eradicated or</t>
   </si>
   <si>
@@ -752,6 +950,9 @@
     <t>Soarcester</t>
   </si>
   <si>
+    <t>Earl Simon Stannard</t>
+  </si>
+  <si>
     <t>argent, four cinquefoils gules arranged two one one</t>
   </si>
   <si>
@@ -764,6 +965,9 @@
     <t>Huntaton</t>
   </si>
   <si>
+    <t>Earl Edmund Ansell</t>
+  </si>
+  <si>
     <t xml:space="preserve">checky vert and sable, a bow with arrow nocked or </t>
   </si>
   <si>
@@ -776,6 +980,9 @@
     <t>Laminton</t>
   </si>
   <si>
+    <t>Baron Robert Tyrrell</t>
+  </si>
+  <si>
     <t>fretty sable and gules, a quarter ermine</t>
   </si>
   <si>
@@ -809,6 +1016,9 @@
     <t>NORWYK</t>
   </si>
   <si>
+    <t>Earl Robert Lund</t>
+  </si>
+  <si>
     <t>per pale ermine and gules, in second quarter a wolf sejant, in fourth quarter a ship argent</t>
   </si>
   <si>
@@ -818,6 +1028,9 @@
     <t>Vodinnsmere</t>
   </si>
   <si>
+    <t>Sir Giles Faramond</t>
+  </si>
+  <si>
     <t>per fess vert and estencely azure and vert, three ravens sable</t>
   </si>
   <si>
@@ -833,6 +1046,9 @@
     <t>GYPPESWYK</t>
   </si>
   <si>
+    <t>Earl Everard Nivett</t>
+  </si>
+  <si>
     <t>per chevron gules and lozengy azure and argent, in chief a sun or, a sunburst or</t>
   </si>
   <si>
@@ -842,12 +1058,18 @@
     <t>Saesmond</t>
   </si>
   <si>
+    <t>Sir Edward Godwin</t>
+  </si>
+  <si>
     <t>per chausse fretty azure and argent and argent, a fish embowed or</t>
   </si>
   <si>
     <t>Aedmondsbury</t>
   </si>
   <si>
+    <t>Sir Lionel Siward</t>
+  </si>
+  <si>
     <t>per pale fretty argent and azure and argent, in sinister side a lion rampant azure</t>
   </si>
   <si>
@@ -860,6 +1082,9 @@
     <t>CELMFORD</t>
   </si>
   <si>
+    <t>Earl Henry Harding</t>
+  </si>
+  <si>
     <t>Walter de Hameton</t>
   </si>
   <si>
@@ -893,6 +1118,9 @@
     <t>Waecia</t>
   </si>
   <si>
+    <t>Sir Charles Bonet</t>
+  </si>
+  <si>
     <t>quarterly lozengy argent and azure and checky azure and argent, five roundels or in orle</t>
   </si>
   <si>
@@ -950,6 +1178,9 @@
     <t>GREATMINSTER</t>
   </si>
   <si>
+    <t>Lord Mayor Nicholas Downes</t>
+  </si>
+  <si>
     <t>per pale chequy argent and azure and lozengy argent and azure, a fess azure charged with three bells or, in chief a crown or and in base a tower argent.</t>
   </si>
   <si>
@@ -971,6 +1202,9 @@
     <t>Redhill</t>
   </si>
   <si>
+    <t>Sir Edwin Norton</t>
+  </si>
+  <si>
     <t>per fess gules and papelonny azure and argent</t>
   </si>
   <si>
@@ -980,15 +1214,27 @@
     <t>Hedgeward</t>
   </si>
   <si>
+    <t>Earl Thomas Falstaff</t>
+  </si>
+  <si>
+    <t>per fess wavy vert and azure, a sword argent above three trees vert</t>
+  </si>
+  <si>
     <t>Harhenhall</t>
   </si>
   <si>
+    <t>Sir Bernard Dacre</t>
+  </si>
+  <si>
     <t>quarterly checky argent and azure, and maily sable and or, crancelin or</t>
   </si>
   <si>
     <t>Haesta</t>
   </si>
   <si>
+    <t>Sir Frederick de Jerrais</t>
+  </si>
+  <si>
     <t>lozengy argent and azure, a knight mounted sable armoured argent maned argent caparisoned or, unguled or</t>
   </si>
   <si>
@@ -998,6 +1244,9 @@
     <t>CANTIABURY</t>
   </si>
   <si>
+    <t>Archbishop Peter</t>
+  </si>
+  <si>
     <t>quarterly estencely azure and argent and roundelly argent and azure, three lions rampant or</t>
   </si>
   <si>
@@ -1010,268 +1259,28 @@
     <t>Bridgeton</t>
   </si>
   <si>
+    <t>argent, a fess vert and a quarter vert</t>
+  </si>
+  <si>
     <t>Speldhall</t>
   </si>
   <si>
     <t>Wealderton</t>
   </si>
   <si>
+    <t>Earl Gerard Lovell</t>
+  </si>
+  <si>
+    <t>per chief throughout azure and argent, a sea-lion gules above seven oak trees vert</t>
+  </si>
+  <si>
     <t>Mootburne</t>
   </si>
   <si>
-    <t>Lord Mayor Nicholas Downes</t>
-  </si>
-  <si>
-    <t>Earl Harold Thirkell</t>
-  </si>
-  <si>
-    <t>Baron Sjoskip</t>
-  </si>
-  <si>
-    <t>Abbott Cuthbert</t>
-  </si>
-  <si>
-    <t>Earl Gareth Beausire</t>
-  </si>
-  <si>
-    <t>Earl Tomos ap Arwyn</t>
-  </si>
-  <si>
-    <t>ermine, two wolves reguardant sable combatant</t>
-  </si>
-  <si>
-    <t>per fess wavy vert and azure, a sword argent above three trees vert</t>
-  </si>
-  <si>
-    <t>Earl Thomas Falstaff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earl Dafydd Llewelyn </t>
-  </si>
-  <si>
-    <t>gules, a rosary or above a lion dormant argent</t>
-  </si>
-  <si>
-    <t>Earl Edmund Ansell</t>
-  </si>
-  <si>
-    <t>Earl Marc ap Rhodri</t>
-  </si>
-  <si>
-    <t>Earl Owain ap Ieuan Gradawc</t>
-  </si>
-  <si>
-    <t>Earl Ieuan Gulliver</t>
-  </si>
-  <si>
-    <t>Earl Cadeyrn Cynwrig</t>
-  </si>
-  <si>
-    <t>Earl Cyndeyrn Wyllt</t>
-  </si>
-  <si>
-    <t>Earl Gerard Lovell</t>
-  </si>
-  <si>
-    <t>per chief throughout azure and argent, a sea-lion gules above seven oak trees vert</t>
-  </si>
-  <si>
-    <t>Earl Eric Sandgate</t>
-  </si>
-  <si>
-    <t>Baron Robert Tyrrell</t>
-  </si>
-  <si>
-    <t>Mayor Hardwin Gunn</t>
-  </si>
-  <si>
-    <t>Earl Osmond Sanderson</t>
-  </si>
-  <si>
-    <t>Mayor Ronald Beck</t>
-  </si>
-  <si>
-    <t>Earl Robert Lund</t>
-  </si>
-  <si>
-    <t>Earl Ralph Ormsby</t>
-  </si>
-  <si>
-    <t>Baron Thomas Hammond</t>
-  </si>
-  <si>
-    <t>Abbott Hildred</t>
-  </si>
-  <si>
-    <t>Baron Thurston Gill</t>
-  </si>
-  <si>
-    <t>Earl Caradog Conway</t>
-  </si>
-  <si>
-    <t>Baron Rhun ap Madoc</t>
-  </si>
-  <si>
-    <t>Mayor Arwyn ap Trefor</t>
-  </si>
-  <si>
-    <t>Baron William Glyn</t>
-  </si>
-  <si>
-    <t>Earl Charles of Aberlune</t>
-  </si>
-  <si>
-    <t>Baron Wolfstan Thwaite</t>
-  </si>
-  <si>
-    <t>Bishop Thomas</t>
-  </si>
-  <si>
-    <t>Mayor Ranulf Rawlinsson</t>
-  </si>
-  <si>
-    <t>Laird James Buchane</t>
-  </si>
-  <si>
-    <t>Laird Neil MacMartane</t>
-  </si>
-  <si>
-    <t>Chief Giles Patrick</t>
-  </si>
-  <si>
-    <t>Chief Giles Atholl</t>
-  </si>
-  <si>
-    <t>Chief Robert Douglad</t>
-  </si>
-  <si>
-    <t>Chief Angus Drennan</t>
-  </si>
-  <si>
-    <t>Chief Fergus Bhlathain</t>
-  </si>
-  <si>
-    <t>Laird Robert MacNakill</t>
-  </si>
-  <si>
-    <t>Laird Alan Erskyn</t>
-  </si>
-  <si>
-    <t>Laird Davy Wardoon</t>
-  </si>
-  <si>
-    <t>Chief Sym Fraser</t>
-  </si>
-  <si>
-    <t>Chief Amer Ross</t>
-  </si>
-  <si>
-    <t>Chief Thomas MacIne</t>
-  </si>
-  <si>
-    <t>Chief Andrew Lumbard</t>
-  </si>
-  <si>
-    <t>Chief Ralf Pharlain</t>
-  </si>
-  <si>
-    <t>Chief Morris MacPharlain</t>
-  </si>
-  <si>
-    <t>Chief Angus Barra</t>
-  </si>
-  <si>
-    <t>Chief John MacFulchiane</t>
-  </si>
-  <si>
-    <t>Chief William Ogill</t>
-  </si>
-  <si>
-    <t>Chief Gylmyne Kiliwhimin</t>
-  </si>
-  <si>
-    <t>Chief Gawter Campbell</t>
-  </si>
-  <si>
-    <t>Laird James Forster</t>
-  </si>
-  <si>
-    <t>Earl Hywel Bevan</t>
-  </si>
-  <si>
-    <t>Sir Hywel Vaughan</t>
-  </si>
-  <si>
-    <t>Sir Owain Wynne</t>
-  </si>
-  <si>
-    <t>Bishop Dafydd</t>
-  </si>
-  <si>
-    <t>Sir Arthur ap Llwyd</t>
-  </si>
-  <si>
-    <t>Mayor Randel Piers</t>
-  </si>
-  <si>
-    <t>Sir Henry Umber</t>
-  </si>
-  <si>
-    <t>Sir Wymond Raven</t>
-  </si>
-  <si>
-    <t>Sir Gunter Foss</t>
-  </si>
-  <si>
-    <t>Sir Giles Faramond</t>
-  </si>
-  <si>
-    <t>Earl Everard Nivett</t>
-  </si>
-  <si>
-    <t>Sir Edward Godwin</t>
-  </si>
-  <si>
-    <t>Sir Lionel Siward</t>
-  </si>
-  <si>
-    <t>Earl Henry Harding</t>
-  </si>
-  <si>
-    <t>Sir Dafydd ap Terwyn</t>
-  </si>
-  <si>
-    <t>Sir Teyrnon Loyw</t>
-  </si>
-  <si>
-    <t>azure, chevron engrailed or, two doves argent legged or armed gules beaked gules above an oak tree vert</t>
-  </si>
-  <si>
-    <t>Sir Bryn ap Rhys</t>
-  </si>
-  <si>
-    <t>Earl Simon Stannard</t>
-  </si>
-  <si>
-    <t>Sir Edwin Norton</t>
-  </si>
-  <si>
-    <t>Archbishop Peter</t>
-  </si>
-  <si>
-    <t>Sir Bernard Dacre</t>
-  </si>
-  <si>
-    <t>Sir Frederick de Jerrais</t>
-  </si>
-  <si>
-    <t>Sir Charles Bonet</t>
-  </si>
-  <si>
-    <t>Baron Margon Flynn</t>
-  </si>
-  <si>
-    <t>gules, bend dovetailed azure, a dragon head erased or</t>
+    <t>Sir Huw Tresco</t>
+  </si>
+  <si>
+    <t>Sir Dafydd Strangeway</t>
   </si>
 </sst>
 </file>
@@ -1554,6 +1563,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1928,395 +1941,395 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>377</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="20"/>
       <c r="D6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="D7" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="D8" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>379</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="D10" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>380</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="D11" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>363</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="D13" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="D14" s="7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>365</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="D15" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="D16" s="7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>367</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="D17" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>368</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>370</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="D19" s="7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="D20" s="7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="D21" s="7" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="D22" s="7" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>369</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="D23" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>366</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="D24" s="7" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>371</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="D26" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="D27" s="7" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="D28" s="7" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>383</v>
+        <v>66</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>364</v>
+        <v>70</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="D30" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="D31" s="7" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="D32" s="7" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="D33" s="7" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>382</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E34" t="s">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="D35" s="7" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="D36" s="7" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
-        <v>375</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E37" t="s">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="D38" s="7" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>373</v>
+        <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="D39" s="7" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="F39" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2324,255 +2337,255 @@
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
       <c r="D40" s="10" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E41" t="s">
-        <v>359</v>
+        <v>102</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
       <c r="B42" s="12" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>
       <c r="B43" s="12" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="D44" s="7" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="D45" s="7" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E45" t="s">
-        <v>357</v>
+        <v>109</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="D46" s="7" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="D47" s="7" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
-        <v>358</v>
+        <v>113</v>
       </c>
       <c r="F47" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="1" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="E48" t="s">
-        <v>385</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="D49" s="7" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="E49" t="s">
-        <v>386</v>
+        <v>120</v>
       </c>
       <c r="F49" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="D50" s="7" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="D51" s="7" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="E51" t="s">
-        <v>331</v>
+        <v>124</v>
       </c>
       <c r="F51" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="D52" s="7" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="E52" t="s">
-        <v>335</v>
+        <v>127</v>
       </c>
       <c r="F52" t="s">
-        <v>336</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="D53" s="7" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="D54" s="7" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="D55" s="7" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="D56" s="7" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="D57" s="7" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="E57" t="s">
-        <v>330</v>
+        <v>134</v>
       </c>
       <c r="F57" t="s">
-        <v>332</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="D58" s="7" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="1" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E59" t="s">
-        <v>355</v>
+        <v>139</v>
       </c>
       <c r="F59" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="D60" s="7" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="D61" s="7" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="D62" s="7" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E62" t="s">
-        <v>356</v>
+        <v>144</v>
       </c>
       <c r="F62" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="D63" s="7" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="1" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -2580,348 +2593,348 @@
       <c r="B65" s="14"/>
       <c r="C65" s="9"/>
       <c r="D65" s="10" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="12"/>
       <c r="B66" s="12" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="E66" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="F66" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="12"/>
       <c r="B67" s="12" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="E67" t="s">
-        <v>342</v>
+        <v>157</v>
       </c>
       <c r="F67" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="12"/>
       <c r="B68" s="12" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="D69" s="7" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="D70" s="7" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="D71" s="7" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="D72" s="7" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="1" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="E73" t="s">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="F73" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="D74" s="7" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="D75" s="7" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="E75" t="s">
-        <v>400</v>
+        <v>171</v>
       </c>
       <c r="F75" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="D76" s="7" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="E76" t="s">
-        <v>399</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
-        <v>401</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="D77" s="7" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="D78" s="7" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="E78" t="s">
-        <v>341</v>
+        <v>178</v>
       </c>
       <c r="F78" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="D79" s="7" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="D80" s="7" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="D81" s="7" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="E81" t="s">
-        <v>402</v>
+        <v>183</v>
       </c>
       <c r="F81" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="D82" s="7" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="E82" t="s">
-        <v>340</v>
+        <v>186</v>
       </c>
       <c r="F82" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="D83" s="7" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="E83" t="s">
-        <v>389</v>
+        <v>189</v>
       </c>
       <c r="F83" t="s">
-        <v>147</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="D84" s="7" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="E84" t="s">
-        <v>339</v>
+        <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="1" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="E85" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="F85" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="D86" s="7" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="1" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="E87" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="F87" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="D88" s="7" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="D89" s="7" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="E89" t="s">
-        <v>409</v>
+        <v>205</v>
       </c>
       <c r="F89" t="s">
-        <v>410</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="D90" s="7" t="s">
-        <v>161</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="D91" s="7" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="D92" s="7" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="D93" s="7" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="D94" s="7" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="E94" t="s">
-        <v>387</v>
+        <v>212</v>
       </c>
       <c r="F94" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="D95" s="7" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="E95" t="s">
-        <v>388</v>
+        <v>215</v>
       </c>
       <c r="F95" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="D96" s="7" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="1" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="E97" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="F97" t="s">
-        <v>173</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -2929,341 +2942,344 @@
       <c r="B98" s="14"/>
       <c r="C98" s="9"/>
       <c r="D98" s="10" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="E98" t="s">
-        <v>175</v>
+        <v>412</v>
       </c>
       <c r="F98" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="15" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="E99" t="s">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="F99" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="16"/>
       <c r="B100" s="16" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="16"/>
       <c r="B101" s="16" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="16"/>
       <c r="B102" s="16"/>
       <c r="D102" s="7" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="16"/>
       <c r="B103" s="16"/>
       <c r="D103" s="7" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="E103" t="s">
-        <v>329</v>
+        <v>235</v>
       </c>
       <c r="F103" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="16"/>
       <c r="B104" s="16"/>
       <c r="D104" s="7" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="E104" t="s">
-        <v>328</v>
+        <v>238</v>
+      </c>
+      <c r="F104" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="16"/>
       <c r="B105" s="16"/>
       <c r="D105" s="7" t="s">
-        <v>189</v>
+        <v>240</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
       <c r="C106" s="1" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="E106" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="F106" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
       <c r="D107" s="7" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="E107" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="F107" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
       <c r="D108" s="7" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
       <c r="D109" s="7" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="E109" t="s">
-        <v>352</v>
+        <v>248</v>
       </c>
       <c r="F109" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
       <c r="D110" s="7" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
       <c r="D111" s="7" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="E111" t="s">
-        <v>354</v>
+        <v>252</v>
       </c>
       <c r="F111" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
       <c r="D112" s="7" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="E112" t="s">
-        <v>353</v>
+        <v>255</v>
       </c>
       <c r="F112" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="16"/>
       <c r="B113" s="16"/>
       <c r="D113" s="7" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="E113" t="s">
-        <v>345</v>
+        <v>258</v>
       </c>
       <c r="F113" t="s">
-        <v>203</v>
+        <v>259</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="16"/>
       <c r="B114" s="16"/>
       <c r="D114" s="7" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="E114" t="s">
-        <v>393</v>
+        <v>261</v>
       </c>
       <c r="F114" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="16"/>
       <c r="B115" s="16"/>
       <c r="D115" s="7" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="E115" t="s">
-        <v>347</v>
+        <v>264</v>
       </c>
       <c r="F115" t="s">
-        <v>207</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="16"/>
       <c r="B116" s="16"/>
       <c r="C116" s="1" t="s">
-        <v>208</v>
+        <v>266</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>208</v>
+        <v>266</v>
       </c>
       <c r="E116" t="s">
-        <v>361</v>
+        <v>267</v>
       </c>
       <c r="F116" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="16"/>
       <c r="B117" s="16"/>
       <c r="D117" s="7" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="16"/>
       <c r="B118" s="16"/>
       <c r="D118" s="7" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="E118" t="s">
-        <v>390</v>
+        <v>271</v>
       </c>
       <c r="F118" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="16"/>
       <c r="B119" s="16"/>
       <c r="D119" s="7" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="E119" t="s">
-        <v>360</v>
+        <v>274</v>
       </c>
       <c r="F119" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="16"/>
       <c r="B120" s="16"/>
       <c r="D120" s="7" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="16"/>
       <c r="B121" s="16"/>
       <c r="D121" s="7" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="16"/>
       <c r="B122" s="16"/>
       <c r="D122" s="7" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="16"/>
       <c r="B123" s="16"/>
       <c r="D123" s="7" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="E123" t="s">
-        <v>391</v>
+        <v>280</v>
       </c>
       <c r="F123" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="16"/>
       <c r="B124" s="16"/>
       <c r="D124" s="7" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="E124" t="s">
-        <v>362</v>
+        <v>283</v>
       </c>
       <c r="F124" t="s">
-        <v>221</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="16"/>
       <c r="B125" s="16"/>
       <c r="D125" s="7" t="s">
-        <v>222</v>
+        <v>285</v>
       </c>
       <c r="E125" t="s">
-        <v>392</v>
+        <v>286</v>
       </c>
       <c r="F125" t="s">
-        <v>223</v>
+        <v>287</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="16"/>
       <c r="B126" s="16"/>
       <c r="D126" s="7" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="16"/>
       <c r="B127" s="16"/>
       <c r="C127" s="1" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="E127" t="s">
-        <v>348</v>
+        <v>290</v>
       </c>
       <c r="F127" t="s">
-        <v>226</v>
+        <v>291</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
@@ -3271,248 +3287,248 @@
       <c r="B128" s="17"/>
       <c r="C128" s="9"/>
       <c r="D128" s="10" t="s">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="E128" t="s">
-        <v>349</v>
+        <v>293</v>
       </c>
       <c r="F128" t="s">
-        <v>228</v>
+        <v>294</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="18" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
       <c r="B129" s="24" t="s">
-        <v>230</v>
+        <v>296</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>231</v>
+        <v>297</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>231</v>
+        <v>297</v>
       </c>
       <c r="E129" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
       <c r="F129" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="18"/>
       <c r="B130" s="23" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="18"/>
       <c r="B131" s="23" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="E131" t="s">
-        <v>403</v>
+        <v>303</v>
       </c>
       <c r="F131" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="18"/>
       <c r="B132" s="23"/>
       <c r="D132" s="7" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="18"/>
       <c r="B133" s="23"/>
       <c r="D133" s="7" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="18"/>
       <c r="B134" s="23"/>
       <c r="D134" s="7" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="E134" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="F134" t="s">
-        <v>241</v>
+        <v>309</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="18"/>
       <c r="B135" s="23"/>
       <c r="D135" s="7" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="18"/>
       <c r="B136" s="23"/>
       <c r="D136" s="7" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="18"/>
       <c r="B137" s="23"/>
       <c r="D137" s="7" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="E137" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="F137" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="18"/>
       <c r="B138" s="23"/>
       <c r="D138" s="7" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="18"/>
       <c r="B139" s="23"/>
       <c r="D139" s="7" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="18"/>
       <c r="B140" s="23"/>
       <c r="C140" s="1" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="E140" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="F140" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="18"/>
       <c r="B141" s="23"/>
       <c r="D141" s="7" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="18"/>
       <c r="B142" s="23"/>
       <c r="D142" s="7" t="s">
-        <v>252</v>
+        <v>321</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="18"/>
       <c r="B143" s="23"/>
       <c r="D143" s="7" t="s">
-        <v>253</v>
+        <v>322</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="18"/>
       <c r="B144" s="23"/>
       <c r="C144" s="1" t="s">
-        <v>254</v>
+        <v>323</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>255</v>
+        <v>324</v>
       </c>
       <c r="E144" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="F144" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="18"/>
       <c r="B145" s="23"/>
       <c r="D145" s="7" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="18"/>
       <c r="B146" s="23"/>
       <c r="D146" s="7" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="E146" t="s">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="F146" t="s">
-        <v>259</v>
+        <v>330</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="18"/>
       <c r="B147" s="23"/>
       <c r="D147" s="7" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="18"/>
       <c r="B148" s="23"/>
       <c r="D148" s="7" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="18"/>
       <c r="B149" s="23"/>
       <c r="C149" s="1" t="s">
-        <v>262</v>
+        <v>333</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="E149" t="s">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="F149" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="18"/>
       <c r="B150" s="23"/>
       <c r="D150" s="7" t="s">
-        <v>265</v>
+        <v>337</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" s="18"/>
       <c r="B151" s="23"/>
       <c r="D151" s="7" t="s">
-        <v>266</v>
+        <v>338</v>
       </c>
       <c r="E151" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
       <c r="F151" t="s">
-        <v>267</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
@@ -3520,324 +3536,330 @@
       <c r="B152" s="25"/>
       <c r="C152" s="9"/>
       <c r="D152" s="10" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="E152" t="s">
-        <v>397</v>
+        <v>342</v>
       </c>
       <c r="F152" t="s">
-        <v>269</v>
+        <v>343</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="18"/>
       <c r="B153" s="23" t="s">
-        <v>270</v>
+        <v>344</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>271</v>
+        <v>345</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>272</v>
+        <v>346</v>
       </c>
       <c r="E153" t="s">
-        <v>398</v>
+        <v>347</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="18"/>
       <c r="B154" s="23" t="s">
-        <v>273</v>
+        <v>348</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>274</v>
+        <v>349</v>
       </c>
       <c r="E154" t="s">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="F154" t="s">
-        <v>276</v>
+        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="18"/>
       <c r="B155" s="23" t="s">
-        <v>277</v>
+        <v>352</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>278</v>
+        <v>353</v>
       </c>
       <c r="E155" t="s">
-        <v>279</v>
+        <v>354</v>
       </c>
       <c r="F155" t="s">
-        <v>280</v>
+        <v>355</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="18"/>
       <c r="B156" s="23"/>
       <c r="D156" s="7" t="s">
-        <v>281</v>
+        <v>356</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="18"/>
       <c r="B157" s="23"/>
       <c r="D157" s="7" t="s">
-        <v>282</v>
+        <v>357</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" s="18"/>
       <c r="B158" s="23"/>
       <c r="D158" s="7" t="s">
-        <v>283</v>
+        <v>358</v>
       </c>
       <c r="E158" t="s">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="F158" t="s">
-        <v>284</v>
+        <v>360</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="18"/>
       <c r="B159" s="23"/>
       <c r="D159" s="7" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" s="18"/>
       <c r="B160" s="18"/>
       <c r="D160" s="7" t="s">
-        <v>286</v>
+        <v>362</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="18"/>
       <c r="B161" s="18"/>
       <c r="C161" s="1" t="s">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>288</v>
+        <v>364</v>
       </c>
       <c r="E161" t="s">
-        <v>289</v>
+        <v>365</v>
       </c>
       <c r="F161" t="s">
-        <v>290</v>
+        <v>366</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="18"/>
       <c r="B162" s="18"/>
       <c r="D162" s="7" t="s">
-        <v>291</v>
+        <v>367</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="18"/>
       <c r="B163" s="18"/>
       <c r="D163" s="7" t="s">
-        <v>292</v>
+        <v>368</v>
+      </c>
+      <c r="E163" t="s">
+        <v>413</v>
       </c>
       <c r="F163" t="s">
-        <v>293</v>
+        <v>369</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" s="18"/>
       <c r="B164" s="18"/>
       <c r="D164" s="7" t="s">
-        <v>294</v>
+        <v>370</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="18"/>
       <c r="B165" s="18"/>
       <c r="D165" s="7" t="s">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="E165" t="s">
-        <v>296</v>
+        <v>372</v>
       </c>
       <c r="F165" t="s">
-        <v>297</v>
+        <v>373</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" s="18"/>
       <c r="B166" s="18"/>
       <c r="D166" s="7" t="s">
-        <v>298</v>
+        <v>374</v>
       </c>
       <c r="E166" t="s">
-        <v>299</v>
+        <v>375</v>
       </c>
       <c r="F166" t="s">
-        <v>300</v>
+        <v>376</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" s="18"/>
       <c r="B167" s="18"/>
       <c r="C167" s="1" t="s">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>302</v>
+        <v>378</v>
       </c>
       <c r="E167" t="s">
-        <v>326</v>
+        <v>379</v>
       </c>
       <c r="F167" t="s">
-        <v>303</v>
+        <v>380</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="18"/>
       <c r="B168" s="18"/>
       <c r="D168" s="7" t="s">
-        <v>304</v>
+        <v>381</v>
       </c>
       <c r="F168" t="s">
-        <v>305</v>
+        <v>382</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="18"/>
       <c r="B169" s="18"/>
       <c r="D169" s="7" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="F169" t="s">
-        <v>307</v>
+        <v>384</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" s="18"/>
       <c r="B170" s="18"/>
       <c r="D170" s="7" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" s="18"/>
       <c r="B171" s="18"/>
       <c r="D171" s="7" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="E171" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="F171" t="s">
-        <v>310</v>
+        <v>388</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" s="18"/>
       <c r="B172" s="18"/>
       <c r="D172" s="7" t="s">
-        <v>311</v>
+        <v>389</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="18"/>
       <c r="B173" s="18"/>
       <c r="D173" s="7" t="s">
-        <v>312</v>
+        <v>390</v>
       </c>
       <c r="E173" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="F173" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="18"/>
       <c r="B174" s="18"/>
       <c r="D174" s="7" t="s">
-        <v>313</v>
+        <v>393</v>
       </c>
       <c r="E174" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="F174" t="s">
-        <v>314</v>
+        <v>395</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="18"/>
       <c r="B175" s="18"/>
       <c r="D175" s="7" t="s">
-        <v>315</v>
+        <v>396</v>
       </c>
       <c r="E175" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="F175" t="s">
-        <v>316</v>
+        <v>398</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="18"/>
       <c r="B176" s="18"/>
       <c r="C176" s="1" t="s">
-        <v>317</v>
+        <v>399</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>318</v>
+        <v>400</v>
       </c>
       <c r="E176" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F176" t="s">
-        <v>319</v>
+        <v>402</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="18"/>
       <c r="B177" s="18"/>
       <c r="D177" s="7" t="s">
-        <v>320</v>
+        <v>403</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="18"/>
       <c r="B178" s="18"/>
       <c r="D178" s="7" t="s">
-        <v>321</v>
+        <v>404</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="18"/>
       <c r="B179" s="18"/>
       <c r="D179" s="7" t="s">
-        <v>322</v>
+        <v>405</v>
+      </c>
+      <c r="F179" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="18"/>
       <c r="B180" s="18"/>
       <c r="D180" s="7" t="s">
-        <v>323</v>
+        <v>407</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="18"/>
       <c r="B181" s="18"/>
       <c r="D181" s="7" t="s">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="E181" t="s">
-        <v>343</v>
+        <v>409</v>
       </c>
       <c r="F181" t="s">
-        <v>344</v>
+        <v>410</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
@@ -3845,7 +3867,7 @@
       <c r="B182" s="19"/>
       <c r="C182" s="9"/>
       <c r="D182" s="10" t="s">
-        <v>325</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/Settlements of Albany.xlsx
+++ b/Settlements of Albany.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a38c727b2e27c7e/Documents/Creative Writing/Tabletop/Albany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{225F5B25-432C-4CAA-8003-08A2104D04C6}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE7F07C-2DE0-4039-A7F3-3A422B707CD2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="425">
   <si>
     <t>Old Kingdom</t>
   </si>
@@ -62,9 +62,6 @@
     <t>PICTONY</t>
   </si>
   <si>
-    <t>LAIRD CHIEF OF LOTHBURN* *The Pictish Clans in practice do not recognise the supremacy of Ducal tites, and the Laird Chief is a ceremonial title from The Old Kingdom</t>
-  </si>
-  <si>
     <t>LOTHBURN</t>
   </si>
   <si>
@@ -1305,6 +1302,18 @@
   </si>
   <si>
     <t>azure, a stag rampant argent</t>
+  </si>
+  <si>
+    <t>LAIRD CHIEF OF LOTHBURN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *The Pictish Clans in practice do not recognise the supremacy of Ducal tites, and the Laird Chief is a ceremonial title from The Old Kingdom</t>
+  </si>
+  <si>
+    <t>Duke</t>
+  </si>
+  <si>
+    <t>Ducal Arms</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1346,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1378,6 +1387,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6D6D"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1473,7 +1488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1503,6 +1518,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1893,19 +1921,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="120" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="133.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="1025" width="11.5703125"/>
+    <col min="2" max="2" width="94" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="120" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="133.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="1027" width="11.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1913,2008 +1942,2377 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>419</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="6"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="6"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="F4" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="20"/>
-      <c r="D6" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="F6" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="F7" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="F8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>20</v>
       </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="F9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="F10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="H10" t="s">
         <v>26</v>
       </c>
-      <c r="F10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="F11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
         <v>32</v>
       </c>
-      <c r="F12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="D13" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="F13" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="F14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
         <v>35</v>
       </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="D15" s="7" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="F15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" t="s">
         <v>37</v>
       </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="F16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
         <v>39</v>
       </c>
-      <c r="E16" t="s">
+      <c r="H16" t="s">
         <v>40</v>
       </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="F17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
         <v>42</v>
       </c>
-      <c r="E17" t="s">
+      <c r="H17" t="s">
         <v>43</v>
       </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="G18" t="s">
         <v>46</v>
       </c>
-      <c r="E18" t="s">
+      <c r="H18" t="s">
         <v>47</v>
       </c>
-      <c r="F18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
-      <c r="D19" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="F19" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="D20" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="F20" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="D21" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="F21" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
-      <c r="D22" s="7" t="s">
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="F22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
         <v>52</v>
       </c>
-      <c r="E22" t="s">
+      <c r="H22" t="s">
         <v>53</v>
       </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
-      <c r="D23" s="7" t="s">
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="F23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" t="s">
         <v>55</v>
       </c>
-      <c r="E23" t="s">
+      <c r="H23" t="s">
         <v>56</v>
       </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
-      <c r="D24" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="F24" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="G25" t="s">
         <v>60</v>
       </c>
-      <c r="E25" t="s">
+      <c r="H25" t="s">
         <v>61</v>
       </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="D26" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="F26" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="D27" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="F27" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
-      <c r="D28" s="7" t="s">
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="F28" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" t="s">
         <v>65</v>
       </c>
-      <c r="E28" t="s">
+      <c r="H28" t="s">
         <v>66</v>
       </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="G29" t="s">
         <v>69</v>
       </c>
-      <c r="E29" t="s">
+      <c r="H29" t="s">
         <v>70</v>
       </c>
-      <c r="F29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="F30" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" t="s">
         <v>72</v>
       </c>
-      <c r="F30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
-      <c r="D31" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="F31" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
-      <c r="D32" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="F32" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
-      <c r="D33" s="7" t="s">
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="F33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" t="s">
         <v>76</v>
       </c>
-      <c r="E33" t="s">
+      <c r="H33" t="s">
         <v>77</v>
       </c>
-      <c r="F33" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="H34" t="s">
         <v>80</v>
       </c>
-      <c r="F34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
-      <c r="D35" s="7" t="s">
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="F35" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" t="s">
         <v>82</v>
       </c>
-      <c r="E35" t="s">
+      <c r="H35" t="s">
         <v>83</v>
       </c>
-      <c r="F35" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
-      <c r="D36" s="7" t="s">
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="F36" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36" t="s">
         <v>85</v>
       </c>
-      <c r="E36" t="s">
+      <c r="H36" t="s">
         <v>86</v>
       </c>
-      <c r="F36" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="G37" t="s">
         <v>89</v>
       </c>
-      <c r="E37" t="s">
+      <c r="H37" t="s">
         <v>90</v>
       </c>
-      <c r="F37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
-      <c r="D38" s="7" t="s">
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="F38" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G38" t="s">
         <v>92</v>
       </c>
-      <c r="E38" t="s">
+      <c r="H38" t="s">
         <v>93</v>
       </c>
-      <c r="F38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
-      <c r="D39" s="7" t="s">
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="F39" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" t="s">
         <v>95</v>
       </c>
-      <c r="E39" t="s">
+      <c r="H39" t="s">
         <v>96</v>
       </c>
-      <c r="F39" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10" t="s">
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
+      <c r="B41" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="C41" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="F41" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="H41" t="s">
         <v>102</v>
       </c>
-      <c r="F41" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="39"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="F42" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="7" t="s">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="12"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="F43" s="7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
-      <c r="D44" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="F44" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
-      <c r="D45" s="7" t="s">
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="F45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G45" t="s">
         <v>108</v>
       </c>
-      <c r="E45" t="s">
+      <c r="H45" t="s">
         <v>109</v>
       </c>
-      <c r="F45" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
-      <c r="D46" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="F46" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
-      <c r="D47" s="7" t="s">
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="F47" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G47" t="s">
         <v>112</v>
       </c>
-      <c r="E47" t="s">
+      <c r="H47" t="s">
         <v>113</v>
       </c>
-      <c r="F47" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="G48" t="s">
         <v>116</v>
       </c>
-      <c r="E48" t="s">
+      <c r="H48" t="s">
         <v>117</v>
       </c>
-      <c r="F48" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
-      <c r="D49" s="7" t="s">
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="F49" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G49" t="s">
         <v>119</v>
       </c>
-      <c r="E49" t="s">
+      <c r="H49" t="s">
         <v>120</v>
       </c>
-      <c r="F49" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
-      <c r="D50" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="F50" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
-      <c r="D51" s="7" t="s">
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="F51" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G51" t="s">
         <v>123</v>
       </c>
-      <c r="E51" t="s">
+      <c r="H51" t="s">
         <v>124</v>
       </c>
-      <c r="F51" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
-      <c r="D52" s="7" t="s">
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="F52" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G52" t="s">
         <v>126</v>
       </c>
-      <c r="E52" t="s">
+      <c r="H52" t="s">
         <v>127</v>
       </c>
-      <c r="F52" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
-      <c r="D53" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="F53" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
-      <c r="D54" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="F54" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
-      <c r="D55" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="F55" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
-      <c r="D56" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="F56" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
-      <c r="D57" s="7" t="s">
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="F57" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G57" t="s">
         <v>133</v>
       </c>
-      <c r="E57" t="s">
+      <c r="H57" t="s">
         <v>134</v>
       </c>
-      <c r="F57" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
-      <c r="D58" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="F58" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="G59" t="s">
         <v>138</v>
       </c>
-      <c r="E59" t="s">
+      <c r="H59" t="s">
         <v>139</v>
       </c>
-      <c r="F59" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
-      <c r="D60" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="F60" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
-      <c r="D61" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="F61" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
-      <c r="D62" s="7" t="s">
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="F62" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G62" t="s">
         <v>143</v>
       </c>
-      <c r="E62" t="s">
+      <c r="H62" t="s">
         <v>144</v>
       </c>
-      <c r="F62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
-      <c r="D63" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="F63" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F64" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="12"/>
       <c r="B65" s="14"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="12"/>
       <c r="B66" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="F66" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="G66" t="s">
         <v>152</v>
       </c>
-      <c r="E66" t="s">
+      <c r="H66" t="s">
         <v>153</v>
       </c>
-      <c r="F66" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="12"/>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="39"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="F67" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="G67" t="s">
         <v>156</v>
       </c>
-      <c r="E67" t="s">
+      <c r="H67" t="s">
         <v>157</v>
       </c>
-      <c r="F67" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="12"/>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="39"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="F68" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
-      <c r="D69" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="F69" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
-      <c r="D70" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="F70" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
-      <c r="D71" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F71" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="F71" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H71" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
-      <c r="D72" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="F72" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
+      <c r="E73" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="G73" t="s">
         <v>166</v>
       </c>
-      <c r="E73" t="s">
+      <c r="H73" t="s">
         <v>167</v>
       </c>
-      <c r="F73" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
-      <c r="D74" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
+      <c r="F74" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
-      <c r="D75" s="7" t="s">
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
+      <c r="F75" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G75" t="s">
         <v>170</v>
       </c>
-      <c r="E75" t="s">
+      <c r="H75" t="s">
         <v>171</v>
       </c>
-      <c r="F75" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
-      <c r="D76" s="7" t="s">
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="F76" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G76" t="s">
         <v>173</v>
       </c>
-      <c r="E76" t="s">
+      <c r="H76" t="s">
         <v>174</v>
       </c>
-      <c r="F76" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
-      <c r="D77" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="29"/>
+      <c r="D77" s="29"/>
+      <c r="F77" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
-      <c r="D78" s="7" t="s">
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
+      <c r="F78" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G78" t="s">
         <v>177</v>
       </c>
-      <c r="E78" t="s">
+      <c r="H78" t="s">
         <v>178</v>
       </c>
-      <c r="F78" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
-      <c r="D79" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C79" s="29"/>
+      <c r="D79" s="29"/>
+      <c r="F79" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
-      <c r="D80" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C80" s="29"/>
+      <c r="D80" s="29"/>
+      <c r="F80" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
-      <c r="D81" s="7" t="s">
+      <c r="C81" s="29"/>
+      <c r="D81" s="29"/>
+      <c r="F81" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G81" t="s">
         <v>182</v>
       </c>
-      <c r="E81" t="s">
+      <c r="H81" t="s">
         <v>183</v>
       </c>
-      <c r="F81" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
-      <c r="D82" s="7" t="s">
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
+      <c r="F82" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G82" t="s">
         <v>185</v>
       </c>
-      <c r="E82" t="s">
+      <c r="H82" t="s">
         <v>186</v>
       </c>
-      <c r="F82" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
-      <c r="D83" s="7" t="s">
+      <c r="C83" s="29"/>
+      <c r="D83" s="29"/>
+      <c r="F83" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G83" t="s">
         <v>188</v>
       </c>
-      <c r="E83" t="s">
+      <c r="H83" t="s">
         <v>189</v>
       </c>
-      <c r="F83" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
-      <c r="D84" s="7" t="s">
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
+      <c r="F84" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G84" t="s">
         <v>191</v>
       </c>
-      <c r="E84" t="s">
-        <v>192</v>
-      </c>
-      <c r="F84" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H84" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="29"/>
+      <c r="D85" s="29"/>
+      <c r="E85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="G85" t="s">
         <v>194</v>
       </c>
-      <c r="E85" t="s">
+      <c r="H85" t="s">
         <v>195</v>
       </c>
-      <c r="F85" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
-      <c r="D86" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C86" s="29"/>
+      <c r="D86" s="29"/>
+      <c r="F86" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="29"/>
+      <c r="D87" s="29"/>
+      <c r="E87" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="G87" t="s">
         <v>199</v>
       </c>
-      <c r="E87" t="s">
+      <c r="H87" t="s">
         <v>200</v>
       </c>
-      <c r="F87" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
-      <c r="D88" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C88" s="29"/>
+      <c r="D88" s="29"/>
+      <c r="F88" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
-      <c r="D89" s="7" t="s">
+      <c r="C89" s="29"/>
+      <c r="D89" s="29"/>
+      <c r="F89" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="G89" t="s">
         <v>203</v>
       </c>
-      <c r="E89" t="s">
+      <c r="H89" t="s">
         <v>204</v>
       </c>
-      <c r="F89" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
-      <c r="D90" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C90" s="29"/>
+      <c r="D90" s="29"/>
+      <c r="F90" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
-      <c r="D91" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C91" s="29"/>
+      <c r="D91" s="29"/>
+      <c r="F91" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
-      <c r="D92" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C92" s="29"/>
+      <c r="D92" s="29"/>
+      <c r="F92" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
-      <c r="D93" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C93" s="29"/>
+      <c r="D93" s="29"/>
+      <c r="F93" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
-      <c r="D94" s="7" t="s">
+      <c r="C94" s="29"/>
+      <c r="D94" s="29"/>
+      <c r="F94" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G94" t="s">
         <v>210</v>
       </c>
-      <c r="E94" t="s">
-        <v>211</v>
-      </c>
-      <c r="F94" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H94" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
-      <c r="D95" s="7" t="s">
+      <c r="C95" s="29"/>
+      <c r="D95" s="29"/>
+      <c r="F95" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G95" t="s">
         <v>212</v>
       </c>
-      <c r="E95" t="s">
+      <c r="H95" t="s">
         <v>213</v>
       </c>
-      <c r="F95" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
-      <c r="D96" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="29"/>
+      <c r="D96" s="29"/>
+      <c r="F96" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="29"/>
+      <c r="D97" s="29"/>
+      <c r="E97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F97" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="G97" t="s">
         <v>217</v>
       </c>
-      <c r="E97" t="s">
+      <c r="H97" t="s">
         <v>218</v>
       </c>
-      <c r="F97" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="14"/>
       <c r="B98" s="14"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="10" t="s">
+      <c r="C98" s="31"/>
+      <c r="D98" s="31"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G98" t="s">
+        <v>407</v>
+      </c>
+      <c r="H98" t="s">
         <v>220</v>
       </c>
-      <c r="E98" t="s">
-        <v>408</v>
-      </c>
-      <c r="F98" t="s">
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="15" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="15" t="s">
+      <c r="B99" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="C99" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="F99" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G99" t="s">
         <v>224</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="H99" t="s">
         <v>225</v>
       </c>
-      <c r="F99" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="16"/>
-      <c r="B100" s="16" t="s">
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="F100" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D100" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="16"/>
-      <c r="B101" s="16" t="s">
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="F101" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D101" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="16"/>
       <c r="B102" s="16"/>
-      <c r="D102" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C102" s="32"/>
+      <c r="D102" s="32"/>
+      <c r="F102" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="16"/>
       <c r="B103" s="16"/>
-      <c r="D103" s="7" t="s">
+      <c r="C103" s="32"/>
+      <c r="D103" s="32"/>
+      <c r="F103" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G103" t="s">
         <v>232</v>
       </c>
-      <c r="E103" t="s">
+      <c r="H103" t="s">
         <v>233</v>
       </c>
-      <c r="F103" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="16"/>
       <c r="B104" s="16"/>
-      <c r="D104" s="7" t="s">
+      <c r="C104" s="32"/>
+      <c r="D104" s="32"/>
+      <c r="F104" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="G104" t="s">
         <v>235</v>
       </c>
-      <c r="E104" t="s">
+      <c r="H104" t="s">
         <v>236</v>
       </c>
-      <c r="F104" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="16"/>
       <c r="B105" s="16"/>
-      <c r="D105" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C105" s="32"/>
+      <c r="D105" s="32"/>
+      <c r="F105" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="32"/>
+      <c r="D106" s="32"/>
+      <c r="E106" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G106" t="s">
         <v>239</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E106" t="s">
-        <v>240</v>
-      </c>
-      <c r="F106" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H106" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
-      <c r="D107" s="7" t="s">
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
+      <c r="F107" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G107" t="s">
         <v>241</v>
       </c>
-      <c r="E107" t="s">
+      <c r="H107" t="s">
         <v>242</v>
       </c>
-      <c r="F107" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
-      <c r="D108" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="32"/>
+      <c r="D108" s="32"/>
+      <c r="F108" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
-      <c r="D109" s="7" t="s">
+      <c r="C109" s="32"/>
+      <c r="D109" s="32"/>
+      <c r="F109" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G109" t="s">
         <v>245</v>
       </c>
-      <c r="E109" t="s">
+      <c r="H109" t="s">
         <v>246</v>
       </c>
-      <c r="F109" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
-      <c r="D110" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C110" s="32"/>
+      <c r="D110" s="32"/>
+      <c r="F110" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
-      <c r="D111" s="7" t="s">
+      <c r="C111" s="32"/>
+      <c r="D111" s="32"/>
+      <c r="F111" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G111" t="s">
         <v>249</v>
       </c>
-      <c r="E111" t="s">
+      <c r="H111" t="s">
         <v>250</v>
       </c>
-      <c r="F111" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
-      <c r="D112" s="7" t="s">
+      <c r="C112" s="32"/>
+      <c r="D112" s="32"/>
+      <c r="F112" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G112" t="s">
         <v>252</v>
       </c>
-      <c r="E112" t="s">
+      <c r="H112" t="s">
         <v>253</v>
       </c>
-      <c r="F112" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="16"/>
       <c r="B113" s="16"/>
-      <c r="D113" s="7" t="s">
+      <c r="C113" s="32"/>
+      <c r="D113" s="32"/>
+      <c r="F113" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G113" t="s">
         <v>255</v>
       </c>
-      <c r="E113" t="s">
+      <c r="H113" t="s">
         <v>256</v>
       </c>
-      <c r="F113" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="16"/>
       <c r="B114" s="16"/>
-      <c r="D114" s="7" t="s">
+      <c r="C114" s="32"/>
+      <c r="D114" s="32"/>
+      <c r="F114" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G114" t="s">
         <v>258</v>
       </c>
-      <c r="E114" t="s">
+      <c r="H114" t="s">
         <v>259</v>
       </c>
-      <c r="F114" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="16"/>
       <c r="B115" s="16"/>
-      <c r="D115" s="7" t="s">
+      <c r="C115" s="32"/>
+      <c r="D115" s="32"/>
+      <c r="F115" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G115" t="s">
         <v>261</v>
       </c>
-      <c r="E115" t="s">
+      <c r="H115" t="s">
         <v>262</v>
       </c>
-      <c r="F115" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="16"/>
       <c r="B116" s="16"/>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="32"/>
+      <c r="D116" s="32"/>
+      <c r="E116" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G116" t="s">
         <v>264</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="H116" t="s">
         <v>265</v>
       </c>
-      <c r="F116" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="16"/>
       <c r="B117" s="16"/>
-      <c r="D117" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C117" s="32"/>
+      <c r="D117" s="32"/>
+      <c r="F117" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="16"/>
       <c r="B118" s="16"/>
-      <c r="D118" s="7" t="s">
+      <c r="C118" s="32"/>
+      <c r="D118" s="32"/>
+      <c r="F118" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G118" t="s">
         <v>268</v>
       </c>
-      <c r="E118" t="s">
+      <c r="H118" t="s">
         <v>269</v>
       </c>
-      <c r="F118" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="16"/>
       <c r="B119" s="16"/>
-      <c r="D119" s="7" t="s">
+      <c r="C119" s="32"/>
+      <c r="D119" s="32"/>
+      <c r="F119" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="G119" t="s">
         <v>271</v>
       </c>
-      <c r="E119" t="s">
+      <c r="H119" t="s">
         <v>272</v>
       </c>
-      <c r="F119" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="16"/>
       <c r="B120" s="16"/>
-      <c r="D120" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C120" s="32"/>
+      <c r="D120" s="32"/>
+      <c r="F120" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="16"/>
       <c r="B121" s="16"/>
-      <c r="D121" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F121" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C121" s="32"/>
+      <c r="D121" s="32"/>
+      <c r="F121" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H121" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="16"/>
       <c r="B122" s="16"/>
-      <c r="D122" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C122" s="32"/>
+      <c r="D122" s="32"/>
+      <c r="F122" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="16"/>
       <c r="B123" s="16"/>
-      <c r="D123" s="7" t="s">
+      <c r="C123" s="32"/>
+      <c r="D123" s="32"/>
+      <c r="F123" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G123" t="s">
         <v>277</v>
       </c>
-      <c r="E123" t="s">
+      <c r="H123" t="s">
         <v>278</v>
       </c>
-      <c r="F123" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="16"/>
       <c r="B124" s="16"/>
-      <c r="D124" s="7" t="s">
+      <c r="C124" s="32"/>
+      <c r="D124" s="32"/>
+      <c r="F124" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G124" t="s">
         <v>280</v>
       </c>
-      <c r="E124" t="s">
+      <c r="H124" t="s">
         <v>281</v>
       </c>
-      <c r="F124" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="16"/>
       <c r="B125" s="16"/>
-      <c r="D125" s="7" t="s">
+      <c r="C125" s="32"/>
+      <c r="D125" s="32"/>
+      <c r="F125" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G125" t="s">
         <v>283</v>
       </c>
-      <c r="E125" t="s">
+      <c r="H125" t="s">
         <v>284</v>
       </c>
-      <c r="F125" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="16"/>
       <c r="B126" s="16"/>
-      <c r="D126" s="7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C126" s="32"/>
+      <c r="D126" s="32"/>
+      <c r="F126" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="16"/>
       <c r="B127" s="16"/>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="32"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G127" t="s">
         <v>287</v>
       </c>
-      <c r="D127" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="H127" t="s">
         <v>288</v>
       </c>
-      <c r="F127" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="17"/>
       <c r="B128" s="17"/>
-      <c r="C128" s="9"/>
-      <c r="D128" s="10" t="s">
+      <c r="C128" s="33"/>
+      <c r="D128" s="33"/>
+      <c r="E128" s="9"/>
+      <c r="F128" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="G128" t="s">
         <v>290</v>
       </c>
-      <c r="E128" t="s">
+      <c r="H128" t="s">
         <v>291</v>
       </c>
-      <c r="F128" t="s">
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A129" s="18" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" s="18" t="s">
+      <c r="B129" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="B129" s="24" t="s">
+      <c r="C129" s="34"/>
+      <c r="D129" s="34"/>
+      <c r="E129" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="F129" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G129" t="s">
         <v>295</v>
       </c>
-      <c r="D129" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="H129" t="s">
         <v>296</v>
       </c>
-      <c r="F129" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="18"/>
       <c r="B130" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="C130" s="35"/>
+      <c r="D130" s="35"/>
+      <c r="F130" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D130" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="18"/>
       <c r="B131" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="D131" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C131" s="35"/>
+      <c r="D131" s="35"/>
+      <c r="F131" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G131" t="s">
         <v>300</v>
       </c>
-      <c r="E131" t="s">
+      <c r="H131" t="s">
         <v>301</v>
       </c>
-      <c r="F131" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="18"/>
       <c r="B132" s="23"/>
-      <c r="D132" s="7" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="35"/>
+      <c r="D132" s="35"/>
+      <c r="F132" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="18"/>
       <c r="B133" s="23"/>
-      <c r="D133" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C133" s="35"/>
+      <c r="D133" s="35"/>
+      <c r="F133" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="18"/>
       <c r="B134" s="23"/>
-      <c r="D134" s="7" t="s">
+      <c r="C134" s="35"/>
+      <c r="D134" s="35"/>
+      <c r="F134" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G134" t="s">
         <v>305</v>
       </c>
-      <c r="E134" t="s">
+      <c r="H134" t="s">
         <v>306</v>
       </c>
-      <c r="F134" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="18"/>
       <c r="B135" s="23"/>
-      <c r="D135" s="7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C135" s="35"/>
+      <c r="D135" s="35"/>
+      <c r="F135" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="18"/>
       <c r="B136" s="23"/>
-      <c r="D136" s="7" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C136" s="35"/>
+      <c r="D136" s="35"/>
+      <c r="F136" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="18"/>
       <c r="B137" s="23"/>
-      <c r="D137" s="7" t="s">
+      <c r="C137" s="35"/>
+      <c r="D137" s="35"/>
+      <c r="F137" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G137" t="s">
         <v>310</v>
       </c>
-      <c r="E137" t="s">
+      <c r="H137" t="s">
         <v>311</v>
       </c>
-      <c r="F137" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="18"/>
       <c r="B138" s="23"/>
-      <c r="D138" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C138" s="35"/>
+      <c r="D138" s="35"/>
+      <c r="F138" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="18"/>
       <c r="B139" s="23"/>
-      <c r="D139" s="7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C139" s="35"/>
+      <c r="D139" s="35"/>
+      <c r="F139" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="18"/>
       <c r="B140" s="23"/>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="35"/>
+      <c r="D140" s="35"/>
+      <c r="E140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="G140" t="s">
         <v>315</v>
       </c>
-      <c r="D140" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E140" t="s">
+      <c r="H140" t="s">
         <v>316</v>
       </c>
-      <c r="F140" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="18"/>
       <c r="B141" s="23"/>
-      <c r="D141" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C141" s="35"/>
+      <c r="D141" s="35"/>
+      <c r="F141" s="7" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="18"/>
       <c r="B142" s="23"/>
-      <c r="D142" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C142" s="35"/>
+      <c r="D142" s="35"/>
+      <c r="F142" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="18"/>
       <c r="B143" s="23"/>
-      <c r="D143" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C143" s="35"/>
+      <c r="D143" s="35"/>
+      <c r="F143" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="18"/>
       <c r="B144" s="23"/>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="35"/>
+      <c r="D144" s="35"/>
+      <c r="E144" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="G144" t="s">
         <v>322</v>
       </c>
-      <c r="E144" t="s">
+      <c r="H144" t="s">
         <v>323</v>
       </c>
-      <c r="F144" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="18"/>
       <c r="B145" s="23"/>
-      <c r="D145" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C145" s="35"/>
+      <c r="D145" s="35"/>
+      <c r="F145" s="7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="18"/>
       <c r="B146" s="23"/>
-      <c r="D146" s="7" t="s">
+      <c r="C146" s="35"/>
+      <c r="D146" s="35"/>
+      <c r="F146" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G146" t="s">
         <v>326</v>
       </c>
-      <c r="E146" t="s">
+      <c r="H146" t="s">
         <v>327</v>
       </c>
-      <c r="F146" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="18"/>
       <c r="B147" s="23"/>
-      <c r="D147" s="7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C147" s="35"/>
+      <c r="D147" s="35"/>
+      <c r="F147" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="18"/>
       <c r="B148" s="23"/>
-      <c r="D148" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C148" s="35"/>
+      <c r="D148" s="35"/>
+      <c r="F148" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="18"/>
       <c r="B149" s="23"/>
-      <c r="C149" s="1" t="s">
+      <c r="C149" s="35"/>
+      <c r="D149" s="35"/>
+      <c r="E149" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F149" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="G149" t="s">
         <v>332</v>
       </c>
-      <c r="E149" t="s">
+      <c r="H149" t="s">
         <v>333</v>
       </c>
-      <c r="F149" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="18"/>
       <c r="B150" s="23"/>
-      <c r="D150" s="7" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C150" s="35"/>
+      <c r="D150" s="35"/>
+      <c r="F150" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="18"/>
       <c r="B151" s="23"/>
-      <c r="D151" s="7" t="s">
+      <c r="C151" s="35"/>
+      <c r="D151" s="35"/>
+      <c r="F151" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="G151" t="s">
         <v>336</v>
       </c>
-      <c r="E151" t="s">
+      <c r="H151" t="s">
         <v>337</v>
       </c>
-      <c r="F151" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="18"/>
       <c r="B152" s="25"/>
-      <c r="C152" s="9"/>
-      <c r="D152" s="10" t="s">
+      <c r="C152" s="36"/>
+      <c r="D152" s="36"/>
+      <c r="E152" s="9"/>
+      <c r="F152" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="G152" t="s">
         <v>339</v>
       </c>
-      <c r="E152" t="s">
+      <c r="H152" t="s">
         <v>340</v>
       </c>
-      <c r="F152" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="18"/>
       <c r="B153" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="C153" s="35"/>
+      <c r="D153" s="35"/>
+      <c r="E153" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="F153" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="D153" s="7" t="s">
+      <c r="G153" t="s">
         <v>344</v>
       </c>
-      <c r="E153" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="18"/>
       <c r="B154" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="C154" s="35"/>
+      <c r="D154" s="35"/>
+      <c r="F154" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="G154" t="s">
         <v>347</v>
       </c>
-      <c r="E154" t="s">
+      <c r="H154" t="s">
         <v>348</v>
       </c>
-      <c r="F154" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="18"/>
       <c r="B155" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="C155" s="35"/>
+      <c r="D155" s="35"/>
+      <c r="F155" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="G155" t="s">
         <v>351</v>
       </c>
-      <c r="E155" t="s">
+      <c r="H155" t="s">
         <v>352</v>
       </c>
-      <c r="F155" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="18"/>
       <c r="B156" s="23"/>
-      <c r="D156" s="7" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C156" s="35"/>
+      <c r="D156" s="35"/>
+      <c r="F156" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="18"/>
       <c r="B157" s="23"/>
-      <c r="D157" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C157" s="35"/>
+      <c r="D157" s="35"/>
+      <c r="F157" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="18"/>
       <c r="B158" s="23"/>
-      <c r="D158" s="7" t="s">
+      <c r="C158" s="35"/>
+      <c r="D158" s="35"/>
+      <c r="F158" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G158" t="s">
         <v>356</v>
       </c>
-      <c r="E158" t="s">
-        <v>357</v>
-      </c>
-      <c r="F158" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H158" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="18"/>
       <c r="B159" s="23"/>
-      <c r="D159" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C159" s="35"/>
+      <c r="D159" s="35"/>
+      <c r="F159" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="18"/>
       <c r="B160" s="18"/>
-      <c r="D160" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C160" s="37"/>
+      <c r="D160" s="37"/>
+      <c r="F160" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="18"/>
       <c r="B161" s="18"/>
-      <c r="C161" s="1" t="s">
+      <c r="C161" s="37"/>
+      <c r="D161" s="37"/>
+      <c r="E161" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F161" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="D161" s="7" t="s">
+      <c r="G161" t="s">
         <v>361</v>
       </c>
-      <c r="E161" t="s">
+      <c r="H161" t="s">
         <v>362</v>
       </c>
-      <c r="F161" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="18"/>
       <c r="B162" s="18"/>
-      <c r="D162" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F162" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="37"/>
+      <c r="D162" s="37"/>
+      <c r="F162" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="H162" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="18"/>
       <c r="B163" s="18"/>
-      <c r="D163" s="7" t="s">
+      <c r="C163" s="37"/>
+      <c r="D163" s="37"/>
+      <c r="F163" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="G163" t="s">
+        <v>408</v>
+      </c>
+      <c r="H163" t="s">
         <v>365</v>
       </c>
-      <c r="E163" t="s">
-        <v>409</v>
-      </c>
-      <c r="F163" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="18"/>
       <c r="B164" s="18"/>
-      <c r="D164" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C164" s="37"/>
+      <c r="D164" s="37"/>
+      <c r="F164" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="18"/>
       <c r="B165" s="18"/>
-      <c r="D165" s="7" t="s">
+      <c r="C165" s="37"/>
+      <c r="D165" s="37"/>
+      <c r="F165" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G165" t="s">
         <v>368</v>
       </c>
-      <c r="E165" t="s">
+      <c r="H165" t="s">
         <v>369</v>
       </c>
-      <c r="F165" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="18"/>
       <c r="B166" s="18"/>
-      <c r="D166" s="7" t="s">
+      <c r="C166" s="37"/>
+      <c r="D166" s="37"/>
+      <c r="F166" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G166" t="s">
         <v>371</v>
       </c>
-      <c r="E166" t="s">
+      <c r="H166" t="s">
         <v>372</v>
       </c>
-      <c r="F166" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="18"/>
       <c r="B167" s="18"/>
-      <c r="C167" s="1" t="s">
+      <c r="C167" s="37"/>
+      <c r="D167" s="37"/>
+      <c r="E167" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F167" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="D167" s="7" t="s">
+      <c r="G167" t="s">
         <v>375</v>
       </c>
-      <c r="E167" t="s">
+      <c r="H167" t="s">
         <v>376</v>
       </c>
-      <c r="F167" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="18"/>
       <c r="B168" s="18"/>
-      <c r="D168" s="7" t="s">
+      <c r="C168" s="37"/>
+      <c r="D168" s="37"/>
+      <c r="F168" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="H168" t="s">
         <v>378</v>
       </c>
-      <c r="F168" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="18"/>
       <c r="B169" s="18"/>
-      <c r="D169" s="7" t="s">
+      <c r="C169" s="37"/>
+      <c r="D169" s="37"/>
+      <c r="F169" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="H169" t="s">
         <v>380</v>
       </c>
-      <c r="F169" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="18"/>
       <c r="B170" s="18"/>
-      <c r="D170" s="7" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C170" s="37"/>
+      <c r="D170" s="37"/>
+      <c r="F170" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="18"/>
       <c r="B171" s="18"/>
-      <c r="D171" s="7" t="s">
+      <c r="C171" s="37"/>
+      <c r="D171" s="37"/>
+      <c r="F171" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="G171" t="s">
         <v>383</v>
       </c>
-      <c r="E171" t="s">
+      <c r="H171" t="s">
         <v>384</v>
       </c>
-      <c r="F171" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="18"/>
       <c r="B172" s="18"/>
-      <c r="D172" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C172" s="37"/>
+      <c r="D172" s="37"/>
+      <c r="F172" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="18"/>
       <c r="B173" s="18"/>
-      <c r="D173" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E173" t="s">
-        <v>391</v>
-      </c>
-      <c r="F173" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C173" s="37"/>
+      <c r="D173" s="37"/>
+      <c r="F173" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G173" t="s">
+        <v>390</v>
+      </c>
+      <c r="H173" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A174" s="18"/>
       <c r="B174" s="18"/>
-      <c r="D174" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="E174" t="s">
-        <v>388</v>
-      </c>
-      <c r="F174" s="26" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C174" s="37"/>
+      <c r="D174" s="37"/>
+      <c r="F174" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="G174" t="s">
+        <v>387</v>
+      </c>
+      <c r="H174" s="26" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="18"/>
       <c r="B175" s="18"/>
-      <c r="D175" s="7" t="s">
+      <c r="C175" s="37"/>
+      <c r="D175" s="37"/>
+      <c r="F175" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="G175" t="s">
         <v>392</v>
       </c>
-      <c r="E175" t="s">
+      <c r="H175" t="s">
         <v>393</v>
       </c>
-      <c r="F175" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="18"/>
       <c r="B176" s="18"/>
-      <c r="C176" s="1" t="s">
+      <c r="C176" s="37"/>
+      <c r="D176" s="37"/>
+      <c r="E176" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F176" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="D176" s="7" t="s">
+      <c r="G176" t="s">
         <v>396</v>
       </c>
-      <c r="E176" t="s">
+      <c r="H176" t="s">
         <v>397</v>
       </c>
-      <c r="F176" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="18"/>
       <c r="B177" s="18"/>
-      <c r="D177" s="7" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C177" s="37"/>
+      <c r="D177" s="37"/>
+      <c r="F177" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="18"/>
       <c r="B178" s="18"/>
-      <c r="D178" s="7" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C178" s="37"/>
+      <c r="D178" s="37"/>
+      <c r="F178" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="18"/>
       <c r="B179" s="18"/>
-      <c r="D179" s="7" t="s">
+      <c r="C179" s="37"/>
+      <c r="D179" s="37"/>
+      <c r="F179" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="H179" t="s">
         <v>401</v>
       </c>
-      <c r="F179" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="18"/>
       <c r="B180" s="18"/>
-      <c r="D180" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="E180" t="s">
-        <v>415</v>
-      </c>
-      <c r="F180" t="s">
+      <c r="C180" s="37"/>
+      <c r="D180" s="37"/>
+      <c r="F180" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="G180" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H180" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="18"/>
       <c r="B181" s="18"/>
-      <c r="D181" s="7" t="s">
+      <c r="C181" s="37"/>
+      <c r="D181" s="37"/>
+      <c r="F181" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="G181" t="s">
         <v>404</v>
       </c>
-      <c r="E181" t="s">
+      <c r="H181" t="s">
         <v>405</v>
       </c>
-      <c r="F181" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="19"/>
       <c r="B182" s="19"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="10" t="s">
-        <v>407</v>
+      <c r="C182" s="38"/>
+      <c r="D182" s="38"/>
+      <c r="E182" s="9"/>
+      <c r="F182" s="10" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/Settlements of Albany.xlsx
+++ b/Settlements of Albany.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a38c727b2e27c7e/Documents/Creative Writing/Tabletop/Albany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="347" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE7F07C-2DE0-4039-A7F3-3A422B707CD2}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B017CE1-6ECA-4843-83DD-08851DEC9D9A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -560,9 +560,6 @@
     <t>Treffynnon</t>
   </si>
   <si>
-    <t>Sir Dafydd ap Terwyn</t>
-  </si>
-  <si>
     <t>azure, chevron engrailed or, two doves argent legged or armed gules beaked gules above an oak tree vert</t>
   </si>
   <si>
@@ -1314,6 +1311,9 @@
   </si>
   <si>
     <t>Ducal Arms</t>
+  </si>
+  <si>
+    <t>Sir Tomos ap Terwyn</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1346,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1392,6 +1392,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF6D6D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2B2B2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1488,7 +1500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1525,12 +1537,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1605,6 +1616,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFB2B2B2"/>
       <color rgb="FFFF6D6D"/>
       <color rgb="FF729FCF"/>
     </mruColors>
@@ -1925,8 +1937,9 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="94" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="120" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="94" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.140625" bestFit="1" customWidth="1"/>
@@ -1942,10 +1955,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -1965,13 +1978,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1980,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -2355,7 +2368,7 @@
         <v>73</v>
       </c>
       <c r="H31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -2516,7 +2529,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="39"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="29"/>
       <c r="D42" s="29"/>
       <c r="F42" s="7" t="s">
@@ -2525,7 +2538,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>
-      <c r="B43" s="39"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
       <c r="F43" s="7" t="s">
@@ -2820,7 +2833,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="12"/>
-      <c r="B67" s="39"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="29"/>
       <c r="D67" s="29"/>
       <c r="F67" s="7" t="s">
@@ -2835,7 +2848,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="12"/>
-      <c r="B68" s="39"/>
+      <c r="B68" s="36"/>
       <c r="C68" s="29"/>
       <c r="D68" s="29"/>
       <c r="F68" s="7" t="s">
@@ -2869,7 +2882,7 @@
         <v>162</v>
       </c>
       <c r="H71" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -2932,10 +2945,10 @@
         <v>172</v>
       </c>
       <c r="G76" t="s">
+        <v>424</v>
+      </c>
+      <c r="H76" t="s">
         <v>173</v>
-      </c>
-      <c r="H76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -2944,7 +2957,7 @@
       <c r="C77" s="29"/>
       <c r="D77" s="29"/>
       <c r="F77" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -2953,13 +2966,13 @@
       <c r="C78" s="29"/>
       <c r="D78" s="29"/>
       <c r="F78" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>176</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>177</v>
-      </c>
-      <c r="H78" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -2968,7 +2981,7 @@
       <c r="C79" s="29"/>
       <c r="D79" s="29"/>
       <c r="F79" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -2977,7 +2990,7 @@
       <c r="C80" s="29"/>
       <c r="D80" s="29"/>
       <c r="F80" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -2986,13 +2999,13 @@
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
       <c r="F81" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G81" t="s">
         <v>181</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>182</v>
-      </c>
-      <c r="H81" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -3001,13 +3014,13 @@
       <c r="C82" s="29"/>
       <c r="D82" s="29"/>
       <c r="F82" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G82" t="s">
         <v>184</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>185</v>
-      </c>
-      <c r="H82" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -3016,13 +3029,13 @@
       <c r="C83" s="29"/>
       <c r="D83" s="29"/>
       <c r="F83" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G83" t="s">
         <v>187</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>188</v>
-      </c>
-      <c r="H83" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -3031,13 +3044,13 @@
       <c r="C84" s="29"/>
       <c r="D84" s="29"/>
       <c r="F84" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G84" t="s">
         <v>190</v>
       </c>
-      <c r="G84" t="s">
-        <v>191</v>
-      </c>
       <c r="H84" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -3046,16 +3059,16 @@
       <c r="C85" s="29"/>
       <c r="D85" s="29"/>
       <c r="E85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="G85" t="s">
         <v>193</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>194</v>
-      </c>
-      <c r="H85" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -3064,7 +3077,7 @@
       <c r="C86" s="29"/>
       <c r="D86" s="29"/>
       <c r="F86" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -3073,16 +3086,16 @@
       <c r="C87" s="29"/>
       <c r="D87" s="29"/>
       <c r="E87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="G87" t="s">
         <v>198</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>199</v>
-      </c>
-      <c r="H87" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -3091,7 +3104,7 @@
       <c r="C88" s="29"/>
       <c r="D88" s="29"/>
       <c r="F88" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -3100,13 +3113,13 @@
       <c r="C89" s="29"/>
       <c r="D89" s="29"/>
       <c r="F89" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G89" t="s">
         <v>202</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>203</v>
-      </c>
-      <c r="H89" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -3115,7 +3128,7 @@
       <c r="C90" s="29"/>
       <c r="D90" s="29"/>
       <c r="F90" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -3124,7 +3137,7 @@
       <c r="C91" s="29"/>
       <c r="D91" s="29"/>
       <c r="F91" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -3133,7 +3146,7 @@
       <c r="C92" s="29"/>
       <c r="D92" s="29"/>
       <c r="F92" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -3142,7 +3155,7 @@
       <c r="C93" s="29"/>
       <c r="D93" s="29"/>
       <c r="F93" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -3151,13 +3164,13 @@
       <c r="C94" s="29"/>
       <c r="D94" s="29"/>
       <c r="F94" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G94" t="s">
         <v>209</v>
       </c>
-      <c r="G94" t="s">
-        <v>210</v>
-      </c>
       <c r="H94" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -3166,13 +3179,13 @@
       <c r="C95" s="29"/>
       <c r="D95" s="29"/>
       <c r="F95" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G95" t="s">
         <v>211</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>212</v>
-      </c>
-      <c r="H95" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -3181,7 +3194,7 @@
       <c r="C96" s="29"/>
       <c r="D96" s="29"/>
       <c r="F96" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -3190,16 +3203,16 @@
       <c r="C97" s="29"/>
       <c r="D97" s="29"/>
       <c r="E97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F97" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="G97" t="s">
         <v>216</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>217</v>
-      </c>
-      <c r="H97" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -3209,55 +3222,57 @@
       <c r="D98" s="31"/>
       <c r="E98" s="9"/>
       <c r="F98" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G98" t="s">
+        <v>406</v>
+      </c>
+      <c r="H98" t="s">
         <v>219</v>
-      </c>
-      <c r="G98" t="s">
-        <v>407</v>
-      </c>
-      <c r="H98" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="C99" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C99" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="E99" s="3" t="s">
+      <c r="F99" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G99" t="s">
         <v>223</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>224</v>
-      </c>
-      <c r="H99" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="16"/>
+      <c r="B100" s="37"/>
       <c r="C100" s="32"/>
       <c r="D100" s="32"/>
       <c r="F100" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="16"/>
+      <c r="B101" s="37"/>
       <c r="C101" s="32"/>
       <c r="D101" s="32"/>
       <c r="F101" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
@@ -3266,7 +3281,7 @@
       <c r="C102" s="32"/>
       <c r="D102" s="32"/>
       <c r="F102" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -3275,13 +3290,13 @@
       <c r="C103" s="32"/>
       <c r="D103" s="32"/>
       <c r="F103" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G103" t="s">
         <v>231</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>232</v>
-      </c>
-      <c r="H103" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -3290,13 +3305,13 @@
       <c r="C104" s="32"/>
       <c r="D104" s="32"/>
       <c r="F104" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G104" t="s">
         <v>234</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>235</v>
-      </c>
-      <c r="H104" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -3305,7 +3320,7 @@
       <c r="C105" s="32"/>
       <c r="D105" s="32"/>
       <c r="F105" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -3314,16 +3329,16 @@
       <c r="C106" s="32"/>
       <c r="D106" s="32"/>
       <c r="E106" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G106" t="s">
         <v>238</v>
       </c>
-      <c r="F106" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="G106" t="s">
-        <v>239</v>
-      </c>
       <c r="H106" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -3332,13 +3347,13 @@
       <c r="C107" s="32"/>
       <c r="D107" s="32"/>
       <c r="F107" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="G107" t="s">
         <v>240</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>241</v>
-      </c>
-      <c r="H107" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -3347,7 +3362,7 @@
       <c r="C108" s="32"/>
       <c r="D108" s="32"/>
       <c r="F108" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -3356,13 +3371,13 @@
       <c r="C109" s="32"/>
       <c r="D109" s="32"/>
       <c r="F109" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G109" t="s">
         <v>244</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>245</v>
-      </c>
-      <c r="H109" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -3371,7 +3386,7 @@
       <c r="C110" s="32"/>
       <c r="D110" s="32"/>
       <c r="F110" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -3380,13 +3395,13 @@
       <c r="C111" s="32"/>
       <c r="D111" s="32"/>
       <c r="F111" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G111" t="s">
         <v>248</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>249</v>
-      </c>
-      <c r="H111" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -3395,13 +3410,13 @@
       <c r="C112" s="32"/>
       <c r="D112" s="32"/>
       <c r="F112" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G112" t="s">
         <v>251</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>252</v>
-      </c>
-      <c r="H112" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -3410,13 +3425,13 @@
       <c r="C113" s="32"/>
       <c r="D113" s="32"/>
       <c r="F113" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G113" t="s">
         <v>254</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>255</v>
-      </c>
-      <c r="H113" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -3425,13 +3440,13 @@
       <c r="C114" s="32"/>
       <c r="D114" s="32"/>
       <c r="F114" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G114" t="s">
         <v>257</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>258</v>
-      </c>
-      <c r="H114" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -3440,13 +3455,13 @@
       <c r="C115" s="32"/>
       <c r="D115" s="32"/>
       <c r="F115" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G115" t="s">
         <v>260</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>261</v>
-      </c>
-      <c r="H115" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -3455,16 +3470,16 @@
       <c r="C116" s="32"/>
       <c r="D116" s="32"/>
       <c r="E116" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G116" t="s">
         <v>263</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>264</v>
-      </c>
-      <c r="H116" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -3473,7 +3488,7 @@
       <c r="C117" s="32"/>
       <c r="D117" s="32"/>
       <c r="F117" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -3482,13 +3497,13 @@
       <c r="C118" s="32"/>
       <c r="D118" s="32"/>
       <c r="F118" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="G118" t="s">
         <v>267</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>268</v>
-      </c>
-      <c r="H118" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -3497,13 +3512,13 @@
       <c r="C119" s="32"/>
       <c r="D119" s="32"/>
       <c r="F119" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G119" t="s">
         <v>270</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>271</v>
-      </c>
-      <c r="H119" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -3512,7 +3527,7 @@
       <c r="C120" s="32"/>
       <c r="D120" s="32"/>
       <c r="F120" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -3521,10 +3536,10 @@
       <c r="C121" s="32"/>
       <c r="D121" s="32"/>
       <c r="F121" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H121" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -3533,7 +3548,7 @@
       <c r="C122" s="32"/>
       <c r="D122" s="32"/>
       <c r="F122" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -3542,13 +3557,13 @@
       <c r="C123" s="32"/>
       <c r="D123" s="32"/>
       <c r="F123" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G123" t="s">
         <v>276</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>277</v>
-      </c>
-      <c r="H123" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -3557,13 +3572,13 @@
       <c r="C124" s="32"/>
       <c r="D124" s="32"/>
       <c r="F124" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="G124" t="s">
         <v>279</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>280</v>
-      </c>
-      <c r="H124" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -3572,13 +3587,13 @@
       <c r="C125" s="32"/>
       <c r="D125" s="32"/>
       <c r="F125" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G125" t="s">
         <v>282</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>283</v>
-      </c>
-      <c r="H125" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -3587,7 +3602,7 @@
       <c r="C126" s="32"/>
       <c r="D126" s="32"/>
       <c r="F126" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -3596,16 +3611,16 @@
       <c r="C127" s="32"/>
       <c r="D127" s="32"/>
       <c r="E127" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G127" t="s">
         <v>286</v>
       </c>
-      <c r="F127" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>287</v>
-      </c>
-      <c r="H127" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -3615,704 +3630,704 @@
       <c r="D128" s="33"/>
       <c r="E128" s="9"/>
       <c r="F128" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="G128" t="s">
         <v>289</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>290</v>
-      </c>
-      <c r="H128" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B129" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="B129" s="24" t="s">
+      <c r="C129" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="D129" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C129" s="34"/>
-      <c r="D129" s="34"/>
-      <c r="E129" s="3" t="s">
+      <c r="F129" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G129" t="s">
         <v>294</v>
       </c>
-      <c r="F129" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>295</v>
-      </c>
-      <c r="H129" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="18"/>
-      <c r="B130" s="23" t="s">
+      <c r="B130" s="38"/>
+      <c r="C130" s="34"/>
+      <c r="D130" s="34"/>
+      <c r="F130" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="C130" s="35"/>
-      <c r="D130" s="35"/>
-      <c r="F130" s="7" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="18"/>
-      <c r="B131" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="C131" s="35"/>
-      <c r="D131" s="35"/>
+      <c r="B131" s="38"/>
+      <c r="C131" s="34"/>
+      <c r="D131" s="34"/>
       <c r="F131" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G131" t="s">
         <v>299</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>300</v>
-      </c>
-      <c r="H131" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="18"/>
       <c r="B132" s="23"/>
-      <c r="C132" s="35"/>
-      <c r="D132" s="35"/>
+      <c r="C132" s="34"/>
+      <c r="D132" s="34"/>
       <c r="F132" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="18"/>
       <c r="B133" s="23"/>
-      <c r="C133" s="35"/>
-      <c r="D133" s="35"/>
+      <c r="C133" s="34"/>
+      <c r="D133" s="34"/>
       <c r="F133" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="18"/>
       <c r="B134" s="23"/>
-      <c r="C134" s="35"/>
-      <c r="D134" s="35"/>
+      <c r="C134" s="34"/>
+      <c r="D134" s="34"/>
       <c r="F134" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G134" t="s">
         <v>304</v>
       </c>
-      <c r="G134" t="s">
+      <c r="H134" t="s">
         <v>305</v>
-      </c>
-      <c r="H134" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="18"/>
       <c r="B135" s="23"/>
-      <c r="C135" s="35"/>
-      <c r="D135" s="35"/>
+      <c r="C135" s="34"/>
+      <c r="D135" s="34"/>
       <c r="F135" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="18"/>
       <c r="B136" s="23"/>
-      <c r="C136" s="35"/>
-      <c r="D136" s="35"/>
+      <c r="C136" s="34"/>
+      <c r="D136" s="34"/>
       <c r="F136" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="18"/>
       <c r="B137" s="23"/>
-      <c r="C137" s="35"/>
-      <c r="D137" s="35"/>
+      <c r="C137" s="34"/>
+      <c r="D137" s="34"/>
       <c r="F137" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G137" t="s">
         <v>309</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>310</v>
-      </c>
-      <c r="H137" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="18"/>
       <c r="B138" s="23"/>
-      <c r="C138" s="35"/>
-      <c r="D138" s="35"/>
+      <c r="C138" s="34"/>
+      <c r="D138" s="34"/>
       <c r="F138" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="18"/>
       <c r="B139" s="23"/>
-      <c r="C139" s="35"/>
-      <c r="D139" s="35"/>
+      <c r="C139" s="34"/>
+      <c r="D139" s="34"/>
       <c r="F139" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="18"/>
       <c r="B140" s="23"/>
-      <c r="C140" s="35"/>
-      <c r="D140" s="35"/>
+      <c r="C140" s="34"/>
+      <c r="D140" s="34"/>
       <c r="E140" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="G140" t="s">
         <v>314</v>
       </c>
-      <c r="F140" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>315</v>
-      </c>
-      <c r="H140" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="18"/>
       <c r="B141" s="23"/>
-      <c r="C141" s="35"/>
-      <c r="D141" s="35"/>
+      <c r="C141" s="34"/>
+      <c r="D141" s="34"/>
       <c r="F141" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="18"/>
       <c r="B142" s="23"/>
-      <c r="C142" s="35"/>
-      <c r="D142" s="35"/>
+      <c r="C142" s="34"/>
+      <c r="D142" s="34"/>
       <c r="F142" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="18"/>
       <c r="B143" s="23"/>
-      <c r="C143" s="35"/>
-      <c r="D143" s="35"/>
+      <c r="C143" s="34"/>
+      <c r="D143" s="34"/>
       <c r="F143" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="18"/>
       <c r="B144" s="23"/>
-      <c r="C144" s="35"/>
-      <c r="D144" s="35"/>
+      <c r="C144" s="34"/>
+      <c r="D144" s="34"/>
       <c r="E144" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="F144" s="7" t="s">
+      <c r="G144" t="s">
         <v>321</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>322</v>
-      </c>
-      <c r="H144" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="18"/>
       <c r="B145" s="23"/>
-      <c r="C145" s="35"/>
-      <c r="D145" s="35"/>
+      <c r="C145" s="34"/>
+      <c r="D145" s="34"/>
       <c r="F145" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="18"/>
       <c r="B146" s="23"/>
-      <c r="C146" s="35"/>
-      <c r="D146" s="35"/>
+      <c r="C146" s="34"/>
+      <c r="D146" s="34"/>
       <c r="F146" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G146" t="s">
         <v>325</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>326</v>
-      </c>
-      <c r="H146" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="18"/>
       <c r="B147" s="23"/>
-      <c r="C147" s="35"/>
-      <c r="D147" s="35"/>
+      <c r="C147" s="34"/>
+      <c r="D147" s="34"/>
       <c r="F147" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="18"/>
       <c r="B148" s="23"/>
-      <c r="C148" s="35"/>
-      <c r="D148" s="35"/>
+      <c r="C148" s="34"/>
+      <c r="D148" s="34"/>
       <c r="F148" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="18"/>
       <c r="B149" s="23"/>
-      <c r="C149" s="35"/>
-      <c r="D149" s="35"/>
+      <c r="C149" s="34"/>
+      <c r="D149" s="34"/>
       <c r="E149" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F149" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="F149" s="7" t="s">
+      <c r="G149" t="s">
         <v>331</v>
       </c>
-      <c r="G149" t="s">
+      <c r="H149" t="s">
         <v>332</v>
-      </c>
-      <c r="H149" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="18"/>
       <c r="B150" s="23"/>
-      <c r="C150" s="35"/>
-      <c r="D150" s="35"/>
+      <c r="C150" s="34"/>
+      <c r="D150" s="34"/>
       <c r="F150" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="18"/>
       <c r="B151" s="23"/>
-      <c r="C151" s="35"/>
-      <c r="D151" s="35"/>
+      <c r="C151" s="34"/>
+      <c r="D151" s="34"/>
       <c r="F151" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G151" t="s">
         <v>335</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="s">
         <v>336</v>
-      </c>
-      <c r="H151" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="18"/>
       <c r="B152" s="25"/>
-      <c r="C152" s="36"/>
-      <c r="D152" s="36"/>
+      <c r="C152" s="35"/>
+      <c r="D152" s="35"/>
       <c r="E152" s="9"/>
       <c r="F152" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="G152" t="s">
         <v>338</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" t="s">
         <v>339</v>
-      </c>
-      <c r="H152" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="18"/>
       <c r="B153" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="C153" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="D153" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C153" s="35"/>
-      <c r="D153" s="35"/>
-      <c r="E153" s="1" t="s">
+      <c r="F153" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F153" s="7" t="s">
+      <c r="G153" t="s">
         <v>343</v>
-      </c>
-      <c r="G153" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="18"/>
-      <c r="B154" s="23" t="s">
+      <c r="B154" s="38"/>
+      <c r="C154" s="34"/>
+      <c r="D154" s="34"/>
+      <c r="F154" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C154" s="35"/>
-      <c r="D154" s="35"/>
-      <c r="F154" s="7" t="s">
+      <c r="G154" t="s">
         <v>346</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" t="s">
         <v>347</v>
-      </c>
-      <c r="H154" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="18"/>
-      <c r="B155" s="23" t="s">
+      <c r="B155" s="38"/>
+      <c r="C155" s="34"/>
+      <c r="D155" s="34"/>
+      <c r="F155" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C155" s="35"/>
-      <c r="D155" s="35"/>
-      <c r="F155" s="7" t="s">
+      <c r="G155" t="s">
         <v>350</v>
       </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
         <v>351</v>
-      </c>
-      <c r="H155" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="18"/>
       <c r="B156" s="23"/>
-      <c r="C156" s="35"/>
-      <c r="D156" s="35"/>
+      <c r="C156" s="34"/>
+      <c r="D156" s="34"/>
       <c r="F156" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="18"/>
       <c r="B157" s="23"/>
-      <c r="C157" s="35"/>
-      <c r="D157" s="35"/>
+      <c r="C157" s="34"/>
+      <c r="D157" s="34"/>
       <c r="F157" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="18"/>
       <c r="B158" s="23"/>
-      <c r="C158" s="35"/>
-      <c r="D158" s="35"/>
+      <c r="C158" s="34"/>
+      <c r="D158" s="34"/>
       <c r="F158" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G158" t="s">
         <v>355</v>
       </c>
-      <c r="G158" t="s">
-        <v>356</v>
-      </c>
       <c r="H158" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="18"/>
       <c r="B159" s="23"/>
-      <c r="C159" s="35"/>
-      <c r="D159" s="35"/>
+      <c r="C159" s="34"/>
+      <c r="D159" s="34"/>
       <c r="F159" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="18"/>
-      <c r="B160" s="18"/>
-      <c r="C160" s="37"/>
-      <c r="D160" s="37"/>
+      <c r="B160" s="23"/>
+      <c r="C160" s="34"/>
+      <c r="D160" s="34"/>
       <c r="F160" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="18"/>
-      <c r="B161" s="18"/>
-      <c r="C161" s="37"/>
-      <c r="D161" s="37"/>
+      <c r="B161" s="23"/>
+      <c r="C161" s="34"/>
+      <c r="D161" s="34"/>
       <c r="E161" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F161" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="F161" s="7" t="s">
+      <c r="G161" t="s">
         <v>360</v>
       </c>
-      <c r="G161" t="s">
+      <c r="H161" t="s">
         <v>361</v>
-      </c>
-      <c r="H161" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="18"/>
-      <c r="B162" s="18"/>
-      <c r="C162" s="37"/>
-      <c r="D162" s="37"/>
+      <c r="B162" s="23"/>
+      <c r="C162" s="34"/>
+      <c r="D162" s="34"/>
       <c r="F162" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H162" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="18"/>
-      <c r="B163" s="18"/>
-      <c r="C163" s="37"/>
-      <c r="D163" s="37"/>
+      <c r="B163" s="23"/>
+      <c r="C163" s="34"/>
+      <c r="D163" s="34"/>
       <c r="F163" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="G163" t="s">
+        <v>407</v>
+      </c>
+      <c r="H163" t="s">
         <v>364</v>
-      </c>
-      <c r="G163" t="s">
-        <v>408</v>
-      </c>
-      <c r="H163" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="18"/>
-      <c r="B164" s="18"/>
-      <c r="C164" s="37"/>
-      <c r="D164" s="37"/>
+      <c r="B164" s="23"/>
+      <c r="C164" s="34"/>
+      <c r="D164" s="34"/>
       <c r="F164" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="18"/>
-      <c r="B165" s="18"/>
-      <c r="C165" s="37"/>
-      <c r="D165" s="37"/>
+      <c r="B165" s="23"/>
+      <c r="C165" s="34"/>
+      <c r="D165" s="34"/>
       <c r="F165" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G165" t="s">
         <v>367</v>
       </c>
-      <c r="G165" t="s">
+      <c r="H165" t="s">
         <v>368</v>
-      </c>
-      <c r="H165" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="18"/>
-      <c r="B166" s="18"/>
-      <c r="C166" s="37"/>
-      <c r="D166" s="37"/>
+      <c r="B166" s="23"/>
+      <c r="C166" s="34"/>
+      <c r="D166" s="34"/>
       <c r="F166" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="G166" t="s">
         <v>370</v>
       </c>
-      <c r="G166" t="s">
+      <c r="H166" t="s">
         <v>371</v>
-      </c>
-      <c r="H166" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="18"/>
-      <c r="B167" s="18"/>
-      <c r="C167" s="37"/>
-      <c r="D167" s="37"/>
+      <c r="B167" s="23"/>
+      <c r="C167" s="34"/>
+      <c r="D167" s="34"/>
       <c r="E167" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F167" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="F167" s="7" t="s">
+      <c r="G167" t="s">
         <v>374</v>
       </c>
-      <c r="G167" t="s">
+      <c r="H167" t="s">
         <v>375</v>
-      </c>
-      <c r="H167" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="18"/>
-      <c r="B168" s="18"/>
-      <c r="C168" s="37"/>
-      <c r="D168" s="37"/>
+      <c r="B168" s="23"/>
+      <c r="C168" s="34"/>
+      <c r="D168" s="34"/>
       <c r="F168" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="H168" t="s">
         <v>377</v>
-      </c>
-      <c r="H168" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="18"/>
-      <c r="B169" s="18"/>
-      <c r="C169" s="37"/>
-      <c r="D169" s="37"/>
+      <c r="B169" s="23"/>
+      <c r="C169" s="34"/>
+      <c r="D169" s="34"/>
       <c r="F169" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="H169" t="s">
         <v>379</v>
-      </c>
-      <c r="H169" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="18"/>
-      <c r="B170" s="18"/>
-      <c r="C170" s="37"/>
-      <c r="D170" s="37"/>
+      <c r="B170" s="23"/>
+      <c r="C170" s="34"/>
+      <c r="D170" s="34"/>
       <c r="F170" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="18"/>
-      <c r="B171" s="18"/>
-      <c r="C171" s="37"/>
-      <c r="D171" s="37"/>
+      <c r="B171" s="23"/>
+      <c r="C171" s="34"/>
+      <c r="D171" s="34"/>
       <c r="F171" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G171" t="s">
         <v>382</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>383</v>
-      </c>
-      <c r="H171" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="18"/>
-      <c r="B172" s="18"/>
-      <c r="C172" s="37"/>
-      <c r="D172" s="37"/>
+      <c r="B172" s="23"/>
+      <c r="C172" s="34"/>
+      <c r="D172" s="34"/>
       <c r="F172" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="18"/>
-      <c r="B173" s="18"/>
-      <c r="C173" s="37"/>
-      <c r="D173" s="37"/>
+      <c r="B173" s="23"/>
+      <c r="C173" s="34"/>
+      <c r="D173" s="34"/>
       <c r="F173" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G173" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H173" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A174" s="18"/>
-      <c r="B174" s="18"/>
-      <c r="C174" s="37"/>
-      <c r="D174" s="37"/>
+      <c r="B174" s="23"/>
+      <c r="C174" s="34"/>
+      <c r="D174" s="34"/>
       <c r="F174" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G174" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H174" s="26" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="18"/>
-      <c r="B175" s="18"/>
-      <c r="C175" s="37"/>
-      <c r="D175" s="37"/>
+      <c r="B175" s="23"/>
+      <c r="C175" s="34"/>
+      <c r="D175" s="34"/>
       <c r="F175" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="G175" t="s">
         <v>391</v>
       </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
         <v>392</v>
-      </c>
-      <c r="H175" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="18"/>
-      <c r="B176" s="18"/>
-      <c r="C176" s="37"/>
-      <c r="D176" s="37"/>
+      <c r="B176" s="23"/>
+      <c r="C176" s="34"/>
+      <c r="D176" s="34"/>
       <c r="E176" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F176" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F176" s="7" t="s">
+      <c r="G176" t="s">
         <v>395</v>
       </c>
-      <c r="G176" t="s">
+      <c r="H176" t="s">
         <v>396</v>
-      </c>
-      <c r="H176" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="18"/>
-      <c r="B177" s="18"/>
-      <c r="C177" s="37"/>
-      <c r="D177" s="37"/>
+      <c r="B177" s="23"/>
+      <c r="C177" s="34"/>
+      <c r="D177" s="34"/>
       <c r="F177" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="18"/>
-      <c r="B178" s="18"/>
-      <c r="C178" s="37"/>
-      <c r="D178" s="37"/>
+      <c r="B178" s="23"/>
+      <c r="C178" s="34"/>
+      <c r="D178" s="34"/>
       <c r="F178" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="18"/>
-      <c r="B179" s="18"/>
-      <c r="C179" s="37"/>
-      <c r="D179" s="37"/>
+      <c r="B179" s="23"/>
+      <c r="C179" s="34"/>
+      <c r="D179" s="34"/>
       <c r="F179" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="H179" t="s">
         <v>400</v>
-      </c>
-      <c r="H179" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="18"/>
-      <c r="B180" s="18"/>
-      <c r="C180" s="37"/>
-      <c r="D180" s="37"/>
+      <c r="B180" s="23"/>
+      <c r="C180" s="34"/>
+      <c r="D180" s="34"/>
       <c r="F180" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G180" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H180" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="18"/>
-      <c r="B181" s="18"/>
-      <c r="C181" s="37"/>
-      <c r="D181" s="37"/>
+      <c r="B181" s="23"/>
+      <c r="C181" s="34"/>
+      <c r="D181" s="34"/>
       <c r="F181" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="G181" t="s">
         <v>403</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>404</v>
-      </c>
-      <c r="H181" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="19"/>
-      <c r="B182" s="19"/>
-      <c r="C182" s="38"/>
-      <c r="D182" s="38"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="35"/>
+      <c r="D182" s="35"/>
       <c r="E182" s="9"/>
       <c r="F182" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/Settlements of Albany.xlsx
+++ b/Settlements of Albany.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a38c727b2e27c7e/Documents/Creative Writing/Tabletop/Albany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B017CE1-6ECA-4843-83DD-08851DEC9D9A}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="11_65DE2AC77BFDDEE96B4BBF074C2640EA306BC28E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{925EA1A6-677D-4DB7-A5F3-20F30764CD80}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="428">
   <si>
     <t>Old Kingdom</t>
   </si>
@@ -68,9 +68,6 @@
     <t>DUN EIDYNN</t>
   </si>
   <si>
-    <t>Laird Murdoch MacNab</t>
-  </si>
-  <si>
     <t>or a yale rampant gules, tressure gules</t>
   </si>
   <si>
@@ -1265,9 +1262,6 @@
     <t>Sir Dafydd Strangeway</t>
   </si>
   <si>
-    <t>vert a stone  argent</t>
-  </si>
-  <si>
     <t>azure seme de teardrop argent, a lightning bolt or</t>
   </si>
   <si>
@@ -1280,9 +1274,6 @@
     <t>per fess vert and lozengy vert and argent, a label of five or, a fox head erased much smaller gules</t>
   </si>
   <si>
-    <t>Sir Russel Foley</t>
-  </si>
-  <si>
     <t>per fess arched fretty azure and gules, vert</t>
   </si>
   <si>
@@ -1304,9 +1295,6 @@
     <t>LAIRD CHIEF OF LOTHBURN</t>
   </si>
   <si>
-    <t xml:space="preserve"> *The Pictish Clans in practice do not recognise the supremacy of Ducal tites, and the Laird Chief is a ceremonial title from The Old Kingdom</t>
-  </si>
-  <si>
     <t>Duke</t>
   </si>
   <si>
@@ -1314,6 +1302,27 @@
   </si>
   <si>
     <t>Sir Tomos ap Terwyn</t>
+  </si>
+  <si>
+    <t>Laird Murdoch MacNab  *The Pictish Clans in practice do not recognise the supremacy of Ducal tites, and the Laird Chief is a ceremonial title from The Old Kingdom</t>
+  </si>
+  <si>
+    <t>argent three bars wavy azure on a Chief indented lozengy gules and azure a lion head argent couped between two stars argent</t>
+  </si>
+  <si>
+    <t>per fess sable and fretty argent and or, two fleeces argent above a lion couchant azure</t>
+  </si>
+  <si>
+    <t>Earl Richard Cantmont</t>
+  </si>
+  <si>
+    <t>Sir Russell Foley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per pile argent and azure, a mitre azure between two anchors or, in base a book closed or leaved argent clasped vert garnished gules </t>
+  </si>
+  <si>
+    <t>vert, a stone circle argent</t>
   </si>
 </sst>
 </file>
@@ -1530,14 +1539,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1933,13 +1942,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="94" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.140625" bestFit="1" customWidth="1"/>
@@ -1947,7 +1956,7 @@
     <col min="9" max="1027" width="11.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1955,10 +1964,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -1973,18 +1982,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1993,190 +2002,187 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="F3" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="22"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
       <c r="F4" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
       <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
       <c r="F6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="F7" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
       <c r="F8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>19</v>
       </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
       <c r="F9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>22</v>
       </c>
-      <c r="H9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
       <c r="F10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
         <v>24</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>25</v>
       </c>
-      <c r="H10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
       <c r="F11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>28</v>
       </c>
-      <c r="H11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
       <c r="E12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>31</v>
       </c>
-      <c r="H12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="27"/>
       <c r="D13" s="27"/>
       <c r="F13" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="27"/>
       <c r="D14" s="27"/>
       <c r="F14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
         <v>34</v>
       </c>
-      <c r="G14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="27"/>
       <c r="D15" s="27"/>
       <c r="F15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
         <v>36</v>
       </c>
-      <c r="H15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
       <c r="F16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" t="s">
         <v>38</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>39</v>
-      </c>
-      <c r="H16" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -2185,13 +2191,13 @@
       <c r="C17" s="27"/>
       <c r="D17" s="27"/>
       <c r="F17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" t="s">
         <v>41</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>42</v>
-      </c>
-      <c r="H17" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -2200,16 +2206,16 @@
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
       <c r="E18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" t="s">
         <v>45</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>46</v>
-      </c>
-      <c r="H18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -2218,7 +2224,7 @@
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
       <c r="F19" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2227,7 +2233,7 @@
       <c r="C20" s="27"/>
       <c r="D20" s="27"/>
       <c r="F20" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -2236,7 +2242,7 @@
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
       <c r="F21" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -2245,13 +2251,13 @@
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
       <c r="F22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" t="s">
         <v>51</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>52</v>
-      </c>
-      <c r="H22" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -2260,13 +2266,13 @@
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
       <c r="F23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
         <v>54</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>55</v>
-      </c>
-      <c r="H23" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -2275,7 +2281,7 @@
       <c r="C24" s="27"/>
       <c r="D24" s="27"/>
       <c r="F24" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -2284,16 +2290,16 @@
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
       <c r="E25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" t="s">
         <v>59</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>60</v>
-      </c>
-      <c r="H25" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -2302,7 +2308,7 @@
       <c r="C26" s="27"/>
       <c r="D26" s="27"/>
       <c r="F26" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -2311,7 +2317,7 @@
       <c r="C27" s="27"/>
       <c r="D27" s="27"/>
       <c r="F27" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -2320,13 +2326,13 @@
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="F28" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" t="s">
         <v>64</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>65</v>
-      </c>
-      <c r="H28" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -2335,16 +2341,16 @@
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="G29" t="s">
         <v>68</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>69</v>
-      </c>
-      <c r="H29" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -2353,10 +2359,10 @@
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="F30" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" t="s">
         <v>71</v>
-      </c>
-      <c r="H30" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -2365,10 +2371,10 @@
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="F31" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H31" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -2377,7 +2383,7 @@
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="F32" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -2386,13 +2392,13 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="F33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s">
         <v>75</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>76</v>
-      </c>
-      <c r="H33" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -2401,16 +2407,16 @@
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" t="s">
         <v>78</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>79</v>
-      </c>
-      <c r="H34" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -2419,13 +2425,13 @@
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="F35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s">
         <v>81</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>82</v>
-      </c>
-      <c r="H35" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -2434,13 +2440,13 @@
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="F36" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" t="s">
         <v>84</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>85</v>
-      </c>
-      <c r="H36" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -2449,16 +2455,16 @@
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="G37" t="s">
         <v>88</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>89</v>
-      </c>
-      <c r="H37" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -2467,13 +2473,13 @@
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
       <c r="F38" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38" t="s">
         <v>91</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>92</v>
-      </c>
-      <c r="H38" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -2482,13 +2488,13 @@
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
       <c r="F39" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" t="s">
         <v>94</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>95</v>
-      </c>
-      <c r="H39" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -2498,33 +2504,33 @@
       <c r="D40" s="28"/>
       <c r="E40" s="9"/>
       <c r="F40" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="C41" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>101</v>
-      </c>
-      <c r="H41" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -2533,7 +2539,7 @@
       <c r="C42" s="29"/>
       <c r="D42" s="29"/>
       <c r="F42" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -2542,7 +2548,7 @@
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
       <c r="F43" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -2551,7 +2557,7 @@
       <c r="C44" s="29"/>
       <c r="D44" s="29"/>
       <c r="F44" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -2560,13 +2566,13 @@
       <c r="C45" s="29"/>
       <c r="D45" s="29"/>
       <c r="F45" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G45" t="s">
         <v>107</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>108</v>
-      </c>
-      <c r="H45" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -2575,7 +2581,7 @@
       <c r="C46" s="29"/>
       <c r="D46" s="29"/>
       <c r="F46" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -2584,13 +2590,13 @@
       <c r="C47" s="29"/>
       <c r="D47" s="29"/>
       <c r="F47" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G47" t="s">
         <v>111</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>112</v>
-      </c>
-      <c r="H47" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -2599,16 +2605,16 @@
       <c r="C48" s="30"/>
       <c r="D48" s="30"/>
       <c r="E48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="G48" t="s">
         <v>115</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>116</v>
-      </c>
-      <c r="H48" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -2617,13 +2623,13 @@
       <c r="C49" s="29"/>
       <c r="D49" s="29"/>
       <c r="F49" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G49" t="s">
         <v>118</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>119</v>
-      </c>
-      <c r="H49" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -2632,7 +2638,7 @@
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
       <c r="F50" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -2641,13 +2647,13 @@
       <c r="C51" s="29"/>
       <c r="D51" s="29"/>
       <c r="F51" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G51" t="s">
         <v>122</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>123</v>
-      </c>
-      <c r="H51" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -2656,13 +2662,13 @@
       <c r="C52" s="29"/>
       <c r="D52" s="29"/>
       <c r="F52" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G52" t="s">
         <v>125</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>126</v>
-      </c>
-      <c r="H52" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -2671,7 +2677,7 @@
       <c r="C53" s="29"/>
       <c r="D53" s="29"/>
       <c r="F53" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2680,7 +2686,7 @@
       <c r="C54" s="29"/>
       <c r="D54" s="29"/>
       <c r="F54" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2689,7 +2695,7 @@
       <c r="C55" s="29"/>
       <c r="D55" s="29"/>
       <c r="F55" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -2698,7 +2704,7 @@
       <c r="C56" s="29"/>
       <c r="D56" s="29"/>
       <c r="F56" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2707,13 +2713,13 @@
       <c r="C57" s="29"/>
       <c r="D57" s="29"/>
       <c r="F57" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57" t="s">
         <v>132</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>133</v>
-      </c>
-      <c r="H57" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2722,7 +2728,7 @@
       <c r="C58" s="29"/>
       <c r="D58" s="29"/>
       <c r="F58" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -2731,16 +2737,16 @@
       <c r="C59" s="29"/>
       <c r="D59" s="29"/>
       <c r="E59" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="G59" t="s">
         <v>137</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>138</v>
-      </c>
-      <c r="H59" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -2749,7 +2755,7 @@
       <c r="C60" s="29"/>
       <c r="D60" s="29"/>
       <c r="F60" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -2758,7 +2764,7 @@
       <c r="C61" s="29"/>
       <c r="D61" s="29"/>
       <c r="F61" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -2767,13 +2773,13 @@
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
       <c r="F62" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G62" t="s">
         <v>142</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>143</v>
-      </c>
-      <c r="H62" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -2782,7 +2788,7 @@
       <c r="C63" s="29"/>
       <c r="D63" s="29"/>
       <c r="F63" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -2791,10 +2797,10 @@
       <c r="C64" s="29"/>
       <c r="D64" s="29"/>
       <c r="E64" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F64" s="7" t="s">
         <v>146</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -2804,31 +2810,31 @@
       <c r="D65" s="31"/>
       <c r="E65" s="9"/>
       <c r="F65" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="12"/>
       <c r="B66" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="G66" t="s">
         <v>151</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>152</v>
-      </c>
-      <c r="H66" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -2837,13 +2843,13 @@
       <c r="C67" s="29"/>
       <c r="D67" s="29"/>
       <c r="F67" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G67" t="s">
         <v>155</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>156</v>
-      </c>
-      <c r="H67" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -2852,7 +2858,7 @@
       <c r="C68" s="29"/>
       <c r="D68" s="29"/>
       <c r="F68" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -2861,7 +2867,7 @@
       <c r="C69" s="29"/>
       <c r="D69" s="29"/>
       <c r="F69" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -2870,7 +2876,7 @@
       <c r="C70" s="29"/>
       <c r="D70" s="29"/>
       <c r="F70" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -2879,10 +2885,10 @@
       <c r="C71" s="29"/>
       <c r="D71" s="29"/>
       <c r="F71" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H71" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -2891,7 +2897,7 @@
       <c r="C72" s="29"/>
       <c r="D72" s="29"/>
       <c r="F72" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -2900,16 +2906,16 @@
       <c r="C73" s="29"/>
       <c r="D73" s="29"/>
       <c r="E73" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="G73" t="s">
         <v>165</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>166</v>
-      </c>
-      <c r="H73" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -2918,7 +2924,7 @@
       <c r="C74" s="29"/>
       <c r="D74" s="29"/>
       <c r="F74" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -2927,13 +2933,13 @@
       <c r="C75" s="29"/>
       <c r="D75" s="29"/>
       <c r="F75" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G75" t="s">
         <v>169</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>170</v>
-      </c>
-      <c r="H75" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -2942,13 +2948,13 @@
       <c r="C76" s="29"/>
       <c r="D76" s="29"/>
       <c r="F76" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G76" t="s">
+        <v>420</v>
+      </c>
+      <c r="H76" t="s">
         <v>172</v>
-      </c>
-      <c r="G76" t="s">
-        <v>424</v>
-      </c>
-      <c r="H76" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -2957,7 +2963,7 @@
       <c r="C77" s="29"/>
       <c r="D77" s="29"/>
       <c r="F77" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -2966,13 +2972,13 @@
       <c r="C78" s="29"/>
       <c r="D78" s="29"/>
       <c r="F78" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>176</v>
-      </c>
-      <c r="H78" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -2981,7 +2987,7 @@
       <c r="C79" s="29"/>
       <c r="D79" s="29"/>
       <c r="F79" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -2990,7 +2996,7 @@
       <c r="C80" s="29"/>
       <c r="D80" s="29"/>
       <c r="F80" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -2999,13 +3005,13 @@
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
       <c r="F81" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G81" t="s">
         <v>180</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>181</v>
-      </c>
-      <c r="H81" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -3014,13 +3020,13 @@
       <c r="C82" s="29"/>
       <c r="D82" s="29"/>
       <c r="F82" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G82" t="s">
         <v>183</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>184</v>
-      </c>
-      <c r="H82" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -3029,13 +3035,13 @@
       <c r="C83" s="29"/>
       <c r="D83" s="29"/>
       <c r="F83" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G83" t="s">
         <v>186</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>187</v>
-      </c>
-      <c r="H83" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -3044,13 +3050,13 @@
       <c r="C84" s="29"/>
       <c r="D84" s="29"/>
       <c r="F84" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G84" t="s">
         <v>189</v>
       </c>
-      <c r="G84" t="s">
-        <v>190</v>
-      </c>
       <c r="H84" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -3059,16 +3065,16 @@
       <c r="C85" s="29"/>
       <c r="D85" s="29"/>
       <c r="E85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="G85" t="s">
         <v>192</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>193</v>
-      </c>
-      <c r="H85" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -3077,7 +3083,7 @@
       <c r="C86" s="29"/>
       <c r="D86" s="29"/>
       <c r="F86" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -3086,16 +3092,16 @@
       <c r="C87" s="29"/>
       <c r="D87" s="29"/>
       <c r="E87" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="G87" t="s">
         <v>197</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>198</v>
-      </c>
-      <c r="H87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -3104,7 +3110,7 @@
       <c r="C88" s="29"/>
       <c r="D88" s="29"/>
       <c r="F88" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -3113,13 +3119,13 @@
       <c r="C89" s="29"/>
       <c r="D89" s="29"/>
       <c r="F89" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G89" t="s">
         <v>201</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>202</v>
-      </c>
-      <c r="H89" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -3128,7 +3134,7 @@
       <c r="C90" s="29"/>
       <c r="D90" s="29"/>
       <c r="F90" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -3137,7 +3143,7 @@
       <c r="C91" s="29"/>
       <c r="D91" s="29"/>
       <c r="F91" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -3146,7 +3152,7 @@
       <c r="C92" s="29"/>
       <c r="D92" s="29"/>
       <c r="F92" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -3155,7 +3161,7 @@
       <c r="C93" s="29"/>
       <c r="D93" s="29"/>
       <c r="F93" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -3164,13 +3170,13 @@
       <c r="C94" s="29"/>
       <c r="D94" s="29"/>
       <c r="F94" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G94" t="s">
         <v>208</v>
       </c>
-      <c r="G94" t="s">
-        <v>209</v>
-      </c>
       <c r="H94" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -3179,13 +3185,13 @@
       <c r="C95" s="29"/>
       <c r="D95" s="29"/>
       <c r="F95" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G95" t="s">
         <v>210</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>211</v>
-      </c>
-      <c r="H95" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -3194,7 +3200,7 @@
       <c r="C96" s="29"/>
       <c r="D96" s="29"/>
       <c r="F96" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -3203,16 +3209,16 @@
       <c r="C97" s="29"/>
       <c r="D97" s="29"/>
       <c r="E97" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F97" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="G97" t="s">
         <v>215</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>216</v>
-      </c>
-      <c r="H97" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -3222,39 +3228,39 @@
       <c r="D98" s="31"/>
       <c r="E98" s="9"/>
       <c r="F98" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G98" t="s">
+        <v>405</v>
+      </c>
+      <c r="H98" t="s">
         <v>218</v>
-      </c>
-      <c r="G98" t="s">
-        <v>406</v>
-      </c>
-      <c r="H98" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="C99" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C99" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="E99" s="3" t="s">
+      <c r="F99" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G99" t="s">
         <v>222</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>223</v>
-      </c>
-      <c r="H99" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -3263,7 +3269,7 @@
       <c r="C100" s="32"/>
       <c r="D100" s="32"/>
       <c r="F100" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -3272,7 +3278,7 @@
       <c r="C101" s="32"/>
       <c r="D101" s="32"/>
       <c r="F101" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
@@ -3281,7 +3287,7 @@
       <c r="C102" s="32"/>
       <c r="D102" s="32"/>
       <c r="F102" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -3290,13 +3296,13 @@
       <c r="C103" s="32"/>
       <c r="D103" s="32"/>
       <c r="F103" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G103" t="s">
         <v>230</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>231</v>
-      </c>
-      <c r="H103" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -3305,13 +3311,13 @@
       <c r="C104" s="32"/>
       <c r="D104" s="32"/>
       <c r="F104" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G104" t="s">
         <v>233</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>234</v>
-      </c>
-      <c r="H104" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -3320,7 +3326,7 @@
       <c r="C105" s="32"/>
       <c r="D105" s="32"/>
       <c r="F105" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -3329,16 +3335,16 @@
       <c r="C106" s="32"/>
       <c r="D106" s="32"/>
       <c r="E106" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G106" t="s">
         <v>237</v>
       </c>
-      <c r="F106" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G106" t="s">
-        <v>238</v>
-      </c>
       <c r="H106" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -3347,13 +3353,13 @@
       <c r="C107" s="32"/>
       <c r="D107" s="32"/>
       <c r="F107" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G107" t="s">
         <v>239</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>240</v>
-      </c>
-      <c r="H107" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -3362,7 +3368,7 @@
       <c r="C108" s="32"/>
       <c r="D108" s="32"/>
       <c r="F108" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -3371,13 +3377,13 @@
       <c r="C109" s="32"/>
       <c r="D109" s="32"/>
       <c r="F109" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="G109" t="s">
         <v>243</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>244</v>
-      </c>
-      <c r="H109" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -3386,7 +3392,7 @@
       <c r="C110" s="32"/>
       <c r="D110" s="32"/>
       <c r="F110" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -3395,13 +3401,13 @@
       <c r="C111" s="32"/>
       <c r="D111" s="32"/>
       <c r="F111" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G111" t="s">
         <v>247</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>248</v>
-      </c>
-      <c r="H111" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -3410,13 +3416,13 @@
       <c r="C112" s="32"/>
       <c r="D112" s="32"/>
       <c r="F112" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G112" t="s">
         <v>250</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>251</v>
-      </c>
-      <c r="H112" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -3425,13 +3431,13 @@
       <c r="C113" s="32"/>
       <c r="D113" s="32"/>
       <c r="F113" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G113" t="s">
         <v>253</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>254</v>
-      </c>
-      <c r="H113" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -3440,13 +3446,13 @@
       <c r="C114" s="32"/>
       <c r="D114" s="32"/>
       <c r="F114" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G114" t="s">
         <v>256</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>257</v>
-      </c>
-      <c r="H114" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -3455,13 +3461,13 @@
       <c r="C115" s="32"/>
       <c r="D115" s="32"/>
       <c r="F115" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G115" t="s">
         <v>259</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>260</v>
-      </c>
-      <c r="H115" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -3470,16 +3476,16 @@
       <c r="C116" s="32"/>
       <c r="D116" s="32"/>
       <c r="E116" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G116" t="s">
         <v>262</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>263</v>
-      </c>
-      <c r="H116" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -3488,7 +3494,7 @@
       <c r="C117" s="32"/>
       <c r="D117" s="32"/>
       <c r="F117" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -3497,13 +3503,13 @@
       <c r="C118" s="32"/>
       <c r="D118" s="32"/>
       <c r="F118" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="G118" t="s">
         <v>266</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>267</v>
-      </c>
-      <c r="H118" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -3512,13 +3518,13 @@
       <c r="C119" s="32"/>
       <c r="D119" s="32"/>
       <c r="F119" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G119" t="s">
         <v>269</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>270</v>
-      </c>
-      <c r="H119" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -3527,7 +3533,7 @@
       <c r="C120" s="32"/>
       <c r="D120" s="32"/>
       <c r="F120" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -3536,10 +3542,10 @@
       <c r="C121" s="32"/>
       <c r="D121" s="32"/>
       <c r="F121" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H121" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -3548,7 +3554,7 @@
       <c r="C122" s="32"/>
       <c r="D122" s="32"/>
       <c r="F122" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -3557,13 +3563,13 @@
       <c r="C123" s="32"/>
       <c r="D123" s="32"/>
       <c r="F123" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="G123" t="s">
         <v>275</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>276</v>
-      </c>
-      <c r="H123" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -3572,13 +3578,13 @@
       <c r="C124" s="32"/>
       <c r="D124" s="32"/>
       <c r="F124" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="G124" t="s">
         <v>278</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>279</v>
-      </c>
-      <c r="H124" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -3587,13 +3593,13 @@
       <c r="C125" s="32"/>
       <c r="D125" s="32"/>
       <c r="F125" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G125" t="s">
         <v>281</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>282</v>
-      </c>
-      <c r="H125" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -3602,7 +3608,7 @@
       <c r="C126" s="32"/>
       <c r="D126" s="32"/>
       <c r="F126" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -3611,16 +3617,16 @@
       <c r="C127" s="32"/>
       <c r="D127" s="32"/>
       <c r="E127" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G127" t="s">
         <v>285</v>
       </c>
-      <c r="F127" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>286</v>
-      </c>
-      <c r="H127" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -3630,39 +3636,39 @@
       <c r="D128" s="33"/>
       <c r="E128" s="9"/>
       <c r="F128" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G128" t="s">
         <v>288</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>289</v>
-      </c>
-      <c r="H128" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="B129" s="24" t="s">
         <v>291</v>
       </c>
-      <c r="B129" s="24" t="s">
+      <c r="C129" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D129" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C129" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="D129" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="E129" s="3" t="s">
+      <c r="F129" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G129" t="s">
         <v>293</v>
       </c>
-      <c r="F129" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>294</v>
-      </c>
-      <c r="H129" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -3671,7 +3677,7 @@
       <c r="C130" s="34"/>
       <c r="D130" s="34"/>
       <c r="F130" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -3680,13 +3686,13 @@
       <c r="C131" s="34"/>
       <c r="D131" s="34"/>
       <c r="F131" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="G131" t="s">
         <v>298</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>299</v>
-      </c>
-      <c r="H131" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -3695,7 +3701,7 @@
       <c r="C132" s="34"/>
       <c r="D132" s="34"/>
       <c r="F132" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -3704,7 +3710,7 @@
       <c r="C133" s="34"/>
       <c r="D133" s="34"/>
       <c r="F133" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -3713,13 +3719,13 @@
       <c r="C134" s="34"/>
       <c r="D134" s="34"/>
       <c r="F134" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="G134" t="s">
         <v>303</v>
       </c>
-      <c r="G134" t="s">
+      <c r="H134" t="s">
         <v>304</v>
-      </c>
-      <c r="H134" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -3728,7 +3734,7 @@
       <c r="C135" s="34"/>
       <c r="D135" s="34"/>
       <c r="F135" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -3737,7 +3743,7 @@
       <c r="C136" s="34"/>
       <c r="D136" s="34"/>
       <c r="F136" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -3746,13 +3752,13 @@
       <c r="C137" s="34"/>
       <c r="D137" s="34"/>
       <c r="F137" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G137" t="s">
         <v>308</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>309</v>
-      </c>
-      <c r="H137" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -3761,7 +3767,7 @@
       <c r="C138" s="34"/>
       <c r="D138" s="34"/>
       <c r="F138" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -3770,7 +3776,7 @@
       <c r="C139" s="34"/>
       <c r="D139" s="34"/>
       <c r="F139" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
@@ -3779,16 +3785,16 @@
       <c r="C140" s="34"/>
       <c r="D140" s="34"/>
       <c r="E140" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G140" t="s">
         <v>313</v>
       </c>
-      <c r="F140" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>314</v>
-      </c>
-      <c r="H140" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -3797,7 +3803,7 @@
       <c r="C141" s="34"/>
       <c r="D141" s="34"/>
       <c r="F141" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -3806,7 +3812,7 @@
       <c r="C142" s="34"/>
       <c r="D142" s="34"/>
       <c r="F142" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
@@ -3815,7 +3821,7 @@
       <c r="C143" s="34"/>
       <c r="D143" s="34"/>
       <c r="F143" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -3824,16 +3830,16 @@
       <c r="C144" s="34"/>
       <c r="D144" s="34"/>
       <c r="E144" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="F144" s="7" t="s">
+      <c r="G144" t="s">
         <v>320</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>321</v>
-      </c>
-      <c r="H144" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -3842,7 +3848,7 @@
       <c r="C145" s="34"/>
       <c r="D145" s="34"/>
       <c r="F145" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -3851,13 +3857,13 @@
       <c r="C146" s="34"/>
       <c r="D146" s="34"/>
       <c r="F146" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G146" t="s">
         <v>324</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>325</v>
-      </c>
-      <c r="H146" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -3866,7 +3872,7 @@
       <c r="C147" s="34"/>
       <c r="D147" s="34"/>
       <c r="F147" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -3875,7 +3881,7 @@
       <c r="C148" s="34"/>
       <c r="D148" s="34"/>
       <c r="F148" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -3884,16 +3890,16 @@
       <c r="C149" s="34"/>
       <c r="D149" s="34"/>
       <c r="E149" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F149" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="F149" s="7" t="s">
+      <c r="G149" t="s">
         <v>330</v>
       </c>
-      <c r="G149" t="s">
+      <c r="H149" t="s">
         <v>331</v>
-      </c>
-      <c r="H149" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -3902,7 +3908,7 @@
       <c r="C150" s="34"/>
       <c r="D150" s="34"/>
       <c r="F150" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -3911,13 +3917,13 @@
       <c r="C151" s="34"/>
       <c r="D151" s="34"/>
       <c r="F151" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G151" t="s">
         <v>334</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="s">
         <v>335</v>
-      </c>
-      <c r="H151" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -3927,34 +3933,37 @@
       <c r="D152" s="35"/>
       <c r="E152" s="9"/>
       <c r="F152" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="G152" t="s">
         <v>337</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" t="s">
         <v>338</v>
-      </c>
-      <c r="H152" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="18"/>
       <c r="B153" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="C153" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D153" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C153" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="D153" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="E153" s="1" t="s">
+      <c r="F153" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="F153" s="7" t="s">
+      <c r="G153" t="s">
         <v>342</v>
       </c>
-      <c r="G153" t="s">
-        <v>343</v>
+      <c r="H153" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -3963,13 +3972,13 @@
       <c r="C154" s="34"/>
       <c r="D154" s="34"/>
       <c r="F154" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="G154" t="s">
         <v>345</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" t="s">
         <v>346</v>
-      </c>
-      <c r="H154" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -3978,13 +3987,13 @@
       <c r="C155" s="34"/>
       <c r="D155" s="34"/>
       <c r="F155" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G155" t="s">
         <v>349</v>
       </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
         <v>350</v>
-      </c>
-      <c r="H155" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -3993,7 +4002,13 @@
       <c r="C156" s="34"/>
       <c r="D156" s="34"/>
       <c r="F156" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
+      </c>
+      <c r="G156" t="s">
+        <v>394</v>
+      </c>
+      <c r="H156" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -4002,7 +4017,7 @@
       <c r="C157" s="34"/>
       <c r="D157" s="34"/>
       <c r="F157" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -4011,13 +4026,13 @@
       <c r="C158" s="34"/>
       <c r="D158" s="34"/>
       <c r="F158" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="G158" t="s">
         <v>354</v>
       </c>
-      <c r="G158" t="s">
-        <v>355</v>
-      </c>
       <c r="H158" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -4026,7 +4041,7 @@
       <c r="C159" s="34"/>
       <c r="D159" s="34"/>
       <c r="F159" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -4035,7 +4050,7 @@
       <c r="C160" s="34"/>
       <c r="D160" s="34"/>
       <c r="F160" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -4044,16 +4059,16 @@
       <c r="C161" s="34"/>
       <c r="D161" s="34"/>
       <c r="E161" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F161" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="F161" s="7" t="s">
+      <c r="G161" t="s">
         <v>359</v>
       </c>
-      <c r="G161" t="s">
+      <c r="H161" t="s">
         <v>360</v>
-      </c>
-      <c r="H161" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -4062,10 +4077,10 @@
       <c r="C162" s="34"/>
       <c r="D162" s="34"/>
       <c r="F162" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H162" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -4074,13 +4089,13 @@
       <c r="C163" s="34"/>
       <c r="D163" s="34"/>
       <c r="F163" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G163" t="s">
+        <v>406</v>
+      </c>
+      <c r="H163" t="s">
         <v>363</v>
-      </c>
-      <c r="G163" t="s">
-        <v>407</v>
-      </c>
-      <c r="H163" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
@@ -4089,7 +4104,10 @@
       <c r="C164" s="34"/>
       <c r="D164" s="34"/>
       <c r="F164" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
+      </c>
+      <c r="H164" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -4098,13 +4116,13 @@
       <c r="C165" s="34"/>
       <c r="D165" s="34"/>
       <c r="F165" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="G165" t="s">
         <v>366</v>
       </c>
-      <c r="G165" t="s">
+      <c r="H165" t="s">
         <v>367</v>
-      </c>
-      <c r="H165" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -4113,13 +4131,13 @@
       <c r="C166" s="34"/>
       <c r="D166" s="34"/>
       <c r="F166" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="G166" t="s">
         <v>369</v>
       </c>
-      <c r="G166" t="s">
+      <c r="H166" t="s">
         <v>370</v>
-      </c>
-      <c r="H166" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -4128,16 +4146,16 @@
       <c r="C167" s="34"/>
       <c r="D167" s="34"/>
       <c r="E167" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F167" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F167" s="7" t="s">
+      <c r="G167" t="s">
         <v>373</v>
       </c>
-      <c r="G167" t="s">
+      <c r="H167" t="s">
         <v>374</v>
-      </c>
-      <c r="H167" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
@@ -4146,10 +4164,10 @@
       <c r="C168" s="34"/>
       <c r="D168" s="34"/>
       <c r="F168" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H168" t="s">
         <v>376</v>
-      </c>
-      <c r="H168" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
@@ -4158,10 +4176,10 @@
       <c r="C169" s="34"/>
       <c r="D169" s="34"/>
       <c r="F169" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="H169" t="s">
         <v>378</v>
-      </c>
-      <c r="H169" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
@@ -4170,7 +4188,7 @@
       <c r="C170" s="34"/>
       <c r="D170" s="34"/>
       <c r="F170" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -4179,13 +4197,13 @@
       <c r="C171" s="34"/>
       <c r="D171" s="34"/>
       <c r="F171" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G171" t="s">
         <v>381</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>382</v>
-      </c>
-      <c r="H171" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -4194,7 +4212,7 @@
       <c r="C172" s="34"/>
       <c r="D172" s="34"/>
       <c r="F172" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -4203,13 +4221,13 @@
       <c r="C173" s="34"/>
       <c r="D173" s="34"/>
       <c r="F173" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G173" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H173" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
@@ -4218,13 +4236,13 @@
       <c r="C174" s="34"/>
       <c r="D174" s="34"/>
       <c r="F174" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G174" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H174" s="26" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -4233,13 +4251,13 @@
       <c r="C175" s="34"/>
       <c r="D175" s="34"/>
       <c r="F175" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="G175" t="s">
         <v>390</v>
       </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
         <v>391</v>
-      </c>
-      <c r="H175" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
@@ -4248,16 +4266,16 @@
       <c r="C176" s="34"/>
       <c r="D176" s="34"/>
       <c r="E176" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F176" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="F176" s="7" t="s">
-        <v>394</v>
-      </c>
       <c r="G176" t="s">
+        <v>424</v>
+      </c>
+      <c r="H176" t="s">
         <v>395</v>
-      </c>
-      <c r="H176" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
@@ -4266,7 +4284,7 @@
       <c r="C177" s="34"/>
       <c r="D177" s="34"/>
       <c r="F177" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
@@ -4275,7 +4293,7 @@
       <c r="C178" s="34"/>
       <c r="D178" s="34"/>
       <c r="F178" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
@@ -4284,10 +4302,10 @@
       <c r="C179" s="34"/>
       <c r="D179" s="34"/>
       <c r="F179" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="H179" t="s">
         <v>399</v>
-      </c>
-      <c r="H179" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -4296,13 +4314,13 @@
       <c r="C180" s="34"/>
       <c r="D180" s="34"/>
       <c r="F180" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G180" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="H180" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -4311,13 +4329,13 @@
       <c r="C181" s="34"/>
       <c r="D181" s="34"/>
       <c r="F181" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="G181" t="s">
         <v>402</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>403</v>
-      </c>
-      <c r="H181" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -4327,7 +4345,7 @@
       <c r="D182" s="35"/>
       <c r="E182" s="9"/>
       <c r="F182" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
